--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="F14" t="n">
-        <v>14.89</v>
+        <v>15.19</v>
       </c>
       <c r="G14" t="n">
-        <v>323.6</v>
+        <v>333.9</v>
       </c>
       <c r="H14" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>45.98</v>
+        <v>95.03</v>
       </c>
       <c r="K14" t="n">
-        <v>48.2</v>
+        <v>-95.62</v>
       </c>
       <c r="L14" t="n">
-        <v>66.61</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:43:35</t>
+          <t>05:43:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6.67</v>
+        <v>5.38</v>
       </c>
       <c r="F15" t="n">
-        <v>15.94</v>
+        <v>15.08</v>
       </c>
       <c r="G15" t="n">
-        <v>323.3</v>
+        <v>324.9</v>
       </c>
       <c r="H15" t="n">
-        <v>77.7</v>
+        <v>71.3</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-61.25</v>
+        <v>-21.41</v>
       </c>
       <c r="K15" t="n">
-        <v>70.15000000000001</v>
+        <v>-170.32</v>
       </c>
       <c r="L15" t="n">
-        <v>93.13</v>
+        <v>171.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:45:40</t>
+          <t>05:44:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.76</v>
+        <v>5.92</v>
       </c>
       <c r="F16" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="G16" t="n">
-        <v>323</v>
+        <v>326.5</v>
       </c>
       <c r="H16" t="n">
-        <v>76.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-185.13</v>
+        <v>19.57</v>
       </c>
       <c r="K16" t="n">
-        <v>292.16</v>
+        <v>121.19</v>
       </c>
       <c r="L16" t="n">
-        <v>345.87</v>
+        <v>122.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:51:05</t>
+          <t>05:50:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.13</v>
+        <v>4.9</v>
       </c>
       <c r="F17" t="n">
-        <v>15.25</v>
+        <v>15.56</v>
       </c>
       <c r="G17" t="n">
-        <v>317.1</v>
+        <v>319</v>
       </c>
       <c r="H17" t="n">
-        <v>78.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>381.68</v>
+        <v>213.05</v>
       </c>
       <c r="K17" t="n">
-        <v>-205.83</v>
+        <v>193.69</v>
       </c>
       <c r="L17" t="n">
-        <v>433.64</v>
+        <v>287.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:52:51</t>
+          <t>05:51:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.34</v>
+        <v>5.23</v>
       </c>
       <c r="F18" t="n">
-        <v>14.8</v>
+        <v>14.73</v>
       </c>
       <c r="G18" t="n">
-        <v>321.8</v>
+        <v>340.4</v>
       </c>
       <c r="H18" t="n">
-        <v>80.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>136.6</v>
+        <v>-238.05</v>
       </c>
       <c r="K18" t="n">
-        <v>325.16</v>
+        <v>136.81</v>
       </c>
       <c r="L18" t="n">
-        <v>352.69</v>
+        <v>274.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:54:29</t>
+          <t>05:53:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.75</v>
+        <v>4.38</v>
       </c>
       <c r="F19" t="n">
-        <v>14.7</v>
+        <v>16.08</v>
       </c>
       <c r="G19" t="n">
-        <v>335.7</v>
+        <v>327.6</v>
       </c>
       <c r="H19" t="n">
-        <v>68.2</v>
+        <v>77.2</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-172.67</v>
+        <v>134.54</v>
       </c>
       <c r="K19" t="n">
-        <v>313.25</v>
+        <v>37.34</v>
       </c>
       <c r="L19" t="n">
-        <v>357.69</v>
+        <v>139.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:58:46</t>
+          <t>05:57:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5.57</v>
       </c>
       <c r="F20" t="n">
-        <v>15.59</v>
+        <v>14.12</v>
       </c>
       <c r="G20" t="n">
-        <v>317.2</v>
+        <v>316.4</v>
       </c>
       <c r="H20" t="n">
-        <v>73.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-297.81</v>
+        <v>-525.15</v>
       </c>
       <c r="K20" t="n">
-        <v>-489.37</v>
+        <v>390.08</v>
       </c>
       <c r="L20" t="n">
-        <v>572.87</v>
+        <v>654.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:00:35</t>
+          <t>06:00:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.15</v>
+        <v>4.99</v>
       </c>
       <c r="F21" t="n">
-        <v>15.04</v>
+        <v>15.4</v>
       </c>
       <c r="G21" t="n">
-        <v>332.4</v>
+        <v>323.1</v>
       </c>
       <c r="H21" t="n">
-        <v>74.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>229.54</v>
+        <v>265.59</v>
       </c>
       <c r="K21" t="n">
-        <v>325.02</v>
+        <v>-307.82</v>
       </c>
       <c r="L21" t="n">
-        <v>397.9</v>
+        <v>406.56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:02:35</t>
+          <t>06:02:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.13</v>
+        <v>5.53</v>
       </c>
       <c r="F22" t="n">
-        <v>15.06</v>
+        <v>14.38</v>
       </c>
       <c r="G22" t="n">
-        <v>305.2</v>
+        <v>325.2</v>
       </c>
       <c r="H22" t="n">
-        <v>79.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>290.74</v>
+        <v>-122.48</v>
       </c>
       <c r="K22" t="n">
-        <v>-202.97</v>
+        <v>-121.6</v>
       </c>
       <c r="L22" t="n">
-        <v>354.58</v>
+        <v>172.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:07:51</t>
+          <t>06:05:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.08</v>
+        <v>5.22</v>
       </c>
       <c r="F23" t="n">
-        <v>15.69</v>
+        <v>15.01</v>
       </c>
       <c r="G23" t="n">
-        <v>339.1</v>
+        <v>321.7</v>
       </c>
       <c r="H23" t="n">
-        <v>67.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>586.02</v>
+        <v>18.53</v>
       </c>
       <c r="K23" t="n">
-        <v>330.86</v>
+        <v>-266.27</v>
       </c>
       <c r="L23" t="n">
-        <v>672.97</v>
+        <v>266.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:08:45</t>
+          <t>06:06:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.36</v>
+        <v>4.61</v>
       </c>
       <c r="F24" t="n">
-        <v>14.89</v>
+        <v>15.06</v>
       </c>
       <c r="G24" t="n">
-        <v>311</v>
+        <v>325.2</v>
       </c>
       <c r="H24" t="n">
-        <v>77</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>191.66</v>
+        <v>-194.52</v>
       </c>
       <c r="K24" t="n">
-        <v>180.82</v>
+        <v>415.59</v>
       </c>
       <c r="L24" t="n">
-        <v>263.49</v>
+        <v>458.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:09:54</t>
+          <t>06:08:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.06</v>
+        <v>5.35</v>
       </c>
       <c r="F25" t="n">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>324.1</v>
+        <v>329.6</v>
       </c>
       <c r="H25" t="n">
-        <v>65.3</v>
+        <v>80</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>297.18</v>
+        <v>333.76</v>
       </c>
       <c r="K25" t="n">
-        <v>-396.38</v>
+        <v>231.3</v>
       </c>
       <c r="L25" t="n">
-        <v>495.41</v>
+        <v>406.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:16:06</t>
+          <t>06:12:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.96</v>
+        <v>5.43</v>
       </c>
       <c r="F26" t="n">
-        <v>15.62</v>
+        <v>15.16</v>
       </c>
       <c r="G26" t="n">
-        <v>335.6</v>
+        <v>334.4</v>
       </c>
       <c r="H26" t="n">
-        <v>78.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-369.94</v>
+        <v>434.6</v>
       </c>
       <c r="K26" t="n">
-        <v>978.47</v>
+        <v>-95.92</v>
       </c>
       <c r="L26" t="n">
-        <v>1046.07</v>
+        <v>445.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:17:18</t>
+          <t>06:13:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.57</v>
+        <v>4.8</v>
       </c>
       <c r="F27" t="n">
-        <v>15.15</v>
+        <v>15.47</v>
       </c>
       <c r="G27" t="n">
-        <v>316.2</v>
+        <v>332.2</v>
       </c>
       <c r="H27" t="n">
-        <v>70.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>665.36</v>
+        <v>-143.54</v>
       </c>
       <c r="K27" t="n">
-        <v>-125.36</v>
+        <v>-195.28</v>
       </c>
       <c r="L27" t="n">
-        <v>677.0599999999999</v>
+        <v>242.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:19:42</t>
+          <t>06:15:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.23</v>
+        <v>5.46</v>
       </c>
       <c r="F28" t="n">
-        <v>15.29</v>
+        <v>14.5</v>
       </c>
       <c r="G28" t="n">
-        <v>322.4</v>
+        <v>347.6</v>
       </c>
       <c r="H28" t="n">
-        <v>68.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="I28" t="n">
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>153.29</v>
+        <v>179.94</v>
       </c>
       <c r="K28" t="n">
-        <v>-565.08</v>
+        <v>416.69</v>
       </c>
       <c r="L28" t="n">
-        <v>585.5</v>
+        <v>453.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:32:17</t>
+          <t>06:26:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.72</v>
+        <v>4.94</v>
       </c>
       <c r="F29" t="n">
-        <v>15.36</v>
+        <v>14.53</v>
       </c>
       <c r="G29" t="n">
-        <v>310.4</v>
+        <v>320.5</v>
       </c>
       <c r="H29" t="n">
-        <v>77.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>83.7</v>
+        <v>112.66</v>
       </c>
       <c r="K29" t="n">
-        <v>333.94</v>
+        <v>-164.83</v>
       </c>
       <c r="L29" t="n">
-        <v>344.27</v>
+        <v>199.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:33:29</t>
+          <t>06:27:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.32</v>
+        <v>5.15</v>
       </c>
       <c r="F30" t="n">
-        <v>15.63</v>
+        <v>15.42</v>
       </c>
       <c r="G30" t="n">
-        <v>326.4</v>
+        <v>330.9</v>
       </c>
       <c r="H30" t="n">
-        <v>77.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-202.3</v>
+        <v>-14.78</v>
       </c>
       <c r="K30" t="n">
-        <v>167.05</v>
+        <v>46.9</v>
       </c>
       <c r="L30" t="n">
-        <v>262.36</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:35:59</t>
+          <t>06:28:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.56</v>
+        <v>5.54</v>
       </c>
       <c r="F31" t="n">
-        <v>14.83</v>
+        <v>14.67</v>
       </c>
       <c r="G31" t="n">
-        <v>325.2</v>
+        <v>330.3</v>
       </c>
       <c r="H31" t="n">
-        <v>79</v>
+        <v>71.5</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>70.01000000000001</v>
+        <v>-35.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-176.92</v>
+        <v>-10.85</v>
       </c>
       <c r="L31" t="n">
-        <v>190.27</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:41:51</t>
+          <t>06:33:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.03</v>
+        <v>5.5</v>
       </c>
       <c r="F32" t="n">
-        <v>15.44</v>
+        <v>15.57</v>
       </c>
       <c r="G32" t="n">
-        <v>326</v>
+        <v>327.2</v>
       </c>
       <c r="H32" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-53.92</v>
+        <v>-129.56</v>
       </c>
       <c r="K32" t="n">
-        <v>256.54</v>
+        <v>-262.8</v>
       </c>
       <c r="L32" t="n">
-        <v>262.15</v>
+        <v>293.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:44:09</t>
+          <t>06:35:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.12</v>
+        <v>4.72</v>
       </c>
       <c r="F33" t="n">
-        <v>15.92</v>
+        <v>14.74</v>
       </c>
       <c r="G33" t="n">
-        <v>324.2</v>
+        <v>331.1</v>
       </c>
       <c r="H33" t="n">
-        <v>84.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>139.12</v>
+        <v>-40.02</v>
       </c>
       <c r="K33" t="n">
-        <v>145.83</v>
+        <v>152.16</v>
       </c>
       <c r="L33" t="n">
-        <v>201.55</v>
+        <v>157.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:45:03</t>
+          <t>06:37:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.34</v>
+        <v>5.89</v>
       </c>
       <c r="F34" t="n">
-        <v>15.04</v>
+        <v>14.89</v>
       </c>
       <c r="G34" t="n">
-        <v>325.9</v>
+        <v>326.8</v>
       </c>
       <c r="H34" t="n">
-        <v>73.2</v>
+        <v>80.3</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>275.63</v>
+        <v>-2.4</v>
       </c>
       <c r="K34" t="n">
-        <v>-151.1</v>
+        <v>-134.02</v>
       </c>
       <c r="L34" t="n">
-        <v>314.33</v>
+        <v>134.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:49:46</t>
+          <t>06:41:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.61</v>
+        <v>5.04</v>
       </c>
       <c r="F35" t="n">
-        <v>15.37</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>328.9</v>
+        <v>325.2</v>
       </c>
       <c r="H35" t="n">
-        <v>75.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-111.43</v>
+        <v>132.34</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.36</v>
+        <v>-245.15</v>
       </c>
       <c r="L35" t="n">
-        <v>111.43</v>
+        <v>278.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:51:27</t>
+          <t>06:43:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.32</v>
+        <v>5.4</v>
       </c>
       <c r="F36" t="n">
-        <v>15.07</v>
+        <v>15.27</v>
       </c>
       <c r="G36" t="n">
-        <v>339.5</v>
+        <v>321.1</v>
       </c>
       <c r="H36" t="n">
-        <v>72.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>302.93</v>
+        <v>-418.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-274.78</v>
+        <v>114.12</v>
       </c>
       <c r="L36" t="n">
-        <v>408.99</v>
+        <v>433.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:52:56</t>
+          <t>06:45:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.58</v>
+        <v>5.78</v>
       </c>
       <c r="F37" t="n">
-        <v>16.25</v>
+        <v>15.1</v>
       </c>
       <c r="G37" t="n">
-        <v>332.1</v>
+        <v>304.2</v>
       </c>
       <c r="H37" t="n">
-        <v>69.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>427.39</v>
+        <v>-800.37</v>
       </c>
       <c r="K37" t="n">
-        <v>-118.93</v>
+        <v>266.25</v>
       </c>
       <c r="L37" t="n">
-        <v>443.63</v>
+        <v>843.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:58:20</t>
+          <t>06:49:37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="F38" t="n">
-        <v>15.32</v>
+        <v>14.63</v>
       </c>
       <c r="G38" t="n">
-        <v>329.5</v>
+        <v>332.8</v>
       </c>
       <c r="H38" t="n">
-        <v>78.7</v>
+        <v>78.3</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-68.01000000000001</v>
+        <v>-30.74</v>
       </c>
       <c r="K38" t="n">
-        <v>506.1</v>
+        <v>500.23</v>
       </c>
       <c r="L38" t="n">
-        <v>510.65</v>
+        <v>501.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:59:50</t>
+          <t>06:51:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.68</v>
+        <v>5.29</v>
       </c>
       <c r="F39" t="n">
-        <v>15.39</v>
+        <v>15.14</v>
       </c>
       <c r="G39" t="n">
-        <v>314.4</v>
+        <v>333.2</v>
       </c>
       <c r="H39" t="n">
-        <v>79.5</v>
+        <v>76.3</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>174.9</v>
+        <v>-52.88</v>
       </c>
       <c r="K39" t="n">
-        <v>-643.6900000000001</v>
+        <v>-274.09</v>
       </c>
       <c r="L39" t="n">
-        <v>667.03</v>
+        <v>279.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:02:14</t>
+          <t>06:53:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="F40" t="n">
-        <v>14.82</v>
+        <v>15.33</v>
       </c>
       <c r="G40" t="n">
-        <v>327.7</v>
+        <v>310.5</v>
       </c>
       <c r="H40" t="n">
-        <v>86.7</v>
+        <v>82.8</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>0.37</v>
+        <v>-519.37</v>
       </c>
       <c r="K40" t="n">
-        <v>395.48</v>
+        <v>-134.2</v>
       </c>
       <c r="L40" t="n">
-        <v>395.48</v>
+        <v>536.4299999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:05:58</t>
+          <t>06:57:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.56</v>
+        <v>5.31</v>
       </c>
       <c r="F41" t="n">
-        <v>14.99</v>
+        <v>15.41</v>
       </c>
       <c r="G41" t="n">
-        <v>329.1</v>
+        <v>313.1</v>
       </c>
       <c r="H41" t="n">
-        <v>76.3</v>
+        <v>72.5</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>259.06</v>
+        <v>507.67</v>
       </c>
       <c r="K41" t="n">
-        <v>183.36</v>
+        <v>-424.84</v>
       </c>
       <c r="L41" t="n">
-        <v>317.39</v>
+        <v>661.98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:07:11</t>
+          <t>06:59:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="F42" t="n">
-        <v>15.32</v>
+        <v>15.86</v>
       </c>
       <c r="G42" t="n">
-        <v>313.7</v>
+        <v>324.5</v>
       </c>
       <c r="H42" t="n">
-        <v>73.2</v>
+        <v>78.7</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-230.45</v>
+        <v>-295.63</v>
       </c>
       <c r="K42" t="n">
-        <v>63.31</v>
+        <v>219.84</v>
       </c>
       <c r="L42" t="n">
-        <v>238.99</v>
+        <v>368.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:08:31</t>
+          <t>07:00:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.74</v>
+        <v>5.55</v>
       </c>
       <c r="F43" t="n">
-        <v>15.05</v>
+        <v>15.38</v>
       </c>
       <c r="G43" t="n">
-        <v>322.6</v>
+        <v>323.4</v>
       </c>
       <c r="H43" t="n">
-        <v>77.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-583.92</v>
+        <v>585.95</v>
       </c>
       <c r="K43" t="n">
-        <v>215.78</v>
+        <v>-57.47</v>
       </c>
       <c r="L43" t="n">
-        <v>622.51</v>
+        <v>588.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:19:33</t>
+          <t>07:11:09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.31</v>
+        <v>5.62</v>
       </c>
       <c r="F44" t="n">
-        <v>14.88</v>
+        <v>15.6</v>
       </c>
       <c r="G44" t="n">
-        <v>335.4</v>
+        <v>334.7</v>
       </c>
       <c r="H44" t="n">
-        <v>81.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-94.2</v>
+        <v>60.52</v>
       </c>
       <c r="K44" t="n">
-        <v>59.89</v>
+        <v>-173.68</v>
       </c>
       <c r="L44" t="n">
-        <v>111.63</v>
+        <v>183.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:20:23</t>
+          <t>07:12:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>6.71</v>
+        <v>5.82</v>
       </c>
       <c r="F45" t="n">
-        <v>15.09</v>
+        <v>15.63</v>
       </c>
       <c r="G45" t="n">
-        <v>311.4</v>
+        <v>329</v>
       </c>
       <c r="H45" t="n">
-        <v>77.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>88.56</v>
+        <v>62.04</v>
       </c>
       <c r="K45" t="n">
-        <v>254.89</v>
+        <v>192.38</v>
       </c>
       <c r="L45" t="n">
-        <v>269.83</v>
+        <v>202.14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:22:23</t>
+          <t>07:14:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.65</v>
+        <v>6.53</v>
       </c>
       <c r="F46" t="n">
-        <v>15.58</v>
+        <v>15.37</v>
       </c>
       <c r="G46" t="n">
-        <v>333.6</v>
+        <v>336.9</v>
       </c>
       <c r="H46" t="n">
-        <v>76.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>109.84</v>
+        <v>-176.05</v>
       </c>
       <c r="K46" t="n">
-        <v>134.49</v>
+        <v>190.64</v>
       </c>
       <c r="L46" t="n">
-        <v>173.64</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:26:36</t>
+          <t>07:20:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.82</v>
+        <v>5.52</v>
       </c>
       <c r="F47" t="n">
-        <v>15.88</v>
+        <v>14.96</v>
       </c>
       <c r="G47" t="n">
-        <v>322.6</v>
+        <v>316.5</v>
       </c>
       <c r="H47" t="n">
-        <v>75.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-262.27</v>
+        <v>320.86</v>
       </c>
       <c r="K47" t="n">
-        <v>-272.84</v>
+        <v>-212.44</v>
       </c>
       <c r="L47" t="n">
-        <v>378.45</v>
+        <v>384.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:28:01</t>
+          <t>07:21:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.71</v>
+        <v>6.07</v>
       </c>
       <c r="F48" t="n">
-        <v>14.92</v>
+        <v>15.04</v>
       </c>
       <c r="G48" t="n">
-        <v>321.9</v>
+        <v>328.3</v>
       </c>
       <c r="H48" t="n">
-        <v>83.5</v>
+        <v>79.5</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-128</v>
+        <v>-70.48</v>
       </c>
       <c r="K48" t="n">
-        <v>17.62</v>
+        <v>250.67</v>
       </c>
       <c r="L48" t="n">
-        <v>129.21</v>
+        <v>260.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:29:40</t>
+          <t>07:23:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.22</v>
+        <v>5.65</v>
       </c>
       <c r="F49" t="n">
-        <v>14.88</v>
+        <v>14.84</v>
       </c>
       <c r="G49" t="n">
-        <v>334.9</v>
+        <v>323.7</v>
       </c>
       <c r="H49" t="n">
-        <v>66.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-288.08</v>
+        <v>167.61</v>
       </c>
       <c r="K49" t="n">
-        <v>129.31</v>
+        <v>-60.16</v>
       </c>
       <c r="L49" t="n">
-        <v>315.77</v>
+        <v>178.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:34:14</t>
+          <t>07:27:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>6.06</v>
+        <v>5.6</v>
       </c>
       <c r="F50" t="n">
-        <v>14.95</v>
+        <v>15.65</v>
       </c>
       <c r="G50" t="n">
-        <v>329.3</v>
+        <v>335.8</v>
       </c>
       <c r="H50" t="n">
-        <v>78.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-18.05</v>
+        <v>570.24</v>
       </c>
       <c r="K50" t="n">
-        <v>-163.73</v>
+        <v>-69.69</v>
       </c>
       <c r="L50" t="n">
-        <v>164.72</v>
+        <v>574.48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:36:08</t>
+          <t>07:29:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.02</v>
+        <v>5.26</v>
       </c>
       <c r="F51" t="n">
-        <v>15.22</v>
+        <v>14.85</v>
       </c>
       <c r="G51" t="n">
-        <v>346.7</v>
+        <v>322.7</v>
       </c>
       <c r="H51" t="n">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>97.45999999999999</v>
+        <v>-345.44</v>
       </c>
       <c r="K51" t="n">
-        <v>75.16</v>
+        <v>-233.4</v>
       </c>
       <c r="L51" t="n">
-        <v>123.07</v>
+        <v>416.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:37:54</t>
+          <t>07:30:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.49</v>
+        <v>6.25</v>
       </c>
       <c r="F52" t="n">
-        <v>14.61</v>
+        <v>14.9</v>
       </c>
       <c r="G52" t="n">
-        <v>321.2</v>
+        <v>330.3</v>
       </c>
       <c r="H52" t="n">
-        <v>76.5</v>
+        <v>83.7</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-261.46</v>
+        <v>244.54</v>
       </c>
       <c r="K52" t="n">
-        <v>214.06</v>
+        <v>-40.54</v>
       </c>
       <c r="L52" t="n">
-        <v>337.91</v>
+        <v>247.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:40:44</t>
+          <t>07:33:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.53</v>
+        <v>5.98</v>
       </c>
       <c r="F53" t="n">
-        <v>15.9</v>
+        <v>15.28</v>
       </c>
       <c r="G53" t="n">
-        <v>332</v>
+        <v>315.8</v>
       </c>
       <c r="H53" t="n">
-        <v>78.8</v>
+        <v>85.3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>385.16</v>
+        <v>-473.82</v>
       </c>
       <c r="K53" t="n">
-        <v>47.09</v>
+        <v>399.68</v>
       </c>
       <c r="L53" t="n">
-        <v>388.03</v>
+        <v>619.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:43:38</t>
+          <t>07:35:58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.4</v>
+        <v>6.53</v>
       </c>
       <c r="F54" t="n">
-        <v>15.07</v>
+        <v>15.29</v>
       </c>
       <c r="G54" t="n">
-        <v>320.2</v>
+        <v>309.6</v>
       </c>
       <c r="H54" t="n">
-        <v>72.2</v>
+        <v>77.8</v>
       </c>
       <c r="I54" t="n">
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-255.08</v>
+        <v>-239.16</v>
       </c>
       <c r="K54" t="n">
-        <v>-643.46</v>
+        <v>209.53</v>
       </c>
       <c r="L54" t="n">
-        <v>692.17</v>
+        <v>317.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:45:24</t>
+          <t>07:38:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.7</v>
+        <v>5.57</v>
       </c>
       <c r="F55" t="n">
-        <v>15.42</v>
+        <v>14.9</v>
       </c>
       <c r="G55" t="n">
-        <v>339.1</v>
+        <v>314.6</v>
       </c>
       <c r="H55" t="n">
-        <v>76.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-73.34999999999999</v>
+        <v>678.39</v>
       </c>
       <c r="K55" t="n">
-        <v>47</v>
+        <v>407.06</v>
       </c>
       <c r="L55" t="n">
-        <v>87.12</v>
+        <v>791.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:49:53</t>
+          <t>07:43:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.79</v>
+        <v>4.86</v>
       </c>
       <c r="F56" t="n">
-        <v>15.45</v>
+        <v>15.51</v>
       </c>
       <c r="G56" t="n">
-        <v>330.4</v>
+        <v>318.8</v>
       </c>
       <c r="H56" t="n">
-        <v>70.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>54.08</v>
+        <v>57.23</v>
       </c>
       <c r="K56" t="n">
-        <v>-97.86</v>
+        <v>-236.18</v>
       </c>
       <c r="L56" t="n">
-        <v>111.8</v>
+        <v>243.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:51:30</t>
+          <t>07:44:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.44</v>
+        <v>5.53</v>
       </c>
       <c r="F57" t="n">
-        <v>15.2</v>
+        <v>14.49</v>
       </c>
       <c r="G57" t="n">
-        <v>336.7</v>
+        <v>329.3</v>
       </c>
       <c r="H57" t="n">
-        <v>74</v>
+        <v>76.2</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>229.93</v>
+        <v>-75.90000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>-564.45</v>
+        <v>837.55</v>
       </c>
       <c r="L57" t="n">
-        <v>609.48</v>
+        <v>840.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:52:46</t>
+          <t>07:46:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.65</v>
+        <v>6.87</v>
       </c>
       <c r="F58" t="n">
-        <v>14.39</v>
+        <v>15.27</v>
       </c>
       <c r="G58" t="n">
-        <v>342.4</v>
+        <v>333.4</v>
       </c>
       <c r="H58" t="n">
-        <v>79.8</v>
+        <v>75.8</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-214.19</v>
+        <v>-878.16</v>
       </c>
       <c r="K58" t="n">
-        <v>86.48</v>
+        <v>-348.72</v>
       </c>
       <c r="L58" t="n">
-        <v>230.99</v>
+        <v>944.87</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:04:49</t>
+          <t>07:55:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.34</v>
+        <v>6.02</v>
       </c>
       <c r="F59" t="n">
-        <v>14.79</v>
+        <v>15.07</v>
       </c>
       <c r="G59" t="n">
-        <v>335.3</v>
+        <v>324.5</v>
       </c>
       <c r="H59" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I59" t="n">
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>271.2</v>
+        <v>365.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-232.28</v>
+        <v>195.41</v>
       </c>
       <c r="L59" t="n">
-        <v>357.07</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:06:58</t>
+          <t>07:56:59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.68</v>
+        <v>5.12</v>
       </c>
       <c r="F60" t="n">
-        <v>14.63</v>
+        <v>14.45</v>
       </c>
       <c r="G60" t="n">
-        <v>304.4</v>
+        <v>326.9</v>
       </c>
       <c r="H60" t="n">
-        <v>77.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-146.55</v>
+        <v>77.28</v>
       </c>
       <c r="K60" t="n">
-        <v>34.28</v>
+        <v>177.34</v>
       </c>
       <c r="L60" t="n">
-        <v>150.5</v>
+        <v>193.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:09:04</t>
+          <t>07:59:26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.27</v>
+        <v>5.05</v>
       </c>
       <c r="F61" t="n">
-        <v>15.87</v>
+        <v>15.56</v>
       </c>
       <c r="G61" t="n">
-        <v>317.5</v>
+        <v>328.2</v>
       </c>
       <c r="H61" t="n">
-        <v>87</v>
+        <v>82.2</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>26.31</v>
+        <v>185.88</v>
       </c>
       <c r="K61" t="n">
-        <v>18.28</v>
+        <v>34.84</v>
       </c>
       <c r="L61" t="n">
-        <v>32.04</v>
+        <v>189.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:14:58</t>
+          <t>08:03:23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.4</v>
+        <v>6.16</v>
       </c>
       <c r="F62" t="n">
-        <v>15.03</v>
+        <v>15.39</v>
       </c>
       <c r="G62" t="n">
-        <v>319.4</v>
+        <v>314.8</v>
       </c>
       <c r="H62" t="n">
-        <v>75.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-340.77</v>
+        <v>84.55</v>
       </c>
       <c r="K62" t="n">
-        <v>-245.03</v>
+        <v>-240.5</v>
       </c>
       <c r="L62" t="n">
-        <v>419.72</v>
+        <v>254.93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:16:16</t>
+          <t>08:05:24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.39</v>
+        <v>5.69</v>
       </c>
       <c r="F63" t="n">
-        <v>15.59</v>
+        <v>14.5</v>
       </c>
       <c r="G63" t="n">
-        <v>338.2</v>
+        <v>315.6</v>
       </c>
       <c r="H63" t="n">
-        <v>74</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>319.35</v>
+        <v>-238.49</v>
       </c>
       <c r="K63" t="n">
-        <v>267.09</v>
+        <v>345.96</v>
       </c>
       <c r="L63" t="n">
-        <v>416.32</v>
+        <v>420.19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:18:09</t>
+          <t>08:06:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="F64" t="n">
-        <v>14.65</v>
+        <v>14.45</v>
       </c>
       <c r="G64" t="n">
-        <v>318.6</v>
+        <v>335</v>
       </c>
       <c r="H64" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-131.96</v>
+        <v>-415.99</v>
       </c>
       <c r="K64" t="n">
-        <v>-318.46</v>
+        <v>-3.21</v>
       </c>
       <c r="L64" t="n">
-        <v>344.71</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:23:22</t>
+          <t>08:11:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.84</v>
+        <v>5.98</v>
       </c>
       <c r="F65" t="n">
-        <v>15.48</v>
+        <v>15.35</v>
       </c>
       <c r="G65" t="n">
-        <v>337</v>
+        <v>326.9</v>
       </c>
       <c r="H65" t="n">
-        <v>76.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-229.4</v>
+        <v>-384.54</v>
       </c>
       <c r="K65" t="n">
-        <v>-210.23</v>
+        <v>323.59</v>
       </c>
       <c r="L65" t="n">
-        <v>311.16</v>
+        <v>502.57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:24:16</t>
+          <t>08:13:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.32</v>
+        <v>5.38</v>
       </c>
       <c r="F66" t="n">
-        <v>15.19</v>
+        <v>14.29</v>
       </c>
       <c r="G66" t="n">
-        <v>321.5</v>
+        <v>331.5</v>
       </c>
       <c r="H66" t="n">
-        <v>77.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>254.41</v>
+        <v>252.5</v>
       </c>
       <c r="K66" t="n">
-        <v>-43.79</v>
+        <v>209.11</v>
       </c>
       <c r="L66" t="n">
-        <v>258.15</v>
+        <v>327.85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:25:52</t>
+          <t>08:14:20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.8</v>
+        <v>5.76</v>
       </c>
       <c r="F67" t="n">
-        <v>14.99</v>
+        <v>15.07</v>
       </c>
       <c r="G67" t="n">
-        <v>314.6</v>
+        <v>324</v>
       </c>
       <c r="H67" t="n">
-        <v>80.5</v>
+        <v>71</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>163.08</v>
+        <v>266.12</v>
       </c>
       <c r="K67" t="n">
-        <v>570.49</v>
+        <v>-277.37</v>
       </c>
       <c r="L67" t="n">
-        <v>593.34</v>
+        <v>384.39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:31:26</t>
+          <t>08:18:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.64</v>
+        <v>5.18</v>
       </c>
       <c r="F68" t="n">
-        <v>14.52</v>
+        <v>15.04</v>
       </c>
       <c r="G68" t="n">
-        <v>336.4</v>
+        <v>323.9</v>
       </c>
       <c r="H68" t="n">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>219.61</v>
+        <v>-469.7</v>
       </c>
       <c r="K68" t="n">
-        <v>34.06</v>
+        <v>-143.16</v>
       </c>
       <c r="L68" t="n">
-        <v>222.24</v>
+        <v>491.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:33:34</t>
+          <t>08:20:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.3</v>
+        <v>5.74</v>
       </c>
       <c r="F69" t="n">
-        <v>14.94</v>
+        <v>15.28</v>
       </c>
       <c r="G69" t="n">
-        <v>325.6</v>
+        <v>333.6</v>
       </c>
       <c r="H69" t="n">
-        <v>81.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-419.66</v>
+        <v>-1292.66</v>
       </c>
       <c r="K69" t="n">
-        <v>344.33</v>
+        <v>-440.35</v>
       </c>
       <c r="L69" t="n">
-        <v>542.84</v>
+        <v>1365.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:34:57</t>
+          <t>08:22:16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="F70" t="n">
-        <v>15.07</v>
+        <v>15.35</v>
       </c>
       <c r="G70" t="n">
-        <v>325.7</v>
+        <v>330.1</v>
       </c>
       <c r="H70" t="n">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>35.57</v>
+        <v>367.34</v>
       </c>
       <c r="K70" t="n">
-        <v>-166.72</v>
+        <v>683.9</v>
       </c>
       <c r="L70" t="n">
-        <v>170.47</v>
+        <v>776.3099999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:41:16</t>
+          <t>08:25:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.39</v>
+        <v>6.27</v>
       </c>
       <c r="F71" t="n">
-        <v>15.98</v>
+        <v>15.04</v>
       </c>
       <c r="G71" t="n">
-        <v>331.5</v>
+        <v>314.1</v>
       </c>
       <c r="H71" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-155.26</v>
+        <v>762.6</v>
       </c>
       <c r="K71" t="n">
-        <v>-230.3</v>
+        <v>-188.66</v>
       </c>
       <c r="L71" t="n">
-        <v>277.75</v>
+        <v>785.59</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:42:33</t>
+          <t>08:26:32</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.13</v>
+        <v>6.5</v>
       </c>
       <c r="F72" t="n">
-        <v>14.54</v>
+        <v>15.39</v>
       </c>
       <c r="G72" t="n">
-        <v>320.2</v>
+        <v>318.4</v>
       </c>
       <c r="H72" t="n">
-        <v>67.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-170.06</v>
+        <v>-820.09</v>
       </c>
       <c r="K72" t="n">
-        <v>68.16</v>
+        <v>20.43</v>
       </c>
       <c r="L72" t="n">
-        <v>183.21</v>
+        <v>820.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:44:23</t>
+          <t>08:27:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.3</v>
+        <v>6.68</v>
       </c>
       <c r="F73" t="n">
-        <v>15.31</v>
+        <v>15.73</v>
       </c>
       <c r="G73" t="n">
-        <v>334.7</v>
+        <v>311.4</v>
       </c>
       <c r="H73" t="n">
-        <v>70.8</v>
+        <v>77.8</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-392.9</v>
+        <v>521.27</v>
       </c>
       <c r="K73" t="n">
-        <v>-502.65</v>
+        <v>94.42</v>
       </c>
       <c r="L73" t="n">
-        <v>637.98</v>
+        <v>529.76</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:55:31</t>
+          <t>08:36:11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.38</v>
+        <v>6.88</v>
       </c>
       <c r="F74" t="n">
-        <v>14.97</v>
+        <v>14.74</v>
       </c>
       <c r="G74" t="n">
-        <v>328.4</v>
+        <v>336.3</v>
       </c>
       <c r="H74" t="n">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>15.08</v>
+        <v>-409.78</v>
       </c>
       <c r="K74" t="n">
-        <v>260.64</v>
+        <v>43.48</v>
       </c>
       <c r="L74" t="n">
-        <v>261.08</v>
+        <v>412.08</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:56:46</t>
+          <t>08:37:55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.44</v>
+        <v>5.95</v>
       </c>
       <c r="F75" t="n">
-        <v>14.77</v>
+        <v>15.61</v>
       </c>
       <c r="G75" t="n">
-        <v>318.4</v>
+        <v>325.1</v>
       </c>
       <c r="H75" t="n">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>250.72</v>
+        <v>176.19</v>
       </c>
       <c r="K75" t="n">
-        <v>98.34999999999999</v>
+        <v>52.87</v>
       </c>
       <c r="L75" t="n">
-        <v>269.32</v>
+        <v>183.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:58:10</t>
+          <t>08:38:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.58</v>
+        <v>7.04</v>
       </c>
       <c r="F76" t="n">
-        <v>15.04</v>
+        <v>15.28</v>
       </c>
       <c r="G76" t="n">
-        <v>334.9</v>
+        <v>319.1</v>
       </c>
       <c r="H76" t="n">
-        <v>78.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-264.23</v>
+        <v>-195.64</v>
       </c>
       <c r="K76" t="n">
-        <v>-308.16</v>
+        <v>-304.59</v>
       </c>
       <c r="L76" t="n">
-        <v>405.93</v>
+        <v>362.01</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:02:50</t>
+          <t>08:43:09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.08</v>
+        <v>6.15</v>
       </c>
       <c r="F77" t="n">
-        <v>14.67</v>
+        <v>14.99</v>
       </c>
       <c r="G77" t="n">
-        <v>310.7</v>
+        <v>327.8</v>
       </c>
       <c r="H77" t="n">
-        <v>79.7</v>
+        <v>81</v>
       </c>
       <c r="I77" t="n">
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-159.59</v>
+        <v>-316.01</v>
       </c>
       <c r="K77" t="n">
-        <v>168.48</v>
+        <v>-152.3</v>
       </c>
       <c r="L77" t="n">
-        <v>232.07</v>
+        <v>350.79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:05:35</t>
+          <t>08:45:37</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="F78" t="n">
-        <v>14.37</v>
+        <v>14.64</v>
       </c>
       <c r="G78" t="n">
-        <v>343.3</v>
+        <v>313.8</v>
       </c>
       <c r="H78" t="n">
-        <v>69.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>195.66</v>
+        <v>-203.41</v>
       </c>
       <c r="K78" t="n">
-        <v>-222.88</v>
+        <v>-143.06</v>
       </c>
       <c r="L78" t="n">
-        <v>296.58</v>
+        <v>248.68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:06:31</t>
+          <t>08:47:13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.83</v>
+        <v>6.17</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="G79" t="n">
-        <v>321.3</v>
+        <v>324.8</v>
       </c>
       <c r="H79" t="n">
-        <v>79</v>
+        <v>71.2</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-470.89</v>
+        <v>-149.59</v>
       </c>
       <c r="K79" t="n">
-        <v>132.18</v>
+        <v>10.61</v>
       </c>
       <c r="L79" t="n">
-        <v>489.09</v>
+        <v>149.97</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:10:47</t>
+          <t>08:51:23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.35</v>
+        <v>6.74</v>
       </c>
       <c r="F80" t="n">
-        <v>14.56</v>
+        <v>15.69</v>
       </c>
       <c r="G80" t="n">
-        <v>323.1</v>
+        <v>322.3</v>
       </c>
       <c r="H80" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-222.37</v>
+        <v>406.95</v>
       </c>
       <c r="K80" t="n">
-        <v>-126.07</v>
+        <v>-16.4</v>
       </c>
       <c r="L80" t="n">
-        <v>255.62</v>
+        <v>407.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:12:44</t>
+          <t>08:52:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3442,31 +3442,31 @@
         <v>6.73</v>
       </c>
       <c r="F81" t="n">
-        <v>14.9</v>
+        <v>15.53</v>
       </c>
       <c r="G81" t="n">
-        <v>328.1</v>
+        <v>312.1</v>
       </c>
       <c r="H81" t="n">
-        <v>77.8</v>
+        <v>70.5</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-326.09</v>
+        <v>762.46</v>
       </c>
       <c r="K81" t="n">
-        <v>-5.93</v>
+        <v>-456.07</v>
       </c>
       <c r="L81" t="n">
-        <v>326.15</v>
+        <v>888.45</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:14:43</t>
+          <t>08:55:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.88</v>
+        <v>6.4</v>
       </c>
       <c r="F82" t="n">
-        <v>15.28</v>
+        <v>15.25</v>
       </c>
       <c r="G82" t="n">
-        <v>334.2</v>
+        <v>320.8</v>
       </c>
       <c r="H82" t="n">
-        <v>75.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-78.14</v>
+        <v>-20.57</v>
       </c>
       <c r="K82" t="n">
-        <v>146.84</v>
+        <v>297.73</v>
       </c>
       <c r="L82" t="n">
-        <v>166.34</v>
+        <v>298.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:18:03</t>
+          <t>08:59:22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.36</v>
+        <v>6.72</v>
       </c>
       <c r="F83" t="n">
-        <v>15.11</v>
+        <v>15.32</v>
       </c>
       <c r="G83" t="n">
-        <v>319</v>
+        <v>320.2</v>
       </c>
       <c r="H83" t="n">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-40.62</v>
+        <v>-20.58</v>
       </c>
       <c r="K83" t="n">
-        <v>246.95</v>
+        <v>-458.83</v>
       </c>
       <c r="L83" t="n">
-        <v>250.27</v>
+        <v>459.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:20:36</t>
+          <t>09:01:37</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.47</v>
+        <v>6.17</v>
       </c>
       <c r="F84" t="n">
-        <v>15.03</v>
+        <v>14.78</v>
       </c>
       <c r="G84" t="n">
         <v>319.4</v>
       </c>
       <c r="H84" t="n">
-        <v>76.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-353.34</v>
+        <v>-962.61</v>
       </c>
       <c r="K84" t="n">
-        <v>492.26</v>
+        <v>-609.85</v>
       </c>
       <c r="L84" t="n">
-        <v>605.9400000000001</v>
+        <v>1139.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:22:48</t>
+          <t>09:03:33</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.25</v>
+        <v>6.58</v>
       </c>
       <c r="F85" t="n">
-        <v>14.62</v>
+        <v>14.87</v>
       </c>
       <c r="G85" t="n">
-        <v>328.5</v>
+        <v>319.7</v>
       </c>
       <c r="H85" t="n">
-        <v>81</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>4.62</v>
+        <v>719.4400000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-409.92</v>
+        <v>172.88</v>
       </c>
       <c r="L85" t="n">
-        <v>409.94</v>
+        <v>739.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:27:21</t>
+          <t>09:07:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.08</v>
+        <v>6.97</v>
       </c>
       <c r="F86" t="n">
-        <v>14.38</v>
+        <v>15.1</v>
       </c>
       <c r="G86" t="n">
-        <v>337.2</v>
+        <v>328.4</v>
       </c>
       <c r="H86" t="n">
-        <v>82.7</v>
+        <v>73.8</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>415.35</v>
+        <v>-390.07</v>
       </c>
       <c r="K86" t="n">
-        <v>287.17</v>
+        <v>676.9400000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>504.95</v>
+        <v>781.28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:29:19</t>
+          <t>09:09:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.39</v>
+        <v>6.61</v>
       </c>
       <c r="F87" t="n">
-        <v>15.68</v>
+        <v>15.24</v>
       </c>
       <c r="G87" t="n">
-        <v>332.8</v>
+        <v>309</v>
       </c>
       <c r="H87" t="n">
-        <v>70.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>45.45</v>
+        <v>280.5</v>
       </c>
       <c r="K87" t="n">
-        <v>456.6</v>
+        <v>157.99</v>
       </c>
       <c r="L87" t="n">
-        <v>458.85</v>
+        <v>321.93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:31:06</t>
+          <t>09:10:58</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.45</v>
+        <v>6.69</v>
       </c>
       <c r="F88" t="n">
-        <v>14.9</v>
+        <v>15.06</v>
       </c>
       <c r="G88" t="n">
-        <v>319.1</v>
+        <v>316.9</v>
       </c>
       <c r="H88" t="n">
-        <v>76.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>635.0599999999999</v>
+        <v>-382.39</v>
       </c>
       <c r="K88" t="n">
-        <v>-518.97</v>
+        <v>519.4299999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>820.14</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>95.03</v>
+        <v>138.92</v>
       </c>
       <c r="K14" t="n">
-        <v>-95.62</v>
+        <v>-139.78</v>
       </c>
       <c r="L14" t="n">
-        <v>134.8</v>
+        <v>197.07</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-21.41</v>
+        <v>-26.71</v>
       </c>
       <c r="K15" t="n">
-        <v>-170.32</v>
+        <v>-212.51</v>
       </c>
       <c r="L15" t="n">
-        <v>171.66</v>
+        <v>214.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>19.57</v>
+        <v>32.88</v>
       </c>
       <c r="K16" t="n">
-        <v>121.19</v>
+        <v>203.64</v>
       </c>
       <c r="L16" t="n">
-        <v>122.76</v>
+        <v>206.28</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>213.05</v>
+        <v>249.93</v>
       </c>
       <c r="K17" t="n">
-        <v>193.69</v>
+        <v>227.22</v>
       </c>
       <c r="L17" t="n">
-        <v>287.94</v>
+        <v>337.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-238.05</v>
+        <v>-253.95</v>
       </c>
       <c r="K18" t="n">
-        <v>136.81</v>
+        <v>145.95</v>
       </c>
       <c r="L18" t="n">
-        <v>274.56</v>
+        <v>292.9</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>134.54</v>
+        <v>182.6</v>
       </c>
       <c r="K19" t="n">
-        <v>37.34</v>
+        <v>50.68</v>
       </c>
       <c r="L19" t="n">
-        <v>139.63</v>
+        <v>189.51</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-525.15</v>
+        <v>-607.14</v>
       </c>
       <c r="K20" t="n">
-        <v>390.08</v>
+        <v>450.98</v>
       </c>
       <c r="L20" t="n">
-        <v>654.17</v>
+        <v>756.3099999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>265.59</v>
+        <v>311.02</v>
       </c>
       <c r="K21" t="n">
-        <v>-307.82</v>
+        <v>-360.47</v>
       </c>
       <c r="L21" t="n">
-        <v>406.56</v>
+        <v>476.1</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-122.48</v>
+        <v>-224.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-121.6</v>
+        <v>-222.78</v>
       </c>
       <c r="L22" t="n">
-        <v>172.59</v>
+        <v>316.2</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>18.53</v>
+        <v>36.69</v>
       </c>
       <c r="K23" t="n">
-        <v>-266.27</v>
+        <v>-527.11</v>
       </c>
       <c r="L23" t="n">
-        <v>266.91</v>
+        <v>528.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-194.52</v>
+        <v>-240.94</v>
       </c>
       <c r="K24" t="n">
-        <v>415.59</v>
+        <v>514.76</v>
       </c>
       <c r="L24" t="n">
-        <v>458.86</v>
+        <v>568.36</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>333.76</v>
+        <v>536.75</v>
       </c>
       <c r="K25" t="n">
-        <v>231.3</v>
+        <v>371.98</v>
       </c>
       <c r="L25" t="n">
-        <v>406.08</v>
+        <v>653.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>434.6</v>
+        <v>793.85</v>
       </c>
       <c r="K26" t="n">
-        <v>-95.92</v>
+        <v>-175.22</v>
       </c>
       <c r="L26" t="n">
-        <v>445.06</v>
+        <v>812.95</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-143.54</v>
+        <v>-277.66</v>
       </c>
       <c r="K27" t="n">
-        <v>-195.28</v>
+        <v>-377.75</v>
       </c>
       <c r="L27" t="n">
-        <v>242.36</v>
+        <v>468.82</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>179.94</v>
+        <v>327.02</v>
       </c>
       <c r="K28" t="n">
-        <v>416.69</v>
+        <v>757.27</v>
       </c>
       <c r="L28" t="n">
-        <v>453.88</v>
+        <v>824.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>112.66</v>
+        <v>140.37</v>
       </c>
       <c r="K29" t="n">
-        <v>-164.83</v>
+        <v>-205.37</v>
       </c>
       <c r="L29" t="n">
-        <v>199.65</v>
+        <v>248.76</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.78</v>
+        <v>-37.6</v>
       </c>
       <c r="K30" t="n">
-        <v>46.9</v>
+        <v>119.32</v>
       </c>
       <c r="L30" t="n">
-        <v>49.18</v>
+        <v>125.1</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.02</v>
+        <v>-124.22</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.85</v>
+        <v>-38.49</v>
       </c>
       <c r="L31" t="n">
-        <v>36.66</v>
+        <v>130.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-129.56</v>
+        <v>-144.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-262.8</v>
+        <v>-294.02</v>
       </c>
       <c r="L32" t="n">
-        <v>293.01</v>
+        <v>327.81</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.02</v>
+        <v>-54.29</v>
       </c>
       <c r="K33" t="n">
-        <v>152.16</v>
+        <v>206.43</v>
       </c>
       <c r="L33" t="n">
-        <v>157.34</v>
+        <v>213.45</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.4</v>
+        <v>-4.71</v>
       </c>
       <c r="K34" t="n">
-        <v>-134.02</v>
+        <v>-262.89</v>
       </c>
       <c r="L34" t="n">
-        <v>134.04</v>
+        <v>262.93</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>132.34</v>
+        <v>164.62</v>
       </c>
       <c r="K35" t="n">
-        <v>-245.15</v>
+        <v>-304.95</v>
       </c>
       <c r="L35" t="n">
-        <v>278.59</v>
+        <v>346.54</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-418.64</v>
+        <v>-551.01</v>
       </c>
       <c r="K36" t="n">
-        <v>114.12</v>
+        <v>150.2</v>
       </c>
       <c r="L36" t="n">
-        <v>433.91</v>
+        <v>571.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-800.37</v>
+        <v>-913.9400000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>266.25</v>
+        <v>304.03</v>
       </c>
       <c r="L37" t="n">
-        <v>843.5</v>
+        <v>963.1799999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-30.74</v>
+        <v>-44.92</v>
       </c>
       <c r="K38" t="n">
-        <v>500.23</v>
+        <v>730.96</v>
       </c>
       <c r="L38" t="n">
-        <v>501.18</v>
+        <v>732.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-52.88</v>
+        <v>-93.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-274.09</v>
+        <v>-486.08</v>
       </c>
       <c r="L39" t="n">
-        <v>279.15</v>
+        <v>495.04</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-519.37</v>
+        <v>-712.76</v>
       </c>
       <c r="K40" t="n">
-        <v>-134.2</v>
+        <v>-184.17</v>
       </c>
       <c r="L40" t="n">
-        <v>536.4299999999999</v>
+        <v>736.17</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>507.67</v>
+        <v>712.2</v>
       </c>
       <c r="K41" t="n">
-        <v>-424.84</v>
+        <v>-595.99</v>
       </c>
       <c r="L41" t="n">
-        <v>661.98</v>
+        <v>928.6799999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-295.63</v>
+        <v>-611.02</v>
       </c>
       <c r="K42" t="n">
-        <v>219.84</v>
+        <v>454.39</v>
       </c>
       <c r="L42" t="n">
-        <v>368.41</v>
+        <v>761.45</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>585.95</v>
+        <v>940.83</v>
       </c>
       <c r="K43" t="n">
-        <v>-57.47</v>
+        <v>-92.27</v>
       </c>
       <c r="L43" t="n">
-        <v>588.76</v>
+        <v>945.35</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>60.52</v>
+        <v>72.77</v>
       </c>
       <c r="K44" t="n">
-        <v>-173.68</v>
+        <v>-208.85</v>
       </c>
       <c r="L44" t="n">
-        <v>183.93</v>
+        <v>221.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>62.04</v>
+        <v>82.42</v>
       </c>
       <c r="K45" t="n">
-        <v>192.38</v>
+        <v>255.58</v>
       </c>
       <c r="L45" t="n">
-        <v>202.14</v>
+        <v>268.54</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-176.05</v>
+        <v>-250.03</v>
       </c>
       <c r="K46" t="n">
-        <v>190.64</v>
+        <v>270.75</v>
       </c>
       <c r="L46" t="n">
-        <v>259.5</v>
+        <v>368.54</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>320.86</v>
+        <v>366.24</v>
       </c>
       <c r="K47" t="n">
-        <v>-212.44</v>
+        <v>-242.48</v>
       </c>
       <c r="L47" t="n">
-        <v>384.81</v>
+        <v>439.23</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.48</v>
+        <v>-96.38</v>
       </c>
       <c r="K48" t="n">
-        <v>250.67</v>
+        <v>342.75</v>
       </c>
       <c r="L48" t="n">
-        <v>260.39</v>
+        <v>356.05</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>167.61</v>
+        <v>249.11</v>
       </c>
       <c r="K49" t="n">
-        <v>-60.16</v>
+        <v>-89.41</v>
       </c>
       <c r="L49" t="n">
-        <v>178.08</v>
+        <v>264.67</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>570.24</v>
+        <v>703.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-69.69</v>
+        <v>-85.92</v>
       </c>
       <c r="L50" t="n">
-        <v>574.48</v>
+        <v>708.28</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-345.44</v>
+        <v>-467.66</v>
       </c>
       <c r="K51" t="n">
-        <v>-233.4</v>
+        <v>-315.98</v>
       </c>
       <c r="L51" t="n">
-        <v>416.9</v>
+        <v>564.4</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>244.54</v>
+        <v>421.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-40.54</v>
+        <v>-69.8</v>
       </c>
       <c r="L52" t="n">
-        <v>247.88</v>
+        <v>426.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-473.82</v>
+        <v>-631.96</v>
       </c>
       <c r="K53" t="n">
-        <v>399.68</v>
+        <v>533.0700000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>619.88</v>
+        <v>826.76</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-239.16</v>
+        <v>-491.24</v>
       </c>
       <c r="K54" t="n">
-        <v>209.53</v>
+        <v>430.38</v>
       </c>
       <c r="L54" t="n">
-        <v>317.96</v>
+        <v>653.11</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>678.39</v>
+        <v>868.25</v>
       </c>
       <c r="K55" t="n">
-        <v>407.06</v>
+        <v>520.98</v>
       </c>
       <c r="L55" t="n">
-        <v>791.15</v>
+        <v>1012.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>57.23</v>
+        <v>107.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-236.18</v>
+        <v>-443.9</v>
       </c>
       <c r="L56" t="n">
-        <v>243.02</v>
+        <v>456.74</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-75.90000000000001</v>
+        <v>-97.47</v>
       </c>
       <c r="K57" t="n">
-        <v>837.55</v>
+        <v>1075.61</v>
       </c>
       <c r="L57" t="n">
-        <v>840.98</v>
+        <v>1080.02</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-878.16</v>
+        <v>-1259.8</v>
       </c>
       <c r="K58" t="n">
-        <v>-348.72</v>
+        <v>-500.26</v>
       </c>
       <c r="L58" t="n">
-        <v>944.87</v>
+        <v>1355.49</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>365.67</v>
+        <v>428.76</v>
       </c>
       <c r="K59" t="n">
-        <v>195.41</v>
+        <v>229.13</v>
       </c>
       <c r="L59" t="n">
-        <v>414.61</v>
+        <v>486.14</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>77.28</v>
+        <v>89.97</v>
       </c>
       <c r="K60" t="n">
-        <v>177.34</v>
+        <v>206.47</v>
       </c>
       <c r="L60" t="n">
-        <v>193.45</v>
+        <v>225.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>185.88</v>
+        <v>256.43</v>
       </c>
       <c r="K61" t="n">
-        <v>34.84</v>
+        <v>48.06</v>
       </c>
       <c r="L61" t="n">
-        <v>189.12</v>
+        <v>260.89</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>84.55</v>
+        <v>122</v>
       </c>
       <c r="K62" t="n">
-        <v>-240.5</v>
+        <v>-347.03</v>
       </c>
       <c r="L62" t="n">
-        <v>254.93</v>
+        <v>367.85</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-238.49</v>
+        <v>-253.43</v>
       </c>
       <c r="K63" t="n">
-        <v>345.96</v>
+        <v>367.62</v>
       </c>
       <c r="L63" t="n">
-        <v>420.19</v>
+        <v>446.51</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-415.99</v>
+        <v>-474.93</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.21</v>
+        <v>-3.67</v>
       </c>
       <c r="L64" t="n">
-        <v>416</v>
+        <v>474.94</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-384.54</v>
+        <v>-429.98</v>
       </c>
       <c r="K65" t="n">
-        <v>323.59</v>
+        <v>361.83</v>
       </c>
       <c r="L65" t="n">
-        <v>502.57</v>
+        <v>561.97</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>252.5</v>
+        <v>332.41</v>
       </c>
       <c r="K66" t="n">
-        <v>209.11</v>
+        <v>275.3</v>
       </c>
       <c r="L66" t="n">
-        <v>327.85</v>
+        <v>431.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>266.12</v>
+        <v>330.39</v>
       </c>
       <c r="K67" t="n">
-        <v>-277.37</v>
+        <v>-344.36</v>
       </c>
       <c r="L67" t="n">
-        <v>384.39</v>
+        <v>477.22</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-469.7</v>
+        <v>-715.83</v>
       </c>
       <c r="K68" t="n">
-        <v>-143.16</v>
+        <v>-218.17</v>
       </c>
       <c r="L68" t="n">
-        <v>491.03</v>
+        <v>748.34</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-1292.66</v>
+        <v>-1401.13</v>
       </c>
       <c r="K69" t="n">
-        <v>-440.35</v>
+        <v>-477.3</v>
       </c>
       <c r="L69" t="n">
-        <v>1365.6</v>
+        <v>1480.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>367.34</v>
+        <v>470.88</v>
       </c>
       <c r="K70" t="n">
-        <v>683.9</v>
+        <v>876.66</v>
       </c>
       <c r="L70" t="n">
-        <v>776.3099999999999</v>
+        <v>995.12</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>762.6</v>
+        <v>1224.11</v>
       </c>
       <c r="K71" t="n">
-        <v>-188.66</v>
+        <v>-302.83</v>
       </c>
       <c r="L71" t="n">
-        <v>785.59</v>
+        <v>1261.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-820.09</v>
+        <v>-1241.58</v>
       </c>
       <c r="K72" t="n">
-        <v>20.43</v>
+        <v>30.92</v>
       </c>
       <c r="L72" t="n">
-        <v>820.34</v>
+        <v>1241.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>521.27</v>
+        <v>845.13</v>
       </c>
       <c r="K73" t="n">
-        <v>94.42</v>
+        <v>153.08</v>
       </c>
       <c r="L73" t="n">
-        <v>529.76</v>
+        <v>858.88</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-409.78</v>
+        <v>-497.28</v>
       </c>
       <c r="K74" t="n">
-        <v>43.48</v>
+        <v>52.76</v>
       </c>
       <c r="L74" t="n">
-        <v>412.08</v>
+        <v>500.07</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>176.19</v>
+        <v>253.89</v>
       </c>
       <c r="K75" t="n">
-        <v>52.87</v>
+        <v>76.19</v>
       </c>
       <c r="L75" t="n">
-        <v>183.95</v>
+        <v>265.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-195.64</v>
+        <v>-249.41</v>
       </c>
       <c r="K76" t="n">
-        <v>-304.59</v>
+        <v>-388.31</v>
       </c>
       <c r="L76" t="n">
-        <v>362.01</v>
+        <v>461.51</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-316.01</v>
+        <v>-413.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-152.3</v>
+        <v>-199.45</v>
       </c>
       <c r="L77" t="n">
-        <v>350.79</v>
+        <v>459.39</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-203.41</v>
+        <v>-263.57</v>
       </c>
       <c r="K78" t="n">
-        <v>-143.06</v>
+        <v>-185.37</v>
       </c>
       <c r="L78" t="n">
-        <v>248.68</v>
+        <v>322.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-149.59</v>
+        <v>-263.58</v>
       </c>
       <c r="K79" t="n">
-        <v>10.61</v>
+        <v>18.7</v>
       </c>
       <c r="L79" t="n">
-        <v>149.97</v>
+        <v>264.25</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>406.95</v>
+        <v>627.22</v>
       </c>
       <c r="K80" t="n">
-        <v>-16.4</v>
+        <v>-25.27</v>
       </c>
       <c r="L80" t="n">
-        <v>407.28</v>
+        <v>627.73</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>762.46</v>
+        <v>937.53</v>
       </c>
       <c r="K81" t="n">
-        <v>-456.07</v>
+        <v>-560.79</v>
       </c>
       <c r="L81" t="n">
-        <v>888.45</v>
+        <v>1092.45</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-20.57</v>
+        <v>-29.39</v>
       </c>
       <c r="K82" t="n">
-        <v>297.73</v>
+        <v>425.44</v>
       </c>
       <c r="L82" t="n">
-        <v>298.44</v>
+        <v>426.45</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-20.58</v>
+        <v>-35.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-458.83</v>
+        <v>-802.15</v>
       </c>
       <c r="L83" t="n">
-        <v>459.29</v>
+        <v>802.96</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-962.61</v>
+        <v>-1037.62</v>
       </c>
       <c r="K84" t="n">
-        <v>-609.85</v>
+        <v>-657.37</v>
       </c>
       <c r="L84" t="n">
-        <v>1139.54</v>
+        <v>1228.33</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>719.4400000000001</v>
+        <v>883</v>
       </c>
       <c r="K85" t="n">
-        <v>172.88</v>
+        <v>212.18</v>
       </c>
       <c r="L85" t="n">
-        <v>739.92</v>
+        <v>908.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-390.07</v>
+        <v>-576.1900000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>676.9400000000001</v>
+        <v>999.9299999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>781.28</v>
+        <v>1154.06</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>280.5</v>
+        <v>642.3099999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>157.99</v>
+        <v>361.77</v>
       </c>
       <c r="L87" t="n">
-        <v>321.93</v>
+        <v>737.1900000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-382.39</v>
+        <v>-567.91</v>
       </c>
       <c r="K88" t="n">
-        <v>519.4299999999999</v>
+        <v>771.4400000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>645</v>
+        <v>957.9400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>138.92</v>
+        <v>101.44</v>
       </c>
       <c r="K14" t="n">
-        <v>-139.78</v>
+        <v>-102.07</v>
       </c>
       <c r="L14" t="n">
-        <v>197.07</v>
+        <v>143.91</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-26.71</v>
+        <v>-20.92</v>
       </c>
       <c r="K15" t="n">
-        <v>-212.51</v>
+        <v>-166.47</v>
       </c>
       <c r="L15" t="n">
-        <v>214.18</v>
+        <v>167.78</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>32.88</v>
+        <v>23.61</v>
       </c>
       <c r="K16" t="n">
-        <v>203.64</v>
+        <v>146.23</v>
       </c>
       <c r="L16" t="n">
-        <v>206.28</v>
+        <v>148.12</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>249.93</v>
+        <v>171.16</v>
       </c>
       <c r="K17" t="n">
-        <v>227.22</v>
+        <v>155.61</v>
       </c>
       <c r="L17" t="n">
-        <v>337.78</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-253.95</v>
+        <v>-200.3</v>
       </c>
       <c r="K18" t="n">
-        <v>145.95</v>
+        <v>115.11</v>
       </c>
       <c r="L18" t="n">
-        <v>292.9</v>
+        <v>231.02</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>182.6</v>
+        <v>135.2</v>
       </c>
       <c r="K19" t="n">
-        <v>50.68</v>
+        <v>37.52</v>
       </c>
       <c r="L19" t="n">
-        <v>189.51</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-607.14</v>
+        <v>-355.66</v>
       </c>
       <c r="K20" t="n">
-        <v>450.98</v>
+        <v>264.18</v>
       </c>
       <c r="L20" t="n">
-        <v>756.3099999999999</v>
+        <v>443.04</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>311.02</v>
+        <v>198.23</v>
       </c>
       <c r="K21" t="n">
-        <v>-360.47</v>
+        <v>-229.74</v>
       </c>
       <c r="L21" t="n">
-        <v>476.1</v>
+        <v>303.44</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-224.39</v>
+        <v>-136.1</v>
       </c>
       <c r="K22" t="n">
-        <v>-222.78</v>
+        <v>-135.12</v>
       </c>
       <c r="L22" t="n">
-        <v>316.2</v>
+        <v>191.79</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>36.69</v>
+        <v>18.09</v>
       </c>
       <c r="K23" t="n">
-        <v>-527.11</v>
+        <v>-259.83</v>
       </c>
       <c r="L23" t="n">
-        <v>528.39</v>
+        <v>260.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-240.94</v>
+        <v>-142.95</v>
       </c>
       <c r="K24" t="n">
-        <v>514.76</v>
+        <v>305.4</v>
       </c>
       <c r="L24" t="n">
-        <v>568.36</v>
+        <v>337.2</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>536.75</v>
+        <v>271.78</v>
       </c>
       <c r="K25" t="n">
-        <v>371.98</v>
+        <v>188.35</v>
       </c>
       <c r="L25" t="n">
-        <v>653.05</v>
+        <v>330.66</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>793.85</v>
+        <v>364.3</v>
       </c>
       <c r="K26" t="n">
-        <v>-175.22</v>
+        <v>-80.41</v>
       </c>
       <c r="L26" t="n">
-        <v>812.95</v>
+        <v>373.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-277.66</v>
+        <v>-149.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-377.75</v>
+        <v>-202.9</v>
       </c>
       <c r="L27" t="n">
-        <v>468.82</v>
+        <v>251.81</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>327.02</v>
+        <v>149.97</v>
       </c>
       <c r="K28" t="n">
-        <v>757.27</v>
+        <v>347.27</v>
       </c>
       <c r="L28" t="n">
-        <v>824.86</v>
+        <v>378.27</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>140.37</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-205.37</v>
+        <v>-146.05</v>
       </c>
       <c r="L29" t="n">
-        <v>248.76</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-37.6</v>
+        <v>-28.51</v>
       </c>
       <c r="K30" t="n">
-        <v>119.32</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>125.1</v>
+        <v>94.84999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-124.22</v>
+        <v>-89.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.49</v>
+        <v>-27.87</v>
       </c>
       <c r="L31" t="n">
-        <v>130.05</v>
+        <v>94.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-144.95</v>
+        <v>-108.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-294.02</v>
+        <v>-220.98</v>
       </c>
       <c r="L32" t="n">
-        <v>327.81</v>
+        <v>246.38</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-54.29</v>
+        <v>-40.06</v>
       </c>
       <c r="K33" t="n">
-        <v>206.43</v>
+        <v>152.33</v>
       </c>
       <c r="L33" t="n">
-        <v>213.45</v>
+        <v>157.51</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.71</v>
+        <v>-2.96</v>
       </c>
       <c r="K34" t="n">
-        <v>-262.89</v>
+        <v>-165.19</v>
       </c>
       <c r="L34" t="n">
-        <v>262.93</v>
+        <v>165.21</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>164.62</v>
+        <v>113.54</v>
       </c>
       <c r="K35" t="n">
-        <v>-304.95</v>
+        <v>-210.32</v>
       </c>
       <c r="L35" t="n">
-        <v>346.54</v>
+        <v>239.01</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-551.01</v>
+        <v>-313.88</v>
       </c>
       <c r="K36" t="n">
-        <v>150.2</v>
+        <v>85.56</v>
       </c>
       <c r="L36" t="n">
-        <v>571.11</v>
+        <v>325.33</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-913.9400000000001</v>
+        <v>-516.27</v>
       </c>
       <c r="K37" t="n">
-        <v>304.03</v>
+        <v>171.74</v>
       </c>
       <c r="L37" t="n">
-        <v>963.1799999999999</v>
+        <v>544.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-44.92</v>
+        <v>-24.05</v>
       </c>
       <c r="K38" t="n">
-        <v>730.96</v>
+        <v>391.38</v>
       </c>
       <c r="L38" t="n">
-        <v>732.34</v>
+        <v>392.12</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-93.77</v>
+        <v>-50.78</v>
       </c>
       <c r="K39" t="n">
-        <v>-486.08</v>
+        <v>-263.22</v>
       </c>
       <c r="L39" t="n">
-        <v>495.04</v>
+        <v>268.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-712.76</v>
+        <v>-375.09</v>
       </c>
       <c r="K40" t="n">
-        <v>-184.17</v>
+        <v>-96.92</v>
       </c>
       <c r="L40" t="n">
-        <v>736.17</v>
+        <v>387.4</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>712.2</v>
+        <v>362.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-595.99</v>
+        <v>-303.73</v>
       </c>
       <c r="L41" t="n">
-        <v>928.6799999999999</v>
+        <v>473.27</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-611.02</v>
+        <v>-286.31</v>
       </c>
       <c r="K42" t="n">
-        <v>454.39</v>
+        <v>212.92</v>
       </c>
       <c r="L42" t="n">
-        <v>761.45</v>
+        <v>356.8</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>940.83</v>
+        <v>444.5</v>
       </c>
       <c r="K43" t="n">
-        <v>-92.27</v>
+        <v>-43.59</v>
       </c>
       <c r="L43" t="n">
-        <v>945.35</v>
+        <v>446.63</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>72.77</v>
+        <v>59.09</v>
       </c>
       <c r="K44" t="n">
-        <v>-208.85</v>
+        <v>-169.58</v>
       </c>
       <c r="L44" t="n">
-        <v>221.17</v>
+        <v>179.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>82.42</v>
+        <v>59.31</v>
       </c>
       <c r="K45" t="n">
-        <v>255.58</v>
+        <v>183.9</v>
       </c>
       <c r="L45" t="n">
-        <v>268.54</v>
+        <v>193.23</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-250.03</v>
+        <v>-161.36</v>
       </c>
       <c r="K46" t="n">
-        <v>270.75</v>
+        <v>174.73</v>
       </c>
       <c r="L46" t="n">
-        <v>368.54</v>
+        <v>237.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>366.24</v>
+        <v>246.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-242.48</v>
+        <v>-163.39</v>
       </c>
       <c r="L47" t="n">
-        <v>439.23</v>
+        <v>295.96</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-96.38</v>
+        <v>-64.19</v>
       </c>
       <c r="K48" t="n">
-        <v>342.75</v>
+        <v>228.3</v>
       </c>
       <c r="L48" t="n">
-        <v>356.05</v>
+        <v>237.16</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>249.11</v>
+        <v>173.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-89.41</v>
+        <v>-62.14</v>
       </c>
       <c r="L49" t="n">
-        <v>264.67</v>
+        <v>183.95</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>703.05</v>
+        <v>398.67</v>
       </c>
       <c r="K50" t="n">
-        <v>-85.92</v>
+        <v>-48.72</v>
       </c>
       <c r="L50" t="n">
-        <v>708.28</v>
+        <v>401.63</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-467.66</v>
+        <v>-259.4</v>
       </c>
       <c r="K51" t="n">
-        <v>-315.98</v>
+        <v>-175.27</v>
       </c>
       <c r="L51" t="n">
-        <v>564.4</v>
+        <v>313.06</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>421.01</v>
+        <v>243.32</v>
       </c>
       <c r="K52" t="n">
-        <v>-69.8</v>
+        <v>-40.34</v>
       </c>
       <c r="L52" t="n">
-        <v>426.76</v>
+        <v>246.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-631.96</v>
+        <v>-349.59</v>
       </c>
       <c r="K53" t="n">
-        <v>533.0700000000001</v>
+        <v>294.89</v>
       </c>
       <c r="L53" t="n">
-        <v>826.76</v>
+        <v>457.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-491.24</v>
+        <v>-243.03</v>
       </c>
       <c r="K54" t="n">
-        <v>430.38</v>
+        <v>212.92</v>
       </c>
       <c r="L54" t="n">
-        <v>653.11</v>
+        <v>323.11</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>868.25</v>
+        <v>451.58</v>
       </c>
       <c r="K55" t="n">
-        <v>520.98</v>
+        <v>270.96</v>
       </c>
       <c r="L55" t="n">
-        <v>1012.56</v>
+        <v>526.64</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>107.56</v>
+        <v>60.12</v>
       </c>
       <c r="K56" t="n">
-        <v>-443.9</v>
+        <v>-248.1</v>
       </c>
       <c r="L56" t="n">
-        <v>456.74</v>
+        <v>255.28</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-97.47</v>
+        <v>-51.37</v>
       </c>
       <c r="K57" t="n">
-        <v>1075.61</v>
+        <v>566.84</v>
       </c>
       <c r="L57" t="n">
-        <v>1080.02</v>
+        <v>569.16</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-1259.8</v>
+        <v>-623.1900000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-500.26</v>
+        <v>-247.47</v>
       </c>
       <c r="L58" t="n">
-        <v>1355.49</v>
+        <v>670.52</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>428.76</v>
+        <v>279.22</v>
       </c>
       <c r="K59" t="n">
-        <v>229.13</v>
+        <v>149.22</v>
       </c>
       <c r="L59" t="n">
-        <v>486.14</v>
+        <v>316.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>89.97</v>
+        <v>70.97</v>
       </c>
       <c r="K60" t="n">
-        <v>206.47</v>
+        <v>162.85</v>
       </c>
       <c r="L60" t="n">
-        <v>225.22</v>
+        <v>177.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>256.43</v>
+        <v>170.86</v>
       </c>
       <c r="K61" t="n">
-        <v>48.06</v>
+        <v>32.02</v>
       </c>
       <c r="L61" t="n">
-        <v>260.89</v>
+        <v>173.84</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>122</v>
+        <v>78.58</v>
       </c>
       <c r="K62" t="n">
-        <v>-347.03</v>
+        <v>-223.53</v>
       </c>
       <c r="L62" t="n">
-        <v>367.85</v>
+        <v>236.94</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-253.43</v>
+        <v>-182.46</v>
       </c>
       <c r="K63" t="n">
-        <v>367.62</v>
+        <v>264.68</v>
       </c>
       <c r="L63" t="n">
-        <v>446.51</v>
+        <v>321.48</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-474.93</v>
+        <v>-336.24</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.67</v>
+        <v>-2.6</v>
       </c>
       <c r="L64" t="n">
-        <v>474.94</v>
+        <v>336.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-429.98</v>
+        <v>-290.28</v>
       </c>
       <c r="K65" t="n">
-        <v>361.83</v>
+        <v>244.27</v>
       </c>
       <c r="L65" t="n">
-        <v>561.97</v>
+        <v>379.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>332.41</v>
+        <v>209.77</v>
       </c>
       <c r="K66" t="n">
-        <v>275.3</v>
+        <v>173.73</v>
       </c>
       <c r="L66" t="n">
-        <v>431.61</v>
+        <v>272.37</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>330.39</v>
+        <v>214.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-344.36</v>
+        <v>-223.99</v>
       </c>
       <c r="L67" t="n">
-        <v>477.22</v>
+        <v>310.42</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-715.83</v>
+        <v>-353.2</v>
       </c>
       <c r="K68" t="n">
-        <v>-218.17</v>
+        <v>-107.65</v>
       </c>
       <c r="L68" t="n">
-        <v>748.34</v>
+        <v>369.24</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-1401.13</v>
+        <v>-778.8099999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-477.3</v>
+        <v>-265.31</v>
       </c>
       <c r="L69" t="n">
-        <v>1480.2</v>
+        <v>822.76</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>470.88</v>
+        <v>258.96</v>
       </c>
       <c r="K70" t="n">
-        <v>876.66</v>
+        <v>482.12</v>
       </c>
       <c r="L70" t="n">
-        <v>995.12</v>
+        <v>547.26</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>1224.11</v>
+        <v>552.1900000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-302.83</v>
+        <v>-136.61</v>
       </c>
       <c r="L71" t="n">
-        <v>1261.01</v>
+        <v>568.84</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-1241.58</v>
+        <v>-595.79</v>
       </c>
       <c r="K72" t="n">
-        <v>30.92</v>
+        <v>14.84</v>
       </c>
       <c r="L72" t="n">
-        <v>1241.96</v>
+        <v>595.97</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>845.13</v>
+        <v>454.32</v>
       </c>
       <c r="K73" t="n">
-        <v>153.08</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>858.88</v>
+        <v>461.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-497.28</v>
+        <v>-328.94</v>
       </c>
       <c r="K74" t="n">
-        <v>52.76</v>
+        <v>34.9</v>
       </c>
       <c r="L74" t="n">
-        <v>500.07</v>
+        <v>330.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>253.89</v>
+        <v>176.13</v>
       </c>
       <c r="K75" t="n">
-        <v>76.19</v>
+        <v>52.85</v>
       </c>
       <c r="L75" t="n">
-        <v>265.08</v>
+        <v>183.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-249.41</v>
+        <v>-164.61</v>
       </c>
       <c r="K76" t="n">
-        <v>-388.31</v>
+        <v>-256.27</v>
       </c>
       <c r="L76" t="n">
-        <v>461.51</v>
+        <v>304.59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-413.84</v>
+        <v>-258.73</v>
       </c>
       <c r="K77" t="n">
-        <v>-199.45</v>
+        <v>-124.7</v>
       </c>
       <c r="L77" t="n">
-        <v>459.39</v>
+        <v>287.21</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-263.57</v>
+        <v>-188.2</v>
       </c>
       <c r="K78" t="n">
-        <v>-185.37</v>
+        <v>-132.36</v>
       </c>
       <c r="L78" t="n">
-        <v>322.23</v>
+        <v>230.09</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-263.58</v>
+        <v>-175.24</v>
       </c>
       <c r="K79" t="n">
-        <v>18.7</v>
+        <v>12.43</v>
       </c>
       <c r="L79" t="n">
-        <v>264.25</v>
+        <v>175.68</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>627.22</v>
+        <v>338</v>
       </c>
       <c r="K80" t="n">
-        <v>-25.27</v>
+        <v>-13.62</v>
       </c>
       <c r="L80" t="n">
-        <v>627.73</v>
+        <v>338.28</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>937.53</v>
+        <v>505.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-560.79</v>
+        <v>-302.25</v>
       </c>
       <c r="L81" t="n">
-        <v>1092.45</v>
+        <v>588.8</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-29.39</v>
+        <v>-18.89</v>
       </c>
       <c r="K82" t="n">
-        <v>425.44</v>
+        <v>273.42</v>
       </c>
       <c r="L82" t="n">
-        <v>426.45</v>
+        <v>274.08</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-35.98</v>
+        <v>-17.75</v>
       </c>
       <c r="K83" t="n">
-        <v>-802.15</v>
+        <v>-395.65</v>
       </c>
       <c r="L83" t="n">
-        <v>802.96</v>
+        <v>396.05</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-1037.62</v>
+        <v>-619.78</v>
       </c>
       <c r="K84" t="n">
-        <v>-657.37</v>
+        <v>-392.65</v>
       </c>
       <c r="L84" t="n">
-        <v>1228.33</v>
+        <v>733.6900000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>883</v>
+        <v>523.74</v>
       </c>
       <c r="K85" t="n">
-        <v>212.18</v>
+        <v>125.85</v>
       </c>
       <c r="L85" t="n">
-        <v>908.13</v>
+        <v>538.65</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-576.1900000000001</v>
+        <v>-295.84</v>
       </c>
       <c r="K86" t="n">
-        <v>999.9299999999999</v>
+        <v>513.41</v>
       </c>
       <c r="L86" t="n">
-        <v>1154.06</v>
+        <v>592.55</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>642.3099999999999</v>
+        <v>307.67</v>
       </c>
       <c r="K87" t="n">
-        <v>361.77</v>
+        <v>173.29</v>
       </c>
       <c r="L87" t="n">
-        <v>737.1900000000001</v>
+        <v>353.12</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-567.91</v>
+        <v>-305.25</v>
       </c>
       <c r="K88" t="n">
-        <v>771.4400000000001</v>
+        <v>414.65</v>
       </c>
       <c r="L88" t="n">
-        <v>957.9400000000001</v>
+        <v>514.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>101.44</v>
+        <v>107.35</v>
       </c>
       <c r="K14" t="n">
-        <v>-102.07</v>
+        <v>-108.02</v>
       </c>
       <c r="L14" t="n">
-        <v>143.91</v>
+        <v>152.29</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.92</v>
+        <v>-21.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-166.47</v>
+        <v>-173.44</v>
       </c>
       <c r="L15" t="n">
-        <v>167.78</v>
+        <v>174.8</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>23.61</v>
+        <v>25.15</v>
       </c>
       <c r="K16" t="n">
-        <v>146.23</v>
+        <v>155.76</v>
       </c>
       <c r="L16" t="n">
-        <v>148.12</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>171.16</v>
+        <v>180.75</v>
       </c>
       <c r="K17" t="n">
-        <v>155.61</v>
+        <v>164.32</v>
       </c>
       <c r="L17" t="n">
-        <v>231.32</v>
+        <v>244.28</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-200.3</v>
+        <v>-209.36</v>
       </c>
       <c r="K18" t="n">
-        <v>115.11</v>
+        <v>120.32</v>
       </c>
       <c r="L18" t="n">
-        <v>231.02</v>
+        <v>241.47</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>135.2</v>
+        <v>142.41</v>
       </c>
       <c r="K19" t="n">
-        <v>37.52</v>
+        <v>39.52</v>
       </c>
       <c r="L19" t="n">
-        <v>140.31</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-355.66</v>
+        <v>-395.15</v>
       </c>
       <c r="K20" t="n">
-        <v>264.18</v>
+        <v>293.51</v>
       </c>
       <c r="L20" t="n">
-        <v>443.04</v>
+        <v>492.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>198.23</v>
+        <v>216.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-229.74</v>
+        <v>-251.2</v>
       </c>
       <c r="L21" t="n">
-        <v>303.44</v>
+        <v>331.78</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-136.1</v>
+        <v>-148.84</v>
       </c>
       <c r="K22" t="n">
-        <v>-135.12</v>
+        <v>-147.78</v>
       </c>
       <c r="L22" t="n">
-        <v>191.79</v>
+        <v>209.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>18.09</v>
+        <v>20.61</v>
       </c>
       <c r="K23" t="n">
-        <v>-259.83</v>
+        <v>-296.08</v>
       </c>
       <c r="L23" t="n">
-        <v>260.46</v>
+        <v>296.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-142.95</v>
+        <v>-161.57</v>
       </c>
       <c r="K24" t="n">
-        <v>305.4</v>
+        <v>345.2</v>
       </c>
       <c r="L24" t="n">
-        <v>337.2</v>
+        <v>381.14</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>271.78</v>
+        <v>311.45</v>
       </c>
       <c r="K25" t="n">
-        <v>188.35</v>
+        <v>215.84</v>
       </c>
       <c r="L25" t="n">
-        <v>330.66</v>
+        <v>378.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>364.3</v>
+        <v>425.37</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.41</v>
+        <v>-93.89</v>
       </c>
       <c r="L26" t="n">
-        <v>373.07</v>
+        <v>435.61</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-149.14</v>
+        <v>-172.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-202.9</v>
+        <v>-234.6</v>
       </c>
       <c r="L27" t="n">
-        <v>251.81</v>
+        <v>291.16</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>149.97</v>
+        <v>174.93</v>
       </c>
       <c r="K28" t="n">
-        <v>347.27</v>
+        <v>405.09</v>
       </c>
       <c r="L28" t="n">
-        <v>378.27</v>
+        <v>441.24</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>99.81999999999999</v>
+        <v>106.45</v>
       </c>
       <c r="K29" t="n">
-        <v>-146.05</v>
+        <v>-155.74</v>
       </c>
       <c r="L29" t="n">
-        <v>176.9</v>
+        <v>188.65</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-28.51</v>
+        <v>-29.72</v>
       </c>
       <c r="K30" t="n">
-        <v>90.45999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="L30" t="n">
-        <v>94.84999999999999</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-89.94</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.87</v>
+        <v>-29.39</v>
       </c>
       <c r="L31" t="n">
-        <v>94.16</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-108.95</v>
+        <v>-114.67</v>
       </c>
       <c r="K32" t="n">
-        <v>-220.98</v>
+        <v>-232.59</v>
       </c>
       <c r="L32" t="n">
-        <v>246.38</v>
+        <v>259.32</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.06</v>
+        <v>-42.24</v>
       </c>
       <c r="K33" t="n">
-        <v>152.33</v>
+        <v>160.58</v>
       </c>
       <c r="L33" t="n">
-        <v>157.51</v>
+        <v>166.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.96</v>
+        <v>-3.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-165.19</v>
+        <v>-179.5</v>
       </c>
       <c r="L34" t="n">
-        <v>165.21</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>113.54</v>
+        <v>123.72</v>
       </c>
       <c r="K35" t="n">
-        <v>-210.32</v>
+        <v>-229.18</v>
       </c>
       <c r="L35" t="n">
-        <v>239.01</v>
+        <v>260.44</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-313.88</v>
+        <v>-347.16</v>
       </c>
       <c r="K36" t="n">
-        <v>85.56</v>
+        <v>94.63</v>
       </c>
       <c r="L36" t="n">
-        <v>325.33</v>
+        <v>359.83</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-516.27</v>
+        <v>-574.33</v>
       </c>
       <c r="K37" t="n">
-        <v>171.74</v>
+        <v>191.05</v>
       </c>
       <c r="L37" t="n">
-        <v>544.09</v>
+        <v>605.27</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-24.05</v>
+        <v>-27.17</v>
       </c>
       <c r="K38" t="n">
-        <v>391.38</v>
+        <v>442.1</v>
       </c>
       <c r="L38" t="n">
-        <v>392.12</v>
+        <v>442.94</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-50.78</v>
+        <v>-57.37</v>
       </c>
       <c r="K39" t="n">
-        <v>-263.22</v>
+        <v>-297.38</v>
       </c>
       <c r="L39" t="n">
-        <v>268.08</v>
+        <v>302.86</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-375.09</v>
+        <v>-430.11</v>
       </c>
       <c r="K40" t="n">
-        <v>-96.92</v>
+        <v>-111.14</v>
       </c>
       <c r="L40" t="n">
-        <v>387.4</v>
+        <v>444.23</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>362.95</v>
+        <v>415.75</v>
       </c>
       <c r="K41" t="n">
-        <v>-303.73</v>
+        <v>-347.92</v>
       </c>
       <c r="L41" t="n">
-        <v>473.27</v>
+        <v>542.12</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-286.31</v>
+        <v>-331.83</v>
       </c>
       <c r="K42" t="n">
-        <v>212.92</v>
+        <v>246.77</v>
       </c>
       <c r="L42" t="n">
-        <v>356.8</v>
+        <v>413.53</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>444.5</v>
+        <v>519.89</v>
       </c>
       <c r="K43" t="n">
-        <v>-43.59</v>
+        <v>-50.99</v>
       </c>
       <c r="L43" t="n">
-        <v>446.63</v>
+        <v>522.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>59.09</v>
+        <v>62.03</v>
       </c>
       <c r="K44" t="n">
-        <v>-169.58</v>
+        <v>-178.02</v>
       </c>
       <c r="L44" t="n">
-        <v>179.58</v>
+        <v>188.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>59.31</v>
+        <v>62.84</v>
       </c>
       <c r="K45" t="n">
-        <v>183.9</v>
+        <v>194.86</v>
       </c>
       <c r="L45" t="n">
-        <v>193.23</v>
+        <v>204.74</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-161.36</v>
+        <v>-175.58</v>
       </c>
       <c r="K46" t="n">
-        <v>174.73</v>
+        <v>190.13</v>
       </c>
       <c r="L46" t="n">
-        <v>237.84</v>
+        <v>258.8</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>246.78</v>
+        <v>262.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-163.39</v>
+        <v>-173.89</v>
       </c>
       <c r="L47" t="n">
-        <v>295.96</v>
+        <v>314.99</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-64.19</v>
+        <v>-69.12</v>
       </c>
       <c r="K48" t="n">
-        <v>228.3</v>
+        <v>245.82</v>
       </c>
       <c r="L48" t="n">
-        <v>237.16</v>
+        <v>255.35</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>173.13</v>
+        <v>183.99</v>
       </c>
       <c r="K49" t="n">
-        <v>-62.14</v>
+        <v>-66.04000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>183.95</v>
+        <v>195.48</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>398.67</v>
+        <v>443.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-48.72</v>
+        <v>-54.14</v>
       </c>
       <c r="L50" t="n">
-        <v>401.63</v>
+        <v>446.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-259.4</v>
+        <v>-289.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-175.27</v>
+        <v>-195.74</v>
       </c>
       <c r="L51" t="n">
-        <v>313.06</v>
+        <v>349.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>243.32</v>
+        <v>271.45</v>
       </c>
       <c r="K52" t="n">
-        <v>-40.34</v>
+        <v>-45</v>
       </c>
       <c r="L52" t="n">
-        <v>246.64</v>
+        <v>275.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-349.59</v>
+        <v>-396.21</v>
       </c>
       <c r="K53" t="n">
-        <v>294.89</v>
+        <v>334.22</v>
       </c>
       <c r="L53" t="n">
-        <v>457.35</v>
+        <v>518.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-243.03</v>
+        <v>-276.08</v>
       </c>
       <c r="K54" t="n">
-        <v>212.92</v>
+        <v>241.87</v>
       </c>
       <c r="L54" t="n">
-        <v>323.11</v>
+        <v>367.05</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>451.58</v>
+        <v>515.65</v>
       </c>
       <c r="K55" t="n">
-        <v>270.96</v>
+        <v>309.4</v>
       </c>
       <c r="L55" t="n">
-        <v>526.64</v>
+        <v>601.35</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>60.12</v>
+        <v>68.75</v>
       </c>
       <c r="K56" t="n">
-        <v>-248.1</v>
+        <v>-283.75</v>
       </c>
       <c r="L56" t="n">
-        <v>255.28</v>
+        <v>291.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-51.37</v>
+        <v>-58.68</v>
       </c>
       <c r="K57" t="n">
-        <v>566.84</v>
+        <v>647.52</v>
       </c>
       <c r="L57" t="n">
-        <v>569.16</v>
+        <v>650.17</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-623.1900000000001</v>
+        <v>-706.79</v>
       </c>
       <c r="K58" t="n">
-        <v>-247.47</v>
+        <v>-280.67</v>
       </c>
       <c r="L58" t="n">
-        <v>670.52</v>
+        <v>760.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>279.22</v>
+        <v>298.93</v>
       </c>
       <c r="K59" t="n">
-        <v>149.22</v>
+        <v>159.75</v>
       </c>
       <c r="L59" t="n">
-        <v>316.59</v>
+        <v>338.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>70.97</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>162.85</v>
+        <v>171.69</v>
       </c>
       <c r="L60" t="n">
-        <v>177.64</v>
+        <v>187.28</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>170.86</v>
+        <v>184.47</v>
       </c>
       <c r="K61" t="n">
-        <v>32.02</v>
+        <v>34.57</v>
       </c>
       <c r="L61" t="n">
-        <v>173.84</v>
+        <v>187.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>78.58</v>
+        <v>85.02</v>
       </c>
       <c r="K62" t="n">
-        <v>-223.53</v>
+        <v>-241.83</v>
       </c>
       <c r="L62" t="n">
-        <v>236.94</v>
+        <v>256.34</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-182.46</v>
+        <v>-194.27</v>
       </c>
       <c r="K63" t="n">
-        <v>264.68</v>
+        <v>281.82</v>
       </c>
       <c r="L63" t="n">
-        <v>321.48</v>
+        <v>342.29</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-336.24</v>
+        <v>-361.24</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.6</v>
+        <v>-2.79</v>
       </c>
       <c r="L64" t="n">
-        <v>336.25</v>
+        <v>361.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-290.28</v>
+        <v>-311.63</v>
       </c>
       <c r="K65" t="n">
-        <v>244.27</v>
+        <v>262.24</v>
       </c>
       <c r="L65" t="n">
-        <v>379.38</v>
+        <v>407.29</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>209.77</v>
+        <v>227.76</v>
       </c>
       <c r="K66" t="n">
-        <v>173.73</v>
+        <v>188.62</v>
       </c>
       <c r="L66" t="n">
-        <v>272.37</v>
+        <v>295.72</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>214.91</v>
+        <v>232.14</v>
       </c>
       <c r="K67" t="n">
-        <v>-223.99</v>
+        <v>-241.95</v>
       </c>
       <c r="L67" t="n">
-        <v>310.42</v>
+        <v>335.31</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-353.2</v>
+        <v>-405.25</v>
       </c>
       <c r="K68" t="n">
-        <v>-107.65</v>
+        <v>-123.51</v>
       </c>
       <c r="L68" t="n">
-        <v>369.24</v>
+        <v>423.65</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-778.8099999999999</v>
+        <v>-870.63</v>
       </c>
       <c r="K69" t="n">
-        <v>-265.31</v>
+        <v>-296.59</v>
       </c>
       <c r="L69" t="n">
-        <v>822.76</v>
+        <v>919.76</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>258.96</v>
+        <v>286.96</v>
       </c>
       <c r="K70" t="n">
-        <v>482.12</v>
+        <v>534.26</v>
       </c>
       <c r="L70" t="n">
-        <v>547.26</v>
+        <v>606.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>552.1900000000001</v>
+        <v>641.79</v>
       </c>
       <c r="K71" t="n">
-        <v>-136.61</v>
+        <v>-158.77</v>
       </c>
       <c r="L71" t="n">
-        <v>568.84</v>
+        <v>661.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-595.79</v>
+        <v>-685.03</v>
       </c>
       <c r="K72" t="n">
-        <v>14.84</v>
+        <v>17.06</v>
       </c>
       <c r="L72" t="n">
-        <v>595.97</v>
+        <v>685.25</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>454.32</v>
+        <v>511.87</v>
       </c>
       <c r="K73" t="n">
-        <v>82.29000000000001</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>461.72</v>
+        <v>520.2</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-328.94</v>
+        <v>-355.05</v>
       </c>
       <c r="K74" t="n">
-        <v>34.9</v>
+        <v>37.67</v>
       </c>
       <c r="L74" t="n">
-        <v>330.78</v>
+        <v>357.04</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>176.13</v>
+        <v>187.95</v>
       </c>
       <c r="K75" t="n">
-        <v>52.85</v>
+        <v>56.4</v>
       </c>
       <c r="L75" t="n">
-        <v>183.89</v>
+        <v>196.23</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-164.61</v>
+        <v>-178.56</v>
       </c>
       <c r="K76" t="n">
-        <v>-256.27</v>
+        <v>-278</v>
       </c>
       <c r="L76" t="n">
-        <v>304.59</v>
+        <v>330.4</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-258.73</v>
+        <v>-281.91</v>
       </c>
       <c r="K77" t="n">
-        <v>-124.7</v>
+        <v>-135.87</v>
       </c>
       <c r="L77" t="n">
-        <v>287.21</v>
+        <v>312.94</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-188.2</v>
+        <v>-199.89</v>
       </c>
       <c r="K78" t="n">
-        <v>-132.36</v>
+        <v>-140.58</v>
       </c>
       <c r="L78" t="n">
-        <v>230.09</v>
+        <v>244.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-175.24</v>
+        <v>-186.72</v>
       </c>
       <c r="K79" t="n">
-        <v>12.43</v>
+        <v>13.25</v>
       </c>
       <c r="L79" t="n">
-        <v>175.68</v>
+        <v>187.19</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>338</v>
+        <v>375.42</v>
       </c>
       <c r="K80" t="n">
-        <v>-13.62</v>
+        <v>-15.13</v>
       </c>
       <c r="L80" t="n">
-        <v>338.28</v>
+        <v>375.72</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>505.3</v>
+        <v>559.04</v>
       </c>
       <c r="K81" t="n">
-        <v>-302.25</v>
+        <v>-334.4</v>
       </c>
       <c r="L81" t="n">
-        <v>588.8</v>
+        <v>651.42</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-18.89</v>
+        <v>-20.46</v>
       </c>
       <c r="K82" t="n">
-        <v>273.42</v>
+        <v>296.23</v>
       </c>
       <c r="L82" t="n">
-        <v>274.08</v>
+        <v>296.93</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-17.75</v>
+        <v>-20.08</v>
       </c>
       <c r="K83" t="n">
-        <v>-395.65</v>
+        <v>-447.78</v>
       </c>
       <c r="L83" t="n">
-        <v>396.05</v>
+        <v>448.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-619.78</v>
+        <v>-684.47</v>
       </c>
       <c r="K84" t="n">
-        <v>-392.65</v>
+        <v>-433.64</v>
       </c>
       <c r="L84" t="n">
-        <v>733.6900000000001</v>
+        <v>810.27</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>523.74</v>
+        <v>581.64</v>
       </c>
       <c r="K85" t="n">
-        <v>125.85</v>
+        <v>139.77</v>
       </c>
       <c r="L85" t="n">
-        <v>538.65</v>
+        <v>598.2</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-295.84</v>
+        <v>-332.63</v>
       </c>
       <c r="K86" t="n">
-        <v>513.41</v>
+        <v>577.26</v>
       </c>
       <c r="L86" t="n">
-        <v>592.55</v>
+        <v>666.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>307.67</v>
+        <v>351.04</v>
       </c>
       <c r="K87" t="n">
-        <v>173.29</v>
+        <v>197.72</v>
       </c>
       <c r="L87" t="n">
-        <v>353.12</v>
+        <v>402.9</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-305.25</v>
+        <v>-345.87</v>
       </c>
       <c r="K88" t="n">
-        <v>414.65</v>
+        <v>469.82</v>
       </c>
       <c r="L88" t="n">
-        <v>514.89</v>
+        <v>583.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>107.35</v>
+        <v>43.08</v>
       </c>
       <c r="K14" t="n">
-        <v>-108.02</v>
+        <v>-43.35</v>
       </c>
       <c r="L14" t="n">
-        <v>152.29</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-21.8</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-173.44</v>
+        <v>-69.86</v>
       </c>
       <c r="L15" t="n">
-        <v>174.8</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>25.15</v>
+        <v>10.23</v>
       </c>
       <c r="K16" t="n">
-        <v>155.76</v>
+        <v>63.34</v>
       </c>
       <c r="L16" t="n">
-        <v>157.78</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>180.75</v>
+        <v>75.44</v>
       </c>
       <c r="K17" t="n">
-        <v>164.32</v>
+        <v>68.58</v>
       </c>
       <c r="L17" t="n">
-        <v>244.28</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-209.36</v>
+        <v>-88.58</v>
       </c>
       <c r="K18" t="n">
-        <v>120.32</v>
+        <v>50.91</v>
       </c>
       <c r="L18" t="n">
-        <v>241.47</v>
+        <v>102.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>142.41</v>
+        <v>62.19</v>
       </c>
       <c r="K19" t="n">
-        <v>39.52</v>
+        <v>17.26</v>
       </c>
       <c r="L19" t="n">
-        <v>147.79</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-395.15</v>
+        <v>-189.01</v>
       </c>
       <c r="K20" t="n">
-        <v>293.51</v>
+        <v>140.39</v>
       </c>
       <c r="L20" t="n">
-        <v>492.23</v>
+        <v>235.45</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>216.74</v>
+        <v>103.52</v>
       </c>
       <c r="K21" t="n">
-        <v>-251.2</v>
+        <v>-119.97</v>
       </c>
       <c r="L21" t="n">
-        <v>331.78</v>
+        <v>158.46</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-148.84</v>
+        <v>-71.19</v>
       </c>
       <c r="K22" t="n">
-        <v>-147.78</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>209.75</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>20.61</v>
+        <v>9.23</v>
       </c>
       <c r="K23" t="n">
-        <v>-296.08</v>
+        <v>-132.53</v>
       </c>
       <c r="L23" t="n">
-        <v>296.8</v>
+        <v>132.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-161.57</v>
+        <v>-71.84</v>
       </c>
       <c r="K24" t="n">
-        <v>345.2</v>
+        <v>153.49</v>
       </c>
       <c r="L24" t="n">
-        <v>381.14</v>
+        <v>169.48</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>311.45</v>
+        <v>140.4</v>
       </c>
       <c r="K25" t="n">
-        <v>215.84</v>
+        <v>97.3</v>
       </c>
       <c r="L25" t="n">
-        <v>378.93</v>
+        <v>170.81</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>425.37</v>
+        <v>229.5</v>
       </c>
       <c r="K26" t="n">
-        <v>-93.89</v>
+        <v>-50.65</v>
       </c>
       <c r="L26" t="n">
-        <v>435.61</v>
+        <v>235.03</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-172.44</v>
+        <v>-91.18000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-234.6</v>
+        <v>-124.04</v>
       </c>
       <c r="L27" t="n">
-        <v>291.16</v>
+        <v>153.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>174.93</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>405.09</v>
+        <v>218.74</v>
       </c>
       <c r="L28" t="n">
-        <v>441.24</v>
+        <v>238.27</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>106.45</v>
+        <v>42.47</v>
       </c>
       <c r="K29" t="n">
-        <v>-155.74</v>
+        <v>-62.14</v>
       </c>
       <c r="L29" t="n">
-        <v>188.65</v>
+        <v>75.27</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-29.72</v>
+        <v>-6.38</v>
       </c>
       <c r="K30" t="n">
-        <v>94.3</v>
+        <v>20.24</v>
       </c>
       <c r="L30" t="n">
-        <v>98.87</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-94.84999999999999</v>
+        <v>-4.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.39</v>
+        <v>-1.5</v>
       </c>
       <c r="L31" t="n">
-        <v>99.3</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-114.67</v>
+        <v>-48.99</v>
       </c>
       <c r="K32" t="n">
-        <v>-232.59</v>
+        <v>-99.38</v>
       </c>
       <c r="L32" t="n">
-        <v>259.32</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.24</v>
+        <v>-17.58</v>
       </c>
       <c r="K33" t="n">
-        <v>160.58</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>166.05</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.22</v>
+        <v>-1.39</v>
       </c>
       <c r="K34" t="n">
-        <v>-179.5</v>
+        <v>-77.66</v>
       </c>
       <c r="L34" t="n">
-        <v>179.53</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>123.72</v>
+        <v>59.1</v>
       </c>
       <c r="K35" t="n">
-        <v>-229.18</v>
+        <v>-109.48</v>
       </c>
       <c r="L35" t="n">
-        <v>260.44</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-347.16</v>
+        <v>-165.99</v>
       </c>
       <c r="K36" t="n">
-        <v>94.63</v>
+        <v>45.25</v>
       </c>
       <c r="L36" t="n">
-        <v>359.83</v>
+        <v>172.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-574.33</v>
+        <v>-274.84</v>
       </c>
       <c r="K37" t="n">
-        <v>191.05</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>605.27</v>
+        <v>289.65</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-27.17</v>
+        <v>-12.52</v>
       </c>
       <c r="K38" t="n">
-        <v>442.1</v>
+        <v>203.72</v>
       </c>
       <c r="L38" t="n">
-        <v>442.94</v>
+        <v>204.11</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-57.37</v>
+        <v>-25.78</v>
       </c>
       <c r="K39" t="n">
-        <v>-297.38</v>
+        <v>-133.62</v>
       </c>
       <c r="L39" t="n">
-        <v>302.86</v>
+        <v>136.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-430.11</v>
+        <v>-190.99</v>
       </c>
       <c r="K40" t="n">
-        <v>-111.14</v>
+        <v>-49.35</v>
       </c>
       <c r="L40" t="n">
-        <v>444.23</v>
+        <v>197.27</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>415.75</v>
+        <v>223.53</v>
       </c>
       <c r="K41" t="n">
-        <v>-347.92</v>
+        <v>-187.05</v>
       </c>
       <c r="L41" t="n">
-        <v>542.12</v>
+        <v>291.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-331.83</v>
+        <v>-181.45</v>
       </c>
       <c r="K42" t="n">
-        <v>246.77</v>
+        <v>134.93</v>
       </c>
       <c r="L42" t="n">
-        <v>413.53</v>
+        <v>226.12</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>519.89</v>
+        <v>281.44</v>
       </c>
       <c r="K43" t="n">
-        <v>-50.99</v>
+        <v>-27.6</v>
       </c>
       <c r="L43" t="n">
-        <v>522.38</v>
+        <v>282.79</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>62.03</v>
+        <v>25.1</v>
       </c>
       <c r="K44" t="n">
-        <v>-178.02</v>
+        <v>-72.03</v>
       </c>
       <c r="L44" t="n">
-        <v>188.52</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>62.84</v>
+        <v>25.51</v>
       </c>
       <c r="K45" t="n">
-        <v>194.86</v>
+        <v>79.12</v>
       </c>
       <c r="L45" t="n">
-        <v>204.74</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-175.58</v>
+        <v>-72.02</v>
       </c>
       <c r="K46" t="n">
-        <v>190.13</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>258.8</v>
+        <v>106.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>262.64</v>
+        <v>112.3</v>
       </c>
       <c r="K47" t="n">
-        <v>-173.89</v>
+        <v>-74.34999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>314.99</v>
+        <v>134.68</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.12</v>
+        <v>-30.06</v>
       </c>
       <c r="K48" t="n">
-        <v>245.82</v>
+        <v>106.9</v>
       </c>
       <c r="L48" t="n">
-        <v>255.35</v>
+        <v>111.04</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>183.99</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.04000000000001</v>
+        <v>-28.36</v>
       </c>
       <c r="L49" t="n">
-        <v>195.48</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>443.02</v>
+        <v>211.92</v>
       </c>
       <c r="K50" t="n">
-        <v>-54.14</v>
+        <v>-25.9</v>
       </c>
       <c r="L50" t="n">
-        <v>446.32</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-289.7</v>
+        <v>-138.46</v>
       </c>
       <c r="K51" t="n">
-        <v>-195.74</v>
+        <v>-93.56</v>
       </c>
       <c r="L51" t="n">
-        <v>349.63</v>
+        <v>167.11</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>271.45</v>
+        <v>130.03</v>
       </c>
       <c r="K52" t="n">
-        <v>-45</v>
+        <v>-21.56</v>
       </c>
       <c r="L52" t="n">
-        <v>275.16</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-396.21</v>
+        <v>-184.02</v>
       </c>
       <c r="K53" t="n">
-        <v>334.22</v>
+        <v>155.23</v>
       </c>
       <c r="L53" t="n">
-        <v>518.35</v>
+        <v>240.75</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-276.08</v>
+        <v>-131.01</v>
       </c>
       <c r="K54" t="n">
-        <v>241.87</v>
+        <v>114.78</v>
       </c>
       <c r="L54" t="n">
-        <v>367.05</v>
+        <v>174.18</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>515.65</v>
+        <v>235.06</v>
       </c>
       <c r="K55" t="n">
-        <v>309.4</v>
+        <v>141.04</v>
       </c>
       <c r="L55" t="n">
-        <v>601.35</v>
+        <v>274.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>68.75</v>
+        <v>36.43</v>
       </c>
       <c r="K56" t="n">
-        <v>-283.75</v>
+        <v>-150.35</v>
       </c>
       <c r="L56" t="n">
-        <v>291.96</v>
+        <v>154.7</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-58.68</v>
+        <v>-31.75</v>
       </c>
       <c r="K57" t="n">
-        <v>647.52</v>
+        <v>350.34</v>
       </c>
       <c r="L57" t="n">
-        <v>650.17</v>
+        <v>351.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-706.79</v>
+        <v>-394.13</v>
       </c>
       <c r="K58" t="n">
-        <v>-280.67</v>
+        <v>-156.51</v>
       </c>
       <c r="L58" t="n">
-        <v>760.48</v>
+        <v>424.07</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>298.93</v>
+        <v>121.76</v>
       </c>
       <c r="K59" t="n">
-        <v>159.75</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>338.94</v>
+        <v>138.05</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>74.81999999999999</v>
+        <v>29.97</v>
       </c>
       <c r="K60" t="n">
-        <v>171.69</v>
+        <v>68.78</v>
       </c>
       <c r="L60" t="n">
-        <v>187.28</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>184.47</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>34.57</v>
+        <v>13.83</v>
       </c>
       <c r="L61" t="n">
-        <v>187.69</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>85.02</v>
+        <v>37.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-241.83</v>
+        <v>-105.42</v>
       </c>
       <c r="L62" t="n">
-        <v>256.34</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-194.27</v>
+        <v>-83.53</v>
       </c>
       <c r="K63" t="n">
-        <v>281.82</v>
+        <v>121.17</v>
       </c>
       <c r="L63" t="n">
-        <v>342.29</v>
+        <v>147.18</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-361.24</v>
+        <v>-159.17</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.79</v>
+        <v>-1.23</v>
       </c>
       <c r="L64" t="n">
-        <v>361.25</v>
+        <v>159.18</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-311.63</v>
+        <v>-149.2</v>
       </c>
       <c r="K65" t="n">
-        <v>262.24</v>
+        <v>125.55</v>
       </c>
       <c r="L65" t="n">
-        <v>407.29</v>
+        <v>194.99</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>227.76</v>
+        <v>108.89</v>
       </c>
       <c r="K66" t="n">
-        <v>188.62</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>295.72</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>232.14</v>
+        <v>111.09</v>
       </c>
       <c r="K67" t="n">
-        <v>-241.95</v>
+        <v>-115.78</v>
       </c>
       <c r="L67" t="n">
-        <v>335.31</v>
+        <v>160.45</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-405.25</v>
+        <v>-180.99</v>
       </c>
       <c r="K68" t="n">
-        <v>-123.51</v>
+        <v>-55.16</v>
       </c>
       <c r="L68" t="n">
-        <v>423.65</v>
+        <v>189.21</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-870.63</v>
+        <v>-400.09</v>
       </c>
       <c r="K69" t="n">
-        <v>-296.59</v>
+        <v>-136.29</v>
       </c>
       <c r="L69" t="n">
-        <v>919.76</v>
+        <v>422.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>286.96</v>
+        <v>135.02</v>
       </c>
       <c r="K70" t="n">
-        <v>534.26</v>
+        <v>251.38</v>
       </c>
       <c r="L70" t="n">
-        <v>606.45</v>
+        <v>285.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>641.79</v>
+        <v>353.61</v>
       </c>
       <c r="K71" t="n">
-        <v>-158.77</v>
+        <v>-87.48</v>
       </c>
       <c r="L71" t="n">
-        <v>661.14</v>
+        <v>364.27</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-685.03</v>
+        <v>-379.27</v>
       </c>
       <c r="K72" t="n">
-        <v>17.06</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>685.25</v>
+        <v>379.39</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>511.87</v>
+        <v>284.42</v>
       </c>
       <c r="K73" t="n">
-        <v>92.70999999999999</v>
+        <v>51.52</v>
       </c>
       <c r="L73" t="n">
-        <v>520.2</v>
+        <v>289.04</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-355.05</v>
+        <v>-146.25</v>
       </c>
       <c r="K74" t="n">
-        <v>37.67</v>
+        <v>15.52</v>
       </c>
       <c r="L74" t="n">
-        <v>357.04</v>
+        <v>147.07</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>187.95</v>
+        <v>76.47</v>
       </c>
       <c r="K75" t="n">
-        <v>56.4</v>
+        <v>22.95</v>
       </c>
       <c r="L75" t="n">
-        <v>196.23</v>
+        <v>79.84</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-178.56</v>
+        <v>-73.68000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-278</v>
+        <v>-114.71</v>
       </c>
       <c r="L76" t="n">
-        <v>330.4</v>
+        <v>136.33</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-281.91</v>
+        <v>-122.86</v>
       </c>
       <c r="K77" t="n">
-        <v>-135.87</v>
+        <v>-59.21</v>
       </c>
       <c r="L77" t="n">
-        <v>312.94</v>
+        <v>136.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-199.89</v>
+        <v>-86.98999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-140.58</v>
+        <v>-61.18</v>
       </c>
       <c r="L78" t="n">
-        <v>244.37</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-186.72</v>
+        <v>-81.42</v>
       </c>
       <c r="K79" t="n">
-        <v>13.25</v>
+        <v>5.78</v>
       </c>
       <c r="L79" t="n">
-        <v>187.19</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>375.42</v>
+        <v>179.98</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.13</v>
+        <v>-7.25</v>
       </c>
       <c r="L80" t="n">
-        <v>375.72</v>
+        <v>180.13</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>559.04</v>
+        <v>268.01</v>
       </c>
       <c r="K81" t="n">
-        <v>-334.4</v>
+        <v>-160.31</v>
       </c>
       <c r="L81" t="n">
-        <v>651.42</v>
+        <v>312.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-20.46</v>
+        <v>-9.81</v>
       </c>
       <c r="K82" t="n">
-        <v>296.23</v>
+        <v>141.93</v>
       </c>
       <c r="L82" t="n">
-        <v>296.93</v>
+        <v>142.27</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-20.08</v>
+        <v>-9.59</v>
       </c>
       <c r="K83" t="n">
-        <v>-447.78</v>
+        <v>-213.91</v>
       </c>
       <c r="L83" t="n">
-        <v>448.23</v>
+        <v>214.12</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-684.47</v>
+        <v>-320.41</v>
       </c>
       <c r="K84" t="n">
-        <v>-433.64</v>
+        <v>-202.99</v>
       </c>
       <c r="L84" t="n">
-        <v>810.27</v>
+        <v>379.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>581.64</v>
+        <v>276.51</v>
       </c>
       <c r="K85" t="n">
-        <v>139.77</v>
+        <v>66.45</v>
       </c>
       <c r="L85" t="n">
-        <v>598.2</v>
+        <v>284.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-332.63</v>
+        <v>-185.83</v>
       </c>
       <c r="K86" t="n">
-        <v>577.26</v>
+        <v>322.49</v>
       </c>
       <c r="L86" t="n">
-        <v>666.24</v>
+        <v>372.19</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>351.04</v>
+        <v>194.79</v>
       </c>
       <c r="K87" t="n">
-        <v>197.72</v>
+        <v>109.71</v>
       </c>
       <c r="L87" t="n">
-        <v>402.9</v>
+        <v>223.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-345.87</v>
+        <v>-192.21</v>
       </c>
       <c r="K88" t="n">
-        <v>469.82</v>
+        <v>261.1</v>
       </c>
       <c r="L88" t="n">
-        <v>583.4</v>
+        <v>324.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>43.08</v>
+        <v>39.06</v>
       </c>
       <c r="K14" t="n">
-        <v>-43.35</v>
+        <v>-39.3</v>
       </c>
       <c r="L14" t="n">
-        <v>61.12</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.779999999999999</v>
+        <v>-7.53</v>
       </c>
       <c r="K15" t="n">
-        <v>-69.86</v>
+        <v>-59.93</v>
       </c>
       <c r="L15" t="n">
-        <v>70.41</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>10.23</v>
+        <v>8.49</v>
       </c>
       <c r="K16" t="n">
-        <v>63.34</v>
+        <v>52.59</v>
       </c>
       <c r="L16" t="n">
-        <v>64.16</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>75.44</v>
+        <v>69.3</v>
       </c>
       <c r="K17" t="n">
-        <v>68.58</v>
+        <v>63.01</v>
       </c>
       <c r="L17" t="n">
-        <v>101.95</v>
+        <v>93.66</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-88.58</v>
+        <v>-76.88</v>
       </c>
       <c r="K18" t="n">
-        <v>50.91</v>
+        <v>44.18</v>
       </c>
       <c r="L18" t="n">
-        <v>102.17</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>62.19</v>
+        <v>62.14</v>
       </c>
       <c r="K19" t="n">
-        <v>17.26</v>
+        <v>17.25</v>
       </c>
       <c r="L19" t="n">
-        <v>64.54000000000001</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-189.01</v>
+        <v>-176.4</v>
       </c>
       <c r="K20" t="n">
-        <v>140.39</v>
+        <v>131.03</v>
       </c>
       <c r="L20" t="n">
-        <v>235.45</v>
+        <v>219.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>103.52</v>
+        <v>99.42</v>
       </c>
       <c r="K21" t="n">
-        <v>-119.97</v>
+        <v>-115.22</v>
       </c>
       <c r="L21" t="n">
-        <v>158.46</v>
+        <v>152.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-71.19</v>
+        <v>-73.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-70.68000000000001</v>
+        <v>-73.06</v>
       </c>
       <c r="L22" t="n">
-        <v>100.32</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>9.23</v>
+        <v>10.41</v>
       </c>
       <c r="K23" t="n">
-        <v>-132.53</v>
+        <v>-149.52</v>
       </c>
       <c r="L23" t="n">
-        <v>132.85</v>
+        <v>149.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-71.84</v>
+        <v>-73.03</v>
       </c>
       <c r="K24" t="n">
-        <v>153.49</v>
+        <v>156.02</v>
       </c>
       <c r="L24" t="n">
-        <v>169.48</v>
+        <v>172.26</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>140.4</v>
+        <v>153.3</v>
       </c>
       <c r="K25" t="n">
-        <v>97.3</v>
+        <v>106.24</v>
       </c>
       <c r="L25" t="n">
-        <v>170.81</v>
+        <v>186.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>229.5</v>
+        <v>275.17</v>
       </c>
       <c r="K26" t="n">
-        <v>-50.65</v>
+        <v>-60.73</v>
       </c>
       <c r="L26" t="n">
-        <v>235.03</v>
+        <v>281.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-91.18000000000001</v>
+        <v>-110.02</v>
       </c>
       <c r="K27" t="n">
-        <v>-124.04</v>
+        <v>-149.68</v>
       </c>
       <c r="L27" t="n">
-        <v>153.95</v>
+        <v>185.77</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>94.45999999999999</v>
+        <v>113.25</v>
       </c>
       <c r="K28" t="n">
-        <v>218.74</v>
+        <v>262.25</v>
       </c>
       <c r="L28" t="n">
-        <v>238.27</v>
+        <v>285.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>42.47</v>
+        <v>39.25</v>
       </c>
       <c r="K29" t="n">
-        <v>-62.14</v>
+        <v>-57.43</v>
       </c>
       <c r="L29" t="n">
-        <v>75.27</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.38</v>
+        <v>-5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>20.24</v>
+        <v>17.44</v>
       </c>
       <c r="L30" t="n">
-        <v>21.22</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.84</v>
+        <v>-3.92</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.5</v>
+        <v>-1.21</v>
       </c>
       <c r="L31" t="n">
-        <v>5.06</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.99</v>
+        <v>-41.24</v>
       </c>
       <c r="K32" t="n">
-        <v>-99.38</v>
+        <v>-83.66</v>
       </c>
       <c r="L32" t="n">
-        <v>110.8</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.58</v>
+        <v>-17.36</v>
       </c>
       <c r="K33" t="n">
-        <v>66.81999999999999</v>
+        <v>66.02</v>
       </c>
       <c r="L33" t="n">
-        <v>69.09999999999999</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.39</v>
+        <v>-1.25</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.66</v>
+        <v>-69.70999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>77.67</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>59.1</v>
+        <v>58.34</v>
       </c>
       <c r="K35" t="n">
-        <v>-109.48</v>
+        <v>-108.07</v>
       </c>
       <c r="L35" t="n">
-        <v>124.41</v>
+        <v>122.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-165.99</v>
+        <v>-159.99</v>
       </c>
       <c r="K36" t="n">
-        <v>45.25</v>
+        <v>43.61</v>
       </c>
       <c r="L36" t="n">
-        <v>172.04</v>
+        <v>165.82</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-274.84</v>
+        <v>-253.29</v>
       </c>
       <c r="K37" t="n">
-        <v>91.43000000000001</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>289.65</v>
+        <v>266.94</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-12.52</v>
+        <v>-13.59</v>
       </c>
       <c r="K38" t="n">
-        <v>203.72</v>
+        <v>221.08</v>
       </c>
       <c r="L38" t="n">
-        <v>204.11</v>
+        <v>221.5</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-25.78</v>
+        <v>-28.92</v>
       </c>
       <c r="K39" t="n">
-        <v>-133.62</v>
+        <v>-149.92</v>
       </c>
       <c r="L39" t="n">
-        <v>136.08</v>
+        <v>152.69</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-190.99</v>
+        <v>-202.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-49.35</v>
+        <v>-52.23</v>
       </c>
       <c r="L40" t="n">
-        <v>197.27</v>
+        <v>208.79</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>223.53</v>
+        <v>256.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-187.05</v>
+        <v>-214.9</v>
       </c>
       <c r="L41" t="n">
-        <v>291.47</v>
+        <v>334.85</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-181.45</v>
+        <v>-226.46</v>
       </c>
       <c r="K42" t="n">
-        <v>134.93</v>
+        <v>168.4</v>
       </c>
       <c r="L42" t="n">
-        <v>226.12</v>
+        <v>282.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>281.44</v>
+        <v>331.74</v>
       </c>
       <c r="K43" t="n">
-        <v>-27.6</v>
+        <v>-32.53</v>
       </c>
       <c r="L43" t="n">
-        <v>282.79</v>
+        <v>333.33</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>25.1</v>
+        <v>20.59</v>
       </c>
       <c r="K44" t="n">
-        <v>-72.03</v>
+        <v>-59.08</v>
       </c>
       <c r="L44" t="n">
-        <v>76.28</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>25.51</v>
+        <v>20.43</v>
       </c>
       <c r="K45" t="n">
-        <v>79.12</v>
+        <v>63.35</v>
       </c>
       <c r="L45" t="n">
-        <v>83.13</v>
+        <v>66.56999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-72.02</v>
+        <v>-55.59</v>
       </c>
       <c r="K46" t="n">
-        <v>77.98999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="L46" t="n">
-        <v>106.16</v>
+        <v>81.94</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>112.3</v>
+        <v>93.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.34999999999999</v>
+        <v>-61.63</v>
       </c>
       <c r="L47" t="n">
-        <v>134.68</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-30.06</v>
+        <v>-25.34</v>
       </c>
       <c r="K48" t="n">
-        <v>106.9</v>
+        <v>90.12</v>
       </c>
       <c r="L48" t="n">
-        <v>111.04</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>79.01000000000001</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-28.36</v>
+        <v>-24.86</v>
       </c>
       <c r="L49" t="n">
-        <v>83.94</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>211.92</v>
+        <v>200.16</v>
       </c>
       <c r="K50" t="n">
-        <v>-25.9</v>
+        <v>-24.46</v>
       </c>
       <c r="L50" t="n">
-        <v>213.5</v>
+        <v>201.65</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-138.46</v>
+        <v>-134.04</v>
       </c>
       <c r="K51" t="n">
-        <v>-93.56</v>
+        <v>-90.56</v>
       </c>
       <c r="L51" t="n">
-        <v>167.11</v>
+        <v>161.76</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>130.03</v>
+        <v>131.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.56</v>
+        <v>-21.78</v>
       </c>
       <c r="L52" t="n">
-        <v>131.8</v>
+        <v>133.14</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-184.02</v>
+        <v>-196.9</v>
       </c>
       <c r="K53" t="n">
-        <v>155.23</v>
+        <v>166.09</v>
       </c>
       <c r="L53" t="n">
-        <v>240.75</v>
+        <v>257.59</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-131.01</v>
+        <v>-150.93</v>
       </c>
       <c r="K54" t="n">
-        <v>114.78</v>
+        <v>132.23</v>
       </c>
       <c r="L54" t="n">
-        <v>174.18</v>
+        <v>200.67</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>235.06</v>
+        <v>245.29</v>
       </c>
       <c r="K55" t="n">
-        <v>141.04</v>
+        <v>147.18</v>
       </c>
       <c r="L55" t="n">
-        <v>274.12</v>
+        <v>286.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>36.43</v>
+        <v>44.09</v>
       </c>
       <c r="K56" t="n">
-        <v>-150.35</v>
+        <v>-181.97</v>
       </c>
       <c r="L56" t="n">
-        <v>154.7</v>
+        <v>187.24</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-31.75</v>
+        <v>-36.15</v>
       </c>
       <c r="K57" t="n">
-        <v>350.34</v>
+        <v>398.89</v>
       </c>
       <c r="L57" t="n">
-        <v>351.77</v>
+        <v>400.53</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-394.13</v>
+        <v>-470.32</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.51</v>
+        <v>-186.76</v>
       </c>
       <c r="L58" t="n">
-        <v>424.07</v>
+        <v>506.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>121.76</v>
+        <v>92.28</v>
       </c>
       <c r="K59" t="n">
-        <v>65.06999999999999</v>
+        <v>49.31</v>
       </c>
       <c r="L59" t="n">
-        <v>138.05</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>29.97</v>
+        <v>26.74</v>
       </c>
       <c r="K60" t="n">
-        <v>68.78</v>
+        <v>61.37</v>
       </c>
       <c r="L60" t="n">
-        <v>75.03</v>
+        <v>66.95</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>73.79000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>13.83</v>
+        <v>12.65</v>
       </c>
       <c r="L61" t="n">
-        <v>75.06999999999999</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>37.06</v>
+        <v>31.37</v>
       </c>
       <c r="K62" t="n">
-        <v>-105.42</v>
+        <v>-89.23</v>
       </c>
       <c r="L62" t="n">
-        <v>111.75</v>
+        <v>94.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-83.53</v>
+        <v>-68.36</v>
       </c>
       <c r="K63" t="n">
-        <v>121.17</v>
+        <v>99.17</v>
       </c>
       <c r="L63" t="n">
-        <v>147.18</v>
+        <v>120.45</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-159.17</v>
+        <v>-127.84</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.23</v>
+        <v>-0.99</v>
       </c>
       <c r="L64" t="n">
-        <v>159.18</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-149.2</v>
+        <v>-141.39</v>
       </c>
       <c r="K65" t="n">
-        <v>125.55</v>
+        <v>118.98</v>
       </c>
       <c r="L65" t="n">
-        <v>194.99</v>
+        <v>184.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>108.89</v>
+        <v>106.87</v>
       </c>
       <c r="K66" t="n">
-        <v>90.18000000000001</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>141.39</v>
+        <v>138.76</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>111.09</v>
+        <v>107.57</v>
       </c>
       <c r="K67" t="n">
-        <v>-115.78</v>
+        <v>-112.12</v>
       </c>
       <c r="L67" t="n">
-        <v>160.45</v>
+        <v>155.38</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-180.99</v>
+        <v>-194.65</v>
       </c>
       <c r="K68" t="n">
-        <v>-55.16</v>
+        <v>-59.33</v>
       </c>
       <c r="L68" t="n">
-        <v>189.21</v>
+        <v>203.49</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-400.09</v>
+        <v>-404.77</v>
       </c>
       <c r="K69" t="n">
-        <v>-136.29</v>
+        <v>-137.89</v>
       </c>
       <c r="L69" t="n">
-        <v>422.67</v>
+        <v>427.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>135.02</v>
+        <v>143.42</v>
       </c>
       <c r="K70" t="n">
-        <v>251.38</v>
+        <v>267.02</v>
       </c>
       <c r="L70" t="n">
-        <v>285.34</v>
+        <v>303.1</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>353.61</v>
+        <v>422.06</v>
       </c>
       <c r="K71" t="n">
-        <v>-87.48</v>
+        <v>-104.41</v>
       </c>
       <c r="L71" t="n">
-        <v>364.27</v>
+        <v>434.78</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-379.27</v>
+        <v>-453.39</v>
       </c>
       <c r="K72" t="n">
-        <v>9.449999999999999</v>
+        <v>11.29</v>
       </c>
       <c r="L72" t="n">
-        <v>379.39</v>
+        <v>453.53</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>284.42</v>
+        <v>352.38</v>
       </c>
       <c r="K73" t="n">
-        <v>51.52</v>
+        <v>63.83</v>
       </c>
       <c r="L73" t="n">
-        <v>289.04</v>
+        <v>358.11</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-146.25</v>
+        <v>-107.52</v>
       </c>
       <c r="K74" t="n">
-        <v>15.52</v>
+        <v>11.41</v>
       </c>
       <c r="L74" t="n">
-        <v>147.07</v>
+        <v>108.13</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>76.47</v>
+        <v>61.42</v>
       </c>
       <c r="K75" t="n">
-        <v>22.95</v>
+        <v>18.43</v>
       </c>
       <c r="L75" t="n">
-        <v>79.84</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-73.68000000000001</v>
+        <v>-54.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-114.71</v>
+        <v>-84.81999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>136.33</v>
+        <v>100.82</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-122.86</v>
+        <v>-101.13</v>
       </c>
       <c r="K77" t="n">
-        <v>-59.21</v>
+        <v>-48.74</v>
       </c>
       <c r="L77" t="n">
-        <v>136.38</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-86.98999999999999</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-61.18</v>
+        <v>-51.41</v>
       </c>
       <c r="L78" t="n">
-        <v>106.36</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-81.42</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>5.78</v>
+        <v>5.08</v>
       </c>
       <c r="L79" t="n">
-        <v>81.62</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>179.98</v>
+        <v>175.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.25</v>
+        <v>-7.06</v>
       </c>
       <c r="L80" t="n">
-        <v>180.13</v>
+        <v>175.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>268.01</v>
+        <v>246.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-160.31</v>
+        <v>-147.46</v>
       </c>
       <c r="L81" t="n">
-        <v>312.3</v>
+        <v>287.25</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-9.81</v>
+        <v>-9.68</v>
       </c>
       <c r="K82" t="n">
-        <v>141.93</v>
+        <v>140.06</v>
       </c>
       <c r="L82" t="n">
-        <v>142.27</v>
+        <v>140.39</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-9.59</v>
+        <v>-10.74</v>
       </c>
       <c r="K83" t="n">
-        <v>-213.91</v>
+        <v>-239.48</v>
       </c>
       <c r="L83" t="n">
-        <v>214.12</v>
+        <v>239.72</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-320.41</v>
+        <v>-328.65</v>
       </c>
       <c r="K84" t="n">
-        <v>-202.99</v>
+        <v>-208.22</v>
       </c>
       <c r="L84" t="n">
-        <v>379.3</v>
+        <v>389.06</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>276.51</v>
+        <v>294.29</v>
       </c>
       <c r="K85" t="n">
-        <v>66.45</v>
+        <v>70.72</v>
       </c>
       <c r="L85" t="n">
-        <v>284.38</v>
+        <v>302.67</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-185.83</v>
+        <v>-224.83</v>
       </c>
       <c r="K86" t="n">
-        <v>322.49</v>
+        <v>390.18</v>
       </c>
       <c r="L86" t="n">
-        <v>372.19</v>
+        <v>450.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>194.79</v>
+        <v>251.35</v>
       </c>
       <c r="K87" t="n">
-        <v>109.71</v>
+        <v>141.57</v>
       </c>
       <c r="L87" t="n">
-        <v>223.56</v>
+        <v>288.48</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-192.21</v>
+        <v>-233.39</v>
       </c>
       <c r="K88" t="n">
-        <v>261.1</v>
+        <v>317.04</v>
       </c>
       <c r="L88" t="n">
-        <v>324.22</v>
+        <v>393.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>39.06</v>
+        <v>40.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-39.3</v>
+        <v>-40.79</v>
       </c>
       <c r="L14" t="n">
-        <v>55.41</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.53</v>
+        <v>-7.63</v>
       </c>
       <c r="K15" t="n">
-        <v>-59.93</v>
+        <v>-60.73</v>
       </c>
       <c r="L15" t="n">
-        <v>60.41</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>8.49</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>52.59</v>
+        <v>54.43</v>
       </c>
       <c r="L16" t="n">
-        <v>53.27</v>
+        <v>55.13</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>69.3</v>
+        <v>68</v>
       </c>
       <c r="K17" t="n">
-        <v>63.01</v>
+        <v>61.82</v>
       </c>
       <c r="L17" t="n">
-        <v>93.66</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-76.88</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>44.18</v>
+        <v>43.33</v>
       </c>
       <c r="L18" t="n">
-        <v>88.67</v>
+        <v>86.97</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>62.14</v>
+        <v>64.28</v>
       </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>17.84</v>
       </c>
       <c r="L19" t="n">
-        <v>64.48999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-176.4</v>
+        <v>-167.26</v>
       </c>
       <c r="K20" t="n">
-        <v>131.03</v>
+        <v>124.24</v>
       </c>
       <c r="L20" t="n">
-        <v>219.73</v>
+        <v>208.35</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>99.42</v>
+        <v>97.12</v>
       </c>
       <c r="K21" t="n">
-        <v>-115.22</v>
+        <v>-112.56</v>
       </c>
       <c r="L21" t="n">
-        <v>152.19</v>
+        <v>148.67</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-73.59</v>
+        <v>-78.25</v>
       </c>
       <c r="K22" t="n">
-        <v>-73.06</v>
+        <v>-77.69</v>
       </c>
       <c r="L22" t="n">
-        <v>103.7</v>
+        <v>110.27</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>10.41</v>
+        <v>11.1</v>
       </c>
       <c r="K23" t="n">
-        <v>-149.52</v>
+        <v>-159.44</v>
       </c>
       <c r="L23" t="n">
-        <v>149.88</v>
+        <v>159.83</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-73.03</v>
+        <v>-72.56999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>156.02</v>
+        <v>155.04</v>
       </c>
       <c r="L24" t="n">
-        <v>172.26</v>
+        <v>171.18</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>153.3</v>
+        <v>157.53</v>
       </c>
       <c r="K25" t="n">
-        <v>106.24</v>
+        <v>109.17</v>
       </c>
       <c r="L25" t="n">
-        <v>186.51</v>
+        <v>191.66</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>275.17</v>
+        <v>288.78</v>
       </c>
       <c r="K26" t="n">
-        <v>-60.73</v>
+        <v>-63.74</v>
       </c>
       <c r="L26" t="n">
-        <v>281.79</v>
+        <v>295.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-110.02</v>
+        <v>-119.31</v>
       </c>
       <c r="K27" t="n">
-        <v>-149.68</v>
+        <v>-162.32</v>
       </c>
       <c r="L27" t="n">
-        <v>185.77</v>
+        <v>201.45</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>113.25</v>
+        <v>118.71</v>
       </c>
       <c r="K28" t="n">
-        <v>262.25</v>
+        <v>274.89</v>
       </c>
       <c r="L28" t="n">
-        <v>285.65</v>
+        <v>299.42</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>39.25</v>
+        <v>39.35</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.43</v>
+        <v>-57.57</v>
       </c>
       <c r="L29" t="n">
-        <v>69.56</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.5</v>
+        <v>-5.93</v>
       </c>
       <c r="K30" t="n">
-        <v>17.44</v>
+        <v>18.81</v>
       </c>
       <c r="L30" t="n">
-        <v>18.29</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.92</v>
+        <v>-4.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.21</v>
+        <v>-1.26</v>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-41.24</v>
+        <v>-40.12</v>
       </c>
       <c r="K32" t="n">
-        <v>-83.66</v>
+        <v>-81.37</v>
       </c>
       <c r="L32" t="n">
-        <v>93.27</v>
+        <v>90.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.36</v>
+        <v>-17.91</v>
       </c>
       <c r="K33" t="n">
-        <v>66.02</v>
+        <v>68.08</v>
       </c>
       <c r="L33" t="n">
-        <v>68.27</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.25</v>
+        <v>-1.32</v>
       </c>
       <c r="K34" t="n">
-        <v>-69.70999999999999</v>
+        <v>-73.58</v>
       </c>
       <c r="L34" t="n">
-        <v>69.72</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>58.34</v>
+        <v>58.85</v>
       </c>
       <c r="K35" t="n">
-        <v>-108.07</v>
+        <v>-109.02</v>
       </c>
       <c r="L35" t="n">
-        <v>122.81</v>
+        <v>123.89</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-159.99</v>
+        <v>-157.52</v>
       </c>
       <c r="K36" t="n">
-        <v>43.61</v>
+        <v>42.94</v>
       </c>
       <c r="L36" t="n">
-        <v>165.82</v>
+        <v>163.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-253.29</v>
+        <v>-236.78</v>
       </c>
       <c r="K37" t="n">
-        <v>84.26000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="L37" t="n">
-        <v>266.94</v>
+        <v>249.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.59</v>
+        <v>-13.76</v>
       </c>
       <c r="K38" t="n">
-        <v>221.08</v>
+        <v>223.94</v>
       </c>
       <c r="L38" t="n">
-        <v>221.5</v>
+        <v>224.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-28.92</v>
+        <v>-30.63</v>
       </c>
       <c r="K39" t="n">
-        <v>-149.92</v>
+        <v>-158.77</v>
       </c>
       <c r="L39" t="n">
-        <v>152.69</v>
+        <v>161.7</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-202.15</v>
+        <v>-201.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-52.23</v>
+        <v>-52.1</v>
       </c>
       <c r="L40" t="n">
-        <v>208.79</v>
+        <v>208.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>256.8</v>
+        <v>258.22</v>
       </c>
       <c r="K41" t="n">
-        <v>-214.9</v>
+        <v>-216.08</v>
       </c>
       <c r="L41" t="n">
-        <v>334.85</v>
+        <v>336.7</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-226.46</v>
+        <v>-243.69</v>
       </c>
       <c r="K42" t="n">
-        <v>168.4</v>
+        <v>181.22</v>
       </c>
       <c r="L42" t="n">
-        <v>282.21</v>
+        <v>303.68</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>331.74</v>
+        <v>340.17</v>
       </c>
       <c r="K43" t="n">
-        <v>-32.53</v>
+        <v>-33.36</v>
       </c>
       <c r="L43" t="n">
-        <v>333.33</v>
+        <v>341.81</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>20.59</v>
+        <v>20.78</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.08</v>
+        <v>-59.64</v>
       </c>
       <c r="L44" t="n">
-        <v>62.56</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>20.43</v>
+        <v>20.48</v>
       </c>
       <c r="K45" t="n">
-        <v>63.35</v>
+        <v>63.51</v>
       </c>
       <c r="L45" t="n">
-        <v>66.56999999999999</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-55.59</v>
+        <v>-54.51</v>
       </c>
       <c r="K46" t="n">
-        <v>60.2</v>
+        <v>59.02</v>
       </c>
       <c r="L46" t="n">
-        <v>81.94</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>93.08</v>
+        <v>88.86</v>
       </c>
       <c r="K47" t="n">
-        <v>-61.63</v>
+        <v>-58.83</v>
       </c>
       <c r="L47" t="n">
-        <v>111.63</v>
+        <v>106.57</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.34</v>
+        <v>-25.18</v>
       </c>
       <c r="K48" t="n">
-        <v>90.12</v>
+        <v>89.55</v>
       </c>
       <c r="L48" t="n">
-        <v>93.61</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>69.26000000000001</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-24.86</v>
+        <v>-25.41</v>
       </c>
       <c r="L49" t="n">
-        <v>73.59</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>200.16</v>
+        <v>192.67</v>
       </c>
       <c r="K50" t="n">
-        <v>-24.46</v>
+        <v>-23.55</v>
       </c>
       <c r="L50" t="n">
-        <v>201.65</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-134.04</v>
+        <v>-132.48</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.56</v>
+        <v>-89.51000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>161.76</v>
+        <v>159.88</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>131.34</v>
+        <v>137.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.78</v>
+        <v>-22.71</v>
       </c>
       <c r="L52" t="n">
-        <v>133.14</v>
+        <v>138.88</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-196.9</v>
+        <v>-195.68</v>
       </c>
       <c r="K53" t="n">
-        <v>166.09</v>
+        <v>165.06</v>
       </c>
       <c r="L53" t="n">
-        <v>257.59</v>
+        <v>255.99</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-150.93</v>
+        <v>-161.5</v>
       </c>
       <c r="K54" t="n">
-        <v>132.23</v>
+        <v>141.49</v>
       </c>
       <c r="L54" t="n">
-        <v>200.67</v>
+        <v>214.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>245.29</v>
+        <v>238.21</v>
       </c>
       <c r="K55" t="n">
-        <v>147.18</v>
+        <v>142.93</v>
       </c>
       <c r="L55" t="n">
-        <v>286.06</v>
+        <v>277.8</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>44.09</v>
+        <v>47.83</v>
       </c>
       <c r="K56" t="n">
-        <v>-181.97</v>
+        <v>-197.39</v>
       </c>
       <c r="L56" t="n">
-        <v>187.24</v>
+        <v>203.1</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-36.15</v>
+        <v>-35.63</v>
       </c>
       <c r="K57" t="n">
-        <v>398.89</v>
+        <v>393.21</v>
       </c>
       <c r="L57" t="n">
-        <v>400.53</v>
+        <v>394.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-470.32</v>
+        <v>-469.77</v>
       </c>
       <c r="K58" t="n">
-        <v>-186.76</v>
+        <v>-186.54</v>
       </c>
       <c r="L58" t="n">
-        <v>506.05</v>
+        <v>505.45</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>92.28</v>
+        <v>86.61</v>
       </c>
       <c r="K59" t="n">
-        <v>49.31</v>
+        <v>46.29</v>
       </c>
       <c r="L59" t="n">
-        <v>104.63</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>26.74</v>
+        <v>26.83</v>
       </c>
       <c r="K60" t="n">
-        <v>61.37</v>
+        <v>61.56</v>
       </c>
       <c r="L60" t="n">
-        <v>66.95</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>67.48999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>12.65</v>
+        <v>12.85</v>
       </c>
       <c r="L61" t="n">
-        <v>68.67</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>31.37</v>
+        <v>31.4</v>
       </c>
       <c r="K62" t="n">
-        <v>-89.23</v>
+        <v>-89.31</v>
       </c>
       <c r="L62" t="n">
-        <v>94.58</v>
+        <v>94.66</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-68.36</v>
+        <v>-64.72</v>
       </c>
       <c r="K63" t="n">
-        <v>99.17</v>
+        <v>93.89</v>
       </c>
       <c r="L63" t="n">
-        <v>120.45</v>
+        <v>114.04</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-127.84</v>
+        <v>-122.05</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.99</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>127.85</v>
+        <v>122.05</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-141.39</v>
+        <v>-137.05</v>
       </c>
       <c r="K65" t="n">
-        <v>118.98</v>
+        <v>115.33</v>
       </c>
       <c r="L65" t="n">
-        <v>184.79</v>
+        <v>179.12</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>106.87</v>
+        <v>107.41</v>
       </c>
       <c r="K66" t="n">
-        <v>88.51000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="L66" t="n">
-        <v>138.76</v>
+        <v>139.46</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>107.57</v>
+        <v>106.79</v>
       </c>
       <c r="K67" t="n">
-        <v>-112.12</v>
+        <v>-111.3</v>
       </c>
       <c r="L67" t="n">
-        <v>155.38</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-194.65</v>
+        <v>-197.31</v>
       </c>
       <c r="K68" t="n">
-        <v>-59.33</v>
+        <v>-60.14</v>
       </c>
       <c r="L68" t="n">
-        <v>203.49</v>
+        <v>206.27</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-404.77</v>
+        <v>-376.73</v>
       </c>
       <c r="K69" t="n">
-        <v>-137.89</v>
+        <v>-128.33</v>
       </c>
       <c r="L69" t="n">
-        <v>427.62</v>
+        <v>397.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>143.42</v>
+        <v>140.66</v>
       </c>
       <c r="K70" t="n">
-        <v>267.02</v>
+        <v>261.88</v>
       </c>
       <c r="L70" t="n">
-        <v>303.1</v>
+        <v>297.27</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>422.06</v>
+        <v>428.59</v>
       </c>
       <c r="K71" t="n">
-        <v>-104.41</v>
+        <v>-106.03</v>
       </c>
       <c r="L71" t="n">
-        <v>434.78</v>
+        <v>441.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-453.39</v>
+        <v>-458.22</v>
       </c>
       <c r="K72" t="n">
-        <v>11.29</v>
+        <v>11.41</v>
       </c>
       <c r="L72" t="n">
-        <v>453.53</v>
+        <v>458.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>352.38</v>
+        <v>368.95</v>
       </c>
       <c r="K73" t="n">
-        <v>63.83</v>
+        <v>66.83</v>
       </c>
       <c r="L73" t="n">
-        <v>358.11</v>
+        <v>374.95</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-107.52</v>
+        <v>-100.94</v>
       </c>
       <c r="K74" t="n">
-        <v>11.41</v>
+        <v>10.71</v>
       </c>
       <c r="L74" t="n">
-        <v>108.13</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="75">
@@ -3208,7 +3208,7 @@
         <v>18.43</v>
       </c>
       <c r="L75" t="n">
-        <v>64.12</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-54.48</v>
+        <v>-51.79</v>
       </c>
       <c r="K76" t="n">
-        <v>-84.81999999999999</v>
+        <v>-80.64</v>
       </c>
       <c r="L76" t="n">
-        <v>100.82</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-101.13</v>
+        <v>-98.05</v>
       </c>
       <c r="K77" t="n">
-        <v>-48.74</v>
+        <v>-47.26</v>
       </c>
       <c r="L77" t="n">
-        <v>112.27</v>
+        <v>108.85</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-73.09999999999999</v>
+        <v>-72.45</v>
       </c>
       <c r="K78" t="n">
-        <v>-51.41</v>
+        <v>-50.96</v>
       </c>
       <c r="L78" t="n">
-        <v>89.37</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-71.54000000000001</v>
+        <v>-74.51000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>5.08</v>
+        <v>5.29</v>
       </c>
       <c r="L79" t="n">
-        <v>71.72</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>175.17</v>
+        <v>175.96</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.06</v>
+        <v>-7.09</v>
       </c>
       <c r="L80" t="n">
-        <v>175.31</v>
+        <v>176.1</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>246.52</v>
+        <v>231.41</v>
       </c>
       <c r="K81" t="n">
-        <v>-147.46</v>
+        <v>-138.42</v>
       </c>
       <c r="L81" t="n">
-        <v>287.25</v>
+        <v>269.65</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-9.68</v>
+        <v>-9.85</v>
       </c>
       <c r="K82" t="n">
-        <v>140.06</v>
+        <v>142.6</v>
       </c>
       <c r="L82" t="n">
-        <v>140.39</v>
+        <v>142.94</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-10.74</v>
+        <v>-11.13</v>
       </c>
       <c r="K83" t="n">
-        <v>-239.48</v>
+        <v>-248.15</v>
       </c>
       <c r="L83" t="n">
-        <v>239.72</v>
+        <v>248.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-328.65</v>
+        <v>-309.15</v>
       </c>
       <c r="K84" t="n">
-        <v>-208.22</v>
+        <v>-195.86</v>
       </c>
       <c r="L84" t="n">
-        <v>389.06</v>
+        <v>365.98</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>294.29</v>
+        <v>288.26</v>
       </c>
       <c r="K85" t="n">
-        <v>70.72</v>
+        <v>69.27</v>
       </c>
       <c r="L85" t="n">
-        <v>302.67</v>
+        <v>296.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-224.83</v>
+        <v>-227.67</v>
       </c>
       <c r="K86" t="n">
-        <v>390.18</v>
+        <v>395.1</v>
       </c>
       <c r="L86" t="n">
-        <v>450.32</v>
+        <v>456</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>251.35</v>
+        <v>274.95</v>
       </c>
       <c r="K87" t="n">
-        <v>141.57</v>
+        <v>154.86</v>
       </c>
       <c r="L87" t="n">
-        <v>288.48</v>
+        <v>315.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-233.39</v>
+        <v>-238.92</v>
       </c>
       <c r="K88" t="n">
-        <v>317.04</v>
+        <v>324.55</v>
       </c>
       <c r="L88" t="n">
-        <v>393.68</v>
+        <v>403.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -628,25 +628,25 @@
         <v>5.2</v>
       </c>
       <c r="F14" t="n">
-        <v>15.19</v>
+        <v>12.79</v>
       </c>
       <c r="G14" t="n">
-        <v>333.9</v>
+        <v>326.6</v>
       </c>
       <c r="H14" t="n">
-        <v>76.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I14" t="n">
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>40.53</v>
+        <v>45.44</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.79</v>
+        <v>-45.6</v>
       </c>
       <c r="L14" t="n">
-        <v>57.5</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>5.38</v>
       </c>
       <c r="F15" t="n">
-        <v>15.08</v>
+        <v>11.82</v>
       </c>
       <c r="G15" t="n">
-        <v>324.9</v>
+        <v>324.3</v>
       </c>
       <c r="H15" t="n">
-        <v>71.3</v>
+        <v>76.3</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.63</v>
+        <v>-10.26</v>
       </c>
       <c r="K15" t="n">
-        <v>-60.73</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>61.2</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>5.92</v>
       </c>
       <c r="F16" t="n">
-        <v>15.1</v>
+        <v>14.46</v>
       </c>
       <c r="G16" t="n">
-        <v>326.5</v>
+        <v>324.7</v>
       </c>
       <c r="H16" t="n">
-        <v>76.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>8.789999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="K16" t="n">
-        <v>54.43</v>
+        <v>61.47</v>
       </c>
       <c r="L16" t="n">
-        <v>55.13</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>4.9</v>
       </c>
       <c r="F17" t="n">
-        <v>15.56</v>
+        <v>11.9</v>
       </c>
       <c r="G17" t="n">
-        <v>319</v>
+        <v>334.1</v>
       </c>
       <c r="H17" t="n">
-        <v>72.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="I17" t="n">
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>68</v>
+        <v>71.89</v>
       </c>
       <c r="K17" t="n">
-        <v>61.82</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>91.91</v>
+        <v>100.66</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>5.23</v>
       </c>
       <c r="F18" t="n">
-        <v>14.73</v>
+        <v>13.35</v>
       </c>
       <c r="G18" t="n">
-        <v>340.4</v>
+        <v>317.5</v>
       </c>
       <c r="H18" t="n">
-        <v>77.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I18" t="n">
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-75.40000000000001</v>
+        <v>-85.16</v>
       </c>
       <c r="K18" t="n">
-        <v>43.33</v>
+        <v>48.77</v>
       </c>
       <c r="L18" t="n">
-        <v>86.97</v>
+        <v>98.13</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>4.38</v>
       </c>
       <c r="F19" t="n">
-        <v>16.08</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>327.6</v>
+        <v>344.4</v>
       </c>
       <c r="H19" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>64.28</v>
+        <v>69.2</v>
       </c>
       <c r="K19" t="n">
-        <v>17.84</v>
+        <v>24.8</v>
       </c>
       <c r="L19" t="n">
-        <v>66.7</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>5.57</v>
       </c>
       <c r="F20" t="n">
-        <v>14.12</v>
+        <v>15.41</v>
       </c>
       <c r="G20" t="n">
-        <v>316.4</v>
+        <v>305.2</v>
       </c>
       <c r="H20" t="n">
-        <v>80.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-167.26</v>
+        <v>-182.82</v>
       </c>
       <c r="K20" t="n">
-        <v>124.24</v>
+        <v>132.33</v>
       </c>
       <c r="L20" t="n">
-        <v>208.35</v>
+        <v>225.69</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.99</v>
       </c>
       <c r="F21" t="n">
-        <v>15.4</v>
+        <v>16.52</v>
       </c>
       <c r="G21" t="n">
-        <v>323.1</v>
+        <v>330.8</v>
       </c>
       <c r="H21" t="n">
-        <v>76.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>97.12</v>
+        <v>119.12</v>
       </c>
       <c r="K21" t="n">
-        <v>-112.56</v>
+        <v>-128.23</v>
       </c>
       <c r="L21" t="n">
-        <v>148.67</v>
+        <v>175.02</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>5.53</v>
       </c>
       <c r="F22" t="n">
-        <v>14.38</v>
+        <v>12.18</v>
       </c>
       <c r="G22" t="n">
-        <v>325.2</v>
+        <v>310.3</v>
       </c>
       <c r="H22" t="n">
-        <v>72.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-78.25</v>
+        <v>-110.74</v>
       </c>
       <c r="K22" t="n">
-        <v>-77.69</v>
+        <v>-51.81</v>
       </c>
       <c r="L22" t="n">
-        <v>110.27</v>
+        <v>122.26</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>5.22</v>
       </c>
       <c r="F23" t="n">
-        <v>15.01</v>
+        <v>14.68</v>
       </c>
       <c r="G23" t="n">
-        <v>321.7</v>
+        <v>323.1</v>
       </c>
       <c r="H23" t="n">
-        <v>71.8</v>
+        <v>74.7</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>11.1</v>
+        <v>-34.01</v>
       </c>
       <c r="K23" t="n">
-        <v>-159.44</v>
+        <v>-169.94</v>
       </c>
       <c r="L23" t="n">
-        <v>159.83</v>
+        <v>173.31</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>4.61</v>
       </c>
       <c r="F24" t="n">
-        <v>15.06</v>
+        <v>13.83</v>
       </c>
       <c r="G24" t="n">
-        <v>325.2</v>
+        <v>324</v>
       </c>
       <c r="H24" t="n">
-        <v>82.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-72.56999999999999</v>
+        <v>-94.51000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>155.04</v>
+        <v>187.96</v>
       </c>
       <c r="L24" t="n">
-        <v>171.18</v>
+        <v>210.38</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>5.35</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>15.13</v>
       </c>
       <c r="G25" t="n">
-        <v>329.6</v>
+        <v>302.8</v>
       </c>
       <c r="H25" t="n">
-        <v>80</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>157.53</v>
+        <v>139.89</v>
       </c>
       <c r="K25" t="n">
-        <v>109.17</v>
+        <v>149.68</v>
       </c>
       <c r="L25" t="n">
-        <v>191.66</v>
+        <v>204.87</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>5.43</v>
       </c>
       <c r="F26" t="n">
-        <v>15.16</v>
+        <v>13.7</v>
       </c>
       <c r="G26" t="n">
-        <v>334.4</v>
+        <v>326.1</v>
       </c>
       <c r="H26" t="n">
-        <v>76.8</v>
+        <v>81</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>288.78</v>
+        <v>318.3</v>
       </c>
       <c r="K26" t="n">
-        <v>-63.74</v>
+        <v>-31.66</v>
       </c>
       <c r="L26" t="n">
-        <v>295.73</v>
+        <v>319.87</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>4.8</v>
       </c>
       <c r="F27" t="n">
-        <v>15.47</v>
+        <v>12.93</v>
       </c>
       <c r="G27" t="n">
         <v>332.2</v>
       </c>
       <c r="H27" t="n">
-        <v>78.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-119.31</v>
+        <v>-196.52</v>
       </c>
       <c r="K27" t="n">
-        <v>-162.32</v>
+        <v>-130.83</v>
       </c>
       <c r="L27" t="n">
-        <v>201.45</v>
+        <v>236.09</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>5.46</v>
       </c>
       <c r="F28" t="n">
-        <v>14.5</v>
+        <v>13.62</v>
       </c>
       <c r="G28" t="n">
-        <v>347.6</v>
+        <v>312.8</v>
       </c>
       <c r="H28" t="n">
-        <v>76.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>118.71</v>
+        <v>33.52</v>
       </c>
       <c r="K28" t="n">
-        <v>274.89</v>
+        <v>309.25</v>
       </c>
       <c r="L28" t="n">
-        <v>299.42</v>
+        <v>311.06</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>4.94</v>
       </c>
       <c r="F29" t="n">
-        <v>14.53</v>
+        <v>11.54</v>
       </c>
       <c r="G29" t="n">
-        <v>320.5</v>
+        <v>330.1</v>
       </c>
       <c r="H29" t="n">
-        <v>80.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>39.35</v>
+        <v>-47.95</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.57</v>
+        <v>-43.73</v>
       </c>
       <c r="L29" t="n">
-        <v>69.73999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1297,28 +1297,28 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.15</v>
+        <v>4.62</v>
       </c>
       <c r="F30" t="n">
-        <v>15.42</v>
+        <v>12.85</v>
       </c>
       <c r="G30" t="n">
-        <v>330.9</v>
+        <v>324.6</v>
       </c>
       <c r="H30" t="n">
-        <v>69.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.93</v>
+        <v>13.27</v>
       </c>
       <c r="K30" t="n">
-        <v>18.81</v>
+        <v>-82.11</v>
       </c>
       <c r="L30" t="n">
-        <v>19.72</v>
+        <v>83.17</v>
       </c>
     </row>
     <row r="31">
@@ -1339,28 +1339,28 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.54</v>
+        <v>5.66</v>
       </c>
       <c r="F31" t="n">
-        <v>14.67</v>
+        <v>15.28</v>
       </c>
       <c r="G31" t="n">
-        <v>330.3</v>
+        <v>324.6</v>
       </c>
       <c r="H31" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.07</v>
+        <v>4.92</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.26</v>
+        <v>-66.64</v>
       </c>
       <c r="L31" t="n">
-        <v>4.26</v>
+        <v>66.81999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1381,28 +1381,28 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.5</v>
+        <v>6.39</v>
       </c>
       <c r="F32" t="n">
-        <v>15.57</v>
+        <v>16.39</v>
       </c>
       <c r="G32" t="n">
-        <v>327.2</v>
+        <v>314</v>
       </c>
       <c r="H32" t="n">
-        <v>77</v>
+        <v>73.8</v>
       </c>
       <c r="I32" t="n">
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-40.12</v>
+        <v>22</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.37</v>
+        <v>95.58</v>
       </c>
       <c r="L32" t="n">
-        <v>90.72</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="33">
@@ -1423,28 +1423,28 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.72</v>
+        <v>5.03</v>
       </c>
       <c r="F33" t="n">
-        <v>14.74</v>
+        <v>12.42</v>
       </c>
       <c r="G33" t="n">
-        <v>331.1</v>
+        <v>306.7</v>
       </c>
       <c r="H33" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.91</v>
+        <v>23.11</v>
       </c>
       <c r="K33" t="n">
-        <v>68.08</v>
+        <v>-69.63</v>
       </c>
       <c r="L33" t="n">
-        <v>70.39</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="34">
@@ -1465,28 +1465,28 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.89</v>
+        <v>5.23</v>
       </c>
       <c r="F34" t="n">
-        <v>14.89</v>
+        <v>12.42</v>
       </c>
       <c r="G34" t="n">
-        <v>326.8</v>
+        <v>319.1</v>
       </c>
       <c r="H34" t="n">
-        <v>80.3</v>
+        <v>72.5</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.32</v>
+        <v>98.08</v>
       </c>
       <c r="K34" t="n">
-        <v>-73.58</v>
+        <v>12.03</v>
       </c>
       <c r="L34" t="n">
-        <v>73.59999999999999</v>
+        <v>98.81</v>
       </c>
     </row>
     <row r="35">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.04</v>
+        <v>6.58</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>17.36</v>
       </c>
       <c r="G35" t="n">
-        <v>325.2</v>
+        <v>325.4</v>
       </c>
       <c r="H35" t="n">
-        <v>81.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>58.85</v>
+        <v>-129.72</v>
       </c>
       <c r="K35" t="n">
-        <v>-109.02</v>
+        <v>140.49</v>
       </c>
       <c r="L35" t="n">
-        <v>123.89</v>
+        <v>191.22</v>
       </c>
     </row>
     <row r="36">
@@ -1549,28 +1549,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.4</v>
+        <v>5.72</v>
       </c>
       <c r="F36" t="n">
-        <v>15.27</v>
+        <v>14.96</v>
       </c>
       <c r="G36" t="n">
-        <v>321.1</v>
+        <v>320.1</v>
       </c>
       <c r="H36" t="n">
-        <v>73.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-157.52</v>
+        <v>20.62</v>
       </c>
       <c r="K36" t="n">
-        <v>42.94</v>
+        <v>-220.19</v>
       </c>
       <c r="L36" t="n">
-        <v>163.27</v>
+        <v>221.15</v>
       </c>
     </row>
     <row r="37">
@@ -1591,28 +1591,28 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.78</v>
+        <v>5.52</v>
       </c>
       <c r="F37" t="n">
-        <v>15.1</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>304.2</v>
+        <v>313.3</v>
       </c>
       <c r="H37" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-236.78</v>
+        <v>100.89</v>
       </c>
       <c r="K37" t="n">
-        <v>78.77</v>
+        <v>-126.24</v>
       </c>
       <c r="L37" t="n">
-        <v>249.53</v>
+        <v>161.6</v>
       </c>
     </row>
     <row r="38">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.8</v>
+        <v>6.24</v>
       </c>
       <c r="F38" t="n">
-        <v>14.63</v>
+        <v>15.04</v>
       </c>
       <c r="G38" t="n">
-        <v>332.8</v>
+        <v>319.5</v>
       </c>
       <c r="H38" t="n">
-        <v>78.3</v>
+        <v>76</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.76</v>
+        <v>209.83</v>
       </c>
       <c r="K38" t="n">
-        <v>223.94</v>
+        <v>109.34</v>
       </c>
       <c r="L38" t="n">
-        <v>224.36</v>
+        <v>236.61</v>
       </c>
     </row>
     <row r="39">
@@ -1675,28 +1675,28 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.29</v>
+        <v>5.37</v>
       </c>
       <c r="F39" t="n">
-        <v>15.14</v>
+        <v>12.43</v>
       </c>
       <c r="G39" t="n">
-        <v>333.2</v>
+        <v>337.9</v>
       </c>
       <c r="H39" t="n">
-        <v>76.3</v>
+        <v>81</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-30.63</v>
+        <v>80.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-158.77</v>
+        <v>229.55</v>
       </c>
       <c r="L39" t="n">
-        <v>161.7</v>
+        <v>243.28</v>
       </c>
     </row>
     <row r="40">
@@ -1717,28 +1717,28 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.08</v>
+        <v>5.59</v>
       </c>
       <c r="F40" t="n">
-        <v>15.33</v>
+        <v>17.26</v>
       </c>
       <c r="G40" t="n">
-        <v>310.5</v>
+        <v>317.4</v>
       </c>
       <c r="H40" t="n">
         <v>82.8</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-201.62</v>
+        <v>113.69</v>
       </c>
       <c r="K40" t="n">
-        <v>-52.1</v>
+        <v>189.79</v>
       </c>
       <c r="L40" t="n">
-        <v>208.25</v>
+        <v>221.24</v>
       </c>
     </row>
     <row r="41">
@@ -1759,28 +1759,28 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.31</v>
+        <v>6.19</v>
       </c>
       <c r="F41" t="n">
-        <v>15.41</v>
+        <v>16.99</v>
       </c>
       <c r="G41" t="n">
-        <v>313.1</v>
+        <v>324.5</v>
       </c>
       <c r="H41" t="n">
-        <v>72.5</v>
+        <v>78.7</v>
       </c>
       <c r="I41" t="n">
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>258.22</v>
+        <v>219.88</v>
       </c>
       <c r="K41" t="n">
-        <v>-216.08</v>
+        <v>11.91</v>
       </c>
       <c r="L41" t="n">
-        <v>336.7</v>
+        <v>220.2</v>
       </c>
     </row>
     <row r="42">
@@ -1801,28 +1801,28 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.94</v>
+        <v>5.66</v>
       </c>
       <c r="F42" t="n">
-        <v>15.86</v>
+        <v>12.7</v>
       </c>
       <c r="G42" t="n">
-        <v>324.5</v>
+        <v>337.6</v>
       </c>
       <c r="H42" t="n">
-        <v>78.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-243.69</v>
+        <v>124.66</v>
       </c>
       <c r="K42" t="n">
-        <v>181.22</v>
+        <v>551.34</v>
       </c>
       <c r="L42" t="n">
-        <v>303.68</v>
+        <v>565.26</v>
       </c>
     </row>
     <row r="43">
@@ -1843,28 +1843,28 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.55</v>
+        <v>6.2</v>
       </c>
       <c r="F43" t="n">
-        <v>15.38</v>
+        <v>15.77</v>
       </c>
       <c r="G43" t="n">
-        <v>323.4</v>
+        <v>334.7</v>
       </c>
       <c r="H43" t="n">
-        <v>82.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>340.17</v>
+        <v>230.54</v>
       </c>
       <c r="K43" t="n">
-        <v>-33.36</v>
+        <v>310.51</v>
       </c>
       <c r="L43" t="n">
-        <v>341.81</v>
+        <v>386.74</v>
       </c>
     </row>
     <row r="44">
@@ -1885,28 +1885,28 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.62</v>
+        <v>5.18</v>
       </c>
       <c r="F44" t="n">
-        <v>15.6</v>
+        <v>12.39</v>
       </c>
       <c r="G44" t="n">
-        <v>334.7</v>
+        <v>318.7</v>
       </c>
       <c r="H44" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>20.78</v>
+        <v>80.52</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.64</v>
+        <v>26.89</v>
       </c>
       <c r="L44" t="n">
-        <v>63.15</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>5.82</v>
       </c>
       <c r="F45" t="n">
-        <v>15.63</v>
+        <v>17.36</v>
       </c>
       <c r="G45" t="n">
-        <v>329</v>
+        <v>336.9</v>
       </c>
       <c r="H45" t="n">
-        <v>73.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>20.48</v>
+        <v>-105.31</v>
       </c>
       <c r="K45" t="n">
-        <v>63.51</v>
+        <v>-33.52</v>
       </c>
       <c r="L45" t="n">
-        <v>66.73</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="46">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.53</v>
+        <v>6.04</v>
       </c>
       <c r="F46" t="n">
-        <v>15.37</v>
+        <v>17.36</v>
       </c>
       <c r="G46" t="n">
-        <v>336.9</v>
+        <v>320.1</v>
       </c>
       <c r="H46" t="n">
-        <v>78.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.51</v>
+        <v>-48.13</v>
       </c>
       <c r="K46" t="n">
-        <v>59.02</v>
+        <v>-42.07</v>
       </c>
       <c r="L46" t="n">
-        <v>80.34</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="47">
@@ -2011,28 +2011,28 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.52</v>
+        <v>6.45</v>
       </c>
       <c r="F47" t="n">
-        <v>14.96</v>
+        <v>17.36</v>
       </c>
       <c r="G47" t="n">
-        <v>316.5</v>
+        <v>328.3</v>
       </c>
       <c r="H47" t="n">
-        <v>73.8</v>
+        <v>79.5</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>88.86</v>
+        <v>125.41</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.83</v>
+        <v>-7.68</v>
       </c>
       <c r="L47" t="n">
-        <v>106.57</v>
+        <v>125.64</v>
       </c>
     </row>
     <row r="48">
@@ -2053,28 +2053,28 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.07</v>
+        <v>6.17</v>
       </c>
       <c r="F48" t="n">
-        <v>15.04</v>
+        <v>13.15</v>
       </c>
       <c r="G48" t="n">
-        <v>328.3</v>
+        <v>323.5</v>
       </c>
       <c r="H48" t="n">
-        <v>79.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.18</v>
+        <v>-68.77</v>
       </c>
       <c r="K48" t="n">
-        <v>89.55</v>
+        <v>68.56</v>
       </c>
       <c r="L48" t="n">
-        <v>93.02</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.65</v>
+        <v>6.08</v>
       </c>
       <c r="F49" t="n">
-        <v>14.84</v>
+        <v>15.33</v>
       </c>
       <c r="G49" t="n">
-        <v>323.7</v>
+        <v>335.8</v>
       </c>
       <c r="H49" t="n">
-        <v>75.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>70.79000000000001</v>
+        <v>-38.67</v>
       </c>
       <c r="K49" t="n">
-        <v>-25.41</v>
+        <v>124.51</v>
       </c>
       <c r="L49" t="n">
-        <v>75.22</v>
+        <v>130.38</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="F50" t="n">
-        <v>15.65</v>
+        <v>12.4</v>
       </c>
       <c r="G50" t="n">
-        <v>335.8</v>
+        <v>327.5</v>
       </c>
       <c r="H50" t="n">
-        <v>77.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>192.67</v>
+        <v>-122.09</v>
       </c>
       <c r="K50" t="n">
-        <v>-23.55</v>
+        <v>-83.51000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>194.1</v>
+        <v>147.92</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="F51" t="n">
-        <v>14.85</v>
+        <v>15.26</v>
       </c>
       <c r="G51" t="n">
-        <v>322.7</v>
+        <v>330.3</v>
       </c>
       <c r="H51" t="n">
-        <v>77.5</v>
+        <v>83.7</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-132.48</v>
+        <v>-104.81</v>
       </c>
       <c r="K51" t="n">
-        <v>-89.51000000000001</v>
+        <v>131.21</v>
       </c>
       <c r="L51" t="n">
-        <v>159.88</v>
+        <v>167.93</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.25</v>
+        <v>5.64</v>
       </c>
       <c r="F52" t="n">
-        <v>14.9</v>
+        <v>17.36</v>
       </c>
       <c r="G52" t="n">
-        <v>330.3</v>
+        <v>343</v>
       </c>
       <c r="H52" t="n">
-        <v>83.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>137.01</v>
+        <v>66.23</v>
       </c>
       <c r="K52" t="n">
-        <v>-22.71</v>
+        <v>123.6</v>
       </c>
       <c r="L52" t="n">
-        <v>138.88</v>
+        <v>140.23</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.98</v>
+        <v>5.3</v>
       </c>
       <c r="F53" t="n">
-        <v>15.28</v>
+        <v>16.29</v>
       </c>
       <c r="G53" t="n">
-        <v>315.8</v>
+        <v>309.6</v>
       </c>
       <c r="H53" t="n">
-        <v>85.3</v>
+        <v>77.8</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-195.68</v>
+        <v>186.26</v>
       </c>
       <c r="K53" t="n">
-        <v>165.06</v>
+        <v>8.5</v>
       </c>
       <c r="L53" t="n">
-        <v>255.99</v>
+        <v>186.45</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.53</v>
+        <v>5.89</v>
       </c>
       <c r="F54" t="n">
-        <v>15.29</v>
+        <v>15.24</v>
       </c>
       <c r="G54" t="n">
-        <v>309.6</v>
+        <v>335.9</v>
       </c>
       <c r="H54" t="n">
-        <v>77.8</v>
+        <v>80.3</v>
       </c>
       <c r="I54" t="n">
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-161.5</v>
+        <v>-136.85</v>
       </c>
       <c r="K54" t="n">
-        <v>141.49</v>
+        <v>-248.14</v>
       </c>
       <c r="L54" t="n">
-        <v>214.72</v>
+        <v>283.37</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.57</v>
+        <v>6.69</v>
       </c>
       <c r="F55" t="n">
-        <v>14.9</v>
+        <v>14.43</v>
       </c>
       <c r="G55" t="n">
-        <v>314.6</v>
+        <v>318.8</v>
       </c>
       <c r="H55" t="n">
-        <v>81.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>238.21</v>
+        <v>204.55</v>
       </c>
       <c r="K55" t="n">
-        <v>142.93</v>
+        <v>155.59</v>
       </c>
       <c r="L55" t="n">
-        <v>277.8</v>
+        <v>256.99</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.86</v>
+        <v>5.52</v>
       </c>
       <c r="F56" t="n">
-        <v>15.51</v>
+        <v>14.61</v>
       </c>
       <c r="G56" t="n">
-        <v>318.8</v>
+        <v>324.8</v>
       </c>
       <c r="H56" t="n">
-        <v>75.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>47.83</v>
+        <v>-447.08</v>
       </c>
       <c r="K56" t="n">
-        <v>-197.39</v>
+        <v>-109.31</v>
       </c>
       <c r="L56" t="n">
-        <v>203.1</v>
+        <v>460.25</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.53</v>
+        <v>5.82</v>
       </c>
       <c r="F57" t="n">
-        <v>14.49</v>
+        <v>16.67</v>
       </c>
       <c r="G57" t="n">
-        <v>329.3</v>
+        <v>324</v>
       </c>
       <c r="H57" t="n">
-        <v>76.2</v>
+        <v>77.8</v>
       </c>
       <c r="I57" t="n">
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-35.63</v>
+        <v>55.6</v>
       </c>
       <c r="K57" t="n">
-        <v>393.21</v>
+        <v>448.53</v>
       </c>
       <c r="L57" t="n">
-        <v>394.83</v>
+        <v>451.97</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.87</v>
+        <v>5.19</v>
       </c>
       <c r="F58" t="n">
-        <v>15.27</v>
+        <v>14.13</v>
       </c>
       <c r="G58" t="n">
-        <v>333.4</v>
+        <v>344</v>
       </c>
       <c r="H58" t="n">
-        <v>75.8</v>
+        <v>78.2</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-469.77</v>
+        <v>-118.06</v>
       </c>
       <c r="K58" t="n">
-        <v>-186.54</v>
+        <v>252.53</v>
       </c>
       <c r="L58" t="n">
-        <v>505.45</v>
+        <v>278.76</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>15.07</v>
+        <v>17.29</v>
       </c>
       <c r="G59" t="n">
-        <v>324.5</v>
+        <v>336.8</v>
       </c>
       <c r="H59" t="n">
-        <v>69</v>
+        <v>82.3</v>
       </c>
       <c r="I59" t="n">
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>86.61</v>
+        <v>-103.03</v>
       </c>
       <c r="K59" t="n">
-        <v>46.29</v>
+        <v>-5.04</v>
       </c>
       <c r="L59" t="n">
-        <v>98.2</v>
+        <v>103.15</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.12</v>
+        <v>6.12</v>
       </c>
       <c r="F60" t="n">
-        <v>14.45</v>
+        <v>13.47</v>
       </c>
       <c r="G60" t="n">
-        <v>326.9</v>
+        <v>333.6</v>
       </c>
       <c r="H60" t="n">
-        <v>82.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I60" t="n">
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>26.83</v>
+        <v>24.59</v>
       </c>
       <c r="K60" t="n">
-        <v>61.56</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>67.16</v>
+        <v>79.68000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.05</v>
+        <v>6.13</v>
       </c>
       <c r="F61" t="n">
-        <v>15.56</v>
+        <v>16.53</v>
       </c>
       <c r="G61" t="n">
-        <v>328.2</v>
+        <v>330.6</v>
       </c>
       <c r="H61" t="n">
-        <v>82.2</v>
+        <v>71.3</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>68.54000000000001</v>
+        <v>62.38</v>
       </c>
       <c r="K61" t="n">
-        <v>12.85</v>
+        <v>-33.85</v>
       </c>
       <c r="L61" t="n">
-        <v>69.73999999999999</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.16</v>
+        <v>6.11</v>
       </c>
       <c r="F62" t="n">
-        <v>15.39</v>
+        <v>15.49</v>
       </c>
       <c r="G62" t="n">
-        <v>314.8</v>
+        <v>330.8</v>
       </c>
       <c r="H62" t="n">
-        <v>79.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>31.4</v>
+        <v>-89.91</v>
       </c>
       <c r="K62" t="n">
-        <v>-89.31</v>
+        <v>-100.43</v>
       </c>
       <c r="L62" t="n">
-        <v>94.66</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.69</v>
+        <v>5.47</v>
       </c>
       <c r="F63" t="n">
-        <v>14.5</v>
+        <v>17.05</v>
       </c>
       <c r="G63" t="n">
-        <v>315.6</v>
+        <v>338.5</v>
       </c>
       <c r="H63" t="n">
-        <v>80.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-64.72</v>
+        <v>-109.74</v>
       </c>
       <c r="K63" t="n">
-        <v>93.89</v>
+        <v>-59</v>
       </c>
       <c r="L63" t="n">
-        <v>114.04</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.59</v>
+        <v>5.14</v>
       </c>
       <c r="F64" t="n">
-        <v>14.45</v>
+        <v>13.75</v>
       </c>
       <c r="G64" t="n">
-        <v>335</v>
+        <v>308.6</v>
       </c>
       <c r="H64" t="n">
-        <v>83</v>
+        <v>76.3</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-122.05</v>
+        <v>19.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.9399999999999999</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>122.05</v>
+        <v>88.34999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.98</v>
+        <v>4.99</v>
       </c>
       <c r="F65" t="n">
-        <v>15.35</v>
+        <v>14.96</v>
       </c>
       <c r="G65" t="n">
-        <v>326.9</v>
+        <v>314.2</v>
       </c>
       <c r="H65" t="n">
-        <v>70.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-137.05</v>
+        <v>-211.49</v>
       </c>
       <c r="K65" t="n">
-        <v>115.33</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>179.12</v>
+        <v>211.66</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.38</v>
+        <v>6.43</v>
       </c>
       <c r="F66" t="n">
-        <v>14.29</v>
+        <v>16.5</v>
       </c>
       <c r="G66" t="n">
-        <v>331.5</v>
+        <v>322.9</v>
       </c>
       <c r="H66" t="n">
-        <v>70.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>107.41</v>
+        <v>-116.33</v>
       </c>
       <c r="K66" t="n">
-        <v>88.95</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>139.46</v>
+        <v>141.15</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.76</v>
+        <v>5.78</v>
       </c>
       <c r="F67" t="n">
-        <v>15.07</v>
+        <v>13.81</v>
       </c>
       <c r="G67" t="n">
-        <v>324</v>
+        <v>325.8</v>
       </c>
       <c r="H67" t="n">
-        <v>71</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>106.79</v>
+        <v>-59.99</v>
       </c>
       <c r="K67" t="n">
-        <v>-111.3</v>
+        <v>-142.19</v>
       </c>
       <c r="L67" t="n">
-        <v>154.25</v>
+        <v>154.33</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.18</v>
+        <v>5.53</v>
       </c>
       <c r="F68" t="n">
-        <v>15.04</v>
+        <v>13.97</v>
       </c>
       <c r="G68" t="n">
-        <v>323.9</v>
+        <v>326.9</v>
       </c>
       <c r="H68" t="n">
-        <v>76.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-197.31</v>
+        <v>181.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-60.14</v>
+        <v>161.86</v>
       </c>
       <c r="L68" t="n">
-        <v>206.27</v>
+        <v>243.24</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.74</v>
+        <v>5.35</v>
       </c>
       <c r="F69" t="n">
-        <v>15.28</v>
+        <v>12.31</v>
       </c>
       <c r="G69" t="n">
-        <v>333.6</v>
+        <v>311.5</v>
       </c>
       <c r="H69" t="n">
-        <v>74.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-376.73</v>
+        <v>51.98</v>
       </c>
       <c r="K69" t="n">
-        <v>-128.33</v>
+        <v>268.7</v>
       </c>
       <c r="L69" t="n">
-        <v>397.99</v>
+        <v>273.68</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.3</v>
+        <v>6.48</v>
       </c>
       <c r="F70" t="n">
-        <v>15.35</v>
+        <v>17.36</v>
       </c>
       <c r="G70" t="n">
-        <v>330.1</v>
+        <v>322.1</v>
       </c>
       <c r="H70" t="n">
-        <v>69.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>140.66</v>
+        <v>-351.74</v>
       </c>
       <c r="K70" t="n">
-        <v>261.88</v>
+        <v>39.44</v>
       </c>
       <c r="L70" t="n">
-        <v>297.27</v>
+        <v>353.95</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.27</v>
+        <v>6.29</v>
       </c>
       <c r="F71" t="n">
-        <v>15.04</v>
+        <v>16.21</v>
       </c>
       <c r="G71" t="n">
-        <v>314.1</v>
+        <v>332.7</v>
       </c>
       <c r="H71" t="n">
-        <v>79.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>428.59</v>
+        <v>361.04</v>
       </c>
       <c r="K71" t="n">
-        <v>-106.03</v>
+        <v>173.1</v>
       </c>
       <c r="L71" t="n">
-        <v>441.51</v>
+        <v>400.39</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.5</v>
+        <v>5.46</v>
       </c>
       <c r="F72" t="n">
-        <v>15.39</v>
+        <v>16.8</v>
       </c>
       <c r="G72" t="n">
-        <v>318.4</v>
+        <v>312.9</v>
       </c>
       <c r="H72" t="n">
-        <v>80.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-458.22</v>
+        <v>-436.94</v>
       </c>
       <c r="K72" t="n">
-        <v>11.41</v>
+        <v>406.97</v>
       </c>
       <c r="L72" t="n">
-        <v>458.36</v>
+        <v>597.12</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.68</v>
+        <v>6.78</v>
       </c>
       <c r="F73" t="n">
-        <v>15.73</v>
+        <v>17.36</v>
       </c>
       <c r="G73" t="n">
-        <v>311.4</v>
+        <v>320.5</v>
       </c>
       <c r="H73" t="n">
-        <v>77.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>368.95</v>
+        <v>-515.16</v>
       </c>
       <c r="K73" t="n">
-        <v>66.83</v>
+        <v>49.31</v>
       </c>
       <c r="L73" t="n">
-        <v>374.95</v>
+        <v>517.51</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.88</v>
+        <v>5.21</v>
       </c>
       <c r="F74" t="n">
-        <v>14.74</v>
+        <v>13.66</v>
       </c>
       <c r="G74" t="n">
-        <v>336.3</v>
+        <v>323.5</v>
       </c>
       <c r="H74" t="n">
-        <v>74.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-100.94</v>
+        <v>0.11</v>
       </c>
       <c r="K74" t="n">
-        <v>10.71</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>101.5</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.95</v>
+        <v>5.57</v>
       </c>
       <c r="F75" t="n">
-        <v>15.61</v>
+        <v>15.45</v>
       </c>
       <c r="G75" t="n">
-        <v>325.1</v>
+        <v>319.1</v>
       </c>
       <c r="H75" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>61.42</v>
+        <v>39.59</v>
       </c>
       <c r="K75" t="n">
-        <v>18.43</v>
+        <v>-62.6</v>
       </c>
       <c r="L75" t="n">
-        <v>64.13</v>
+        <v>74.06999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.04</v>
+        <v>5.44</v>
       </c>
       <c r="F76" t="n">
-        <v>15.28</v>
+        <v>15.95</v>
       </c>
       <c r="G76" t="n">
-        <v>319.1</v>
+        <v>334.4</v>
       </c>
       <c r="H76" t="n">
-        <v>77.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.79</v>
+        <v>-55.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-80.64</v>
+        <v>11.61</v>
       </c>
       <c r="L76" t="n">
-        <v>95.84</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.15</v>
+        <v>5.51</v>
       </c>
       <c r="F77" t="n">
-        <v>14.99</v>
+        <v>14.9</v>
       </c>
       <c r="G77" t="n">
-        <v>327.8</v>
+        <v>313.8</v>
       </c>
       <c r="H77" t="n">
-        <v>81</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-98.05</v>
+        <v>59.67</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.26</v>
+        <v>-65.12</v>
       </c>
       <c r="L77" t="n">
-        <v>108.85</v>
+        <v>88.31999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.1</v>
+        <v>5.79</v>
       </c>
       <c r="F78" t="n">
-        <v>14.64</v>
+        <v>14.31</v>
       </c>
       <c r="G78" t="n">
-        <v>313.8</v>
+        <v>314.7</v>
       </c>
       <c r="H78" t="n">
-        <v>76.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-72.45</v>
+        <v>-89.3</v>
       </c>
       <c r="K78" t="n">
-        <v>-50.96</v>
+        <v>27.06</v>
       </c>
       <c r="L78" t="n">
-        <v>88.56999999999999</v>
+        <v>93.31</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.17</v>
+        <v>5.89</v>
       </c>
       <c r="F79" t="n">
-        <v>14.8</v>
+        <v>17.36</v>
       </c>
       <c r="G79" t="n">
-        <v>324.8</v>
+        <v>322.3</v>
       </c>
       <c r="H79" t="n">
-        <v>71.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-74.51000000000001</v>
+        <v>-14.09</v>
       </c>
       <c r="K79" t="n">
-        <v>5.29</v>
+        <v>105.87</v>
       </c>
       <c r="L79" t="n">
-        <v>74.7</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.74</v>
+        <v>6.06</v>
       </c>
       <c r="F80" t="n">
-        <v>15.69</v>
+        <v>17.19</v>
       </c>
       <c r="G80" t="n">
-        <v>322.3</v>
+        <v>313.3</v>
       </c>
       <c r="H80" t="n">
-        <v>73.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>175.96</v>
+        <v>101.37</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.09</v>
+        <v>166.69</v>
       </c>
       <c r="L80" t="n">
-        <v>176.1</v>
+        <v>195.09</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.73</v>
+        <v>7.32</v>
       </c>
       <c r="F81" t="n">
-        <v>15.53</v>
+        <v>17.36</v>
       </c>
       <c r="G81" t="n">
-        <v>312.1</v>
+        <v>320.8</v>
       </c>
       <c r="H81" t="n">
-        <v>70.5</v>
+        <v>73.2</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>231.41</v>
+        <v>-181.11</v>
       </c>
       <c r="K81" t="n">
-        <v>-138.42</v>
+        <v>67.88</v>
       </c>
       <c r="L81" t="n">
-        <v>269.65</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.4</v>
+        <v>6.56</v>
       </c>
       <c r="F82" t="n">
-        <v>15.25</v>
+        <v>17.36</v>
       </c>
       <c r="G82" t="n">
-        <v>320.8</v>
+        <v>323.7</v>
       </c>
       <c r="H82" t="n">
-        <v>73.2</v>
+        <v>78</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-9.85</v>
+        <v>61.41</v>
       </c>
       <c r="K82" t="n">
-        <v>142.6</v>
+        <v>-148.05</v>
       </c>
       <c r="L82" t="n">
-        <v>142.94</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.72</v>
+        <v>6.24</v>
       </c>
       <c r="F83" t="n">
-        <v>15.32</v>
+        <v>17.04</v>
       </c>
       <c r="G83" t="n">
-        <v>320.2</v>
+        <v>319.4</v>
       </c>
       <c r="H83" t="n">
-        <v>75.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-11.13</v>
+        <v>-60.13</v>
       </c>
       <c r="K83" t="n">
-        <v>-248.15</v>
+        <v>-366.71</v>
       </c>
       <c r="L83" t="n">
-        <v>248.4</v>
+        <v>371.6</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.17</v>
+        <v>5.32</v>
       </c>
       <c r="F84" t="n">
-        <v>14.78</v>
+        <v>14.83</v>
       </c>
       <c r="G84" t="n">
-        <v>319.4</v>
+        <v>332.6</v>
       </c>
       <c r="H84" t="n">
-        <v>74.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-309.15</v>
+        <v>-174.67</v>
       </c>
       <c r="K84" t="n">
-        <v>-195.86</v>
+        <v>-97.94</v>
       </c>
       <c r="L84" t="n">
-        <v>365.98</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.58</v>
+        <v>7.12</v>
       </c>
       <c r="F85" t="n">
-        <v>14.87</v>
+        <v>17.36</v>
       </c>
       <c r="G85" t="n">
-        <v>319.7</v>
+        <v>320</v>
       </c>
       <c r="H85" t="n">
-        <v>80.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>288.26</v>
+        <v>-48</v>
       </c>
       <c r="K85" t="n">
-        <v>69.27</v>
+        <v>461.57</v>
       </c>
       <c r="L85" t="n">
-        <v>296.46</v>
+        <v>464.06</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.97</v>
+        <v>5.95</v>
       </c>
       <c r="F86" t="n">
-        <v>15.1</v>
+        <v>17.36</v>
       </c>
       <c r="G86" t="n">
-        <v>328.4</v>
+        <v>327.4</v>
       </c>
       <c r="H86" t="n">
-        <v>73.8</v>
+        <v>76.8</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-227.67</v>
+        <v>-568.61</v>
       </c>
       <c r="K86" t="n">
-        <v>395.1</v>
+        <v>178.26</v>
       </c>
       <c r="L86" t="n">
-        <v>456</v>
+        <v>595.9</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.61</v>
+        <v>6.43</v>
       </c>
       <c r="F87" t="n">
-        <v>15.24</v>
+        <v>17.36</v>
       </c>
       <c r="G87" t="n">
-        <v>309</v>
+        <v>336.5</v>
       </c>
       <c r="H87" t="n">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>274.95</v>
+        <v>-111.32</v>
       </c>
       <c r="K87" t="n">
-        <v>154.86</v>
+        <v>436.26</v>
       </c>
       <c r="L87" t="n">
-        <v>315.56</v>
+        <v>450.24</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.69</v>
+        <v>5.98</v>
       </c>
       <c r="F88" t="n">
-        <v>15.06</v>
+        <v>15.93</v>
       </c>
       <c r="G88" t="n">
-        <v>316.9</v>
+        <v>323.4</v>
       </c>
       <c r="H88" t="n">
-        <v>82.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-238.92</v>
+        <v>509.73</v>
       </c>
       <c r="K88" t="n">
-        <v>324.55</v>
+        <v>-131.35</v>
       </c>
       <c r="L88" t="n">
-        <v>403.01</v>
+        <v>526.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>45.44</v>
+        <v>45.04</v>
       </c>
       <c r="K14" t="n">
-        <v>-45.6</v>
+        <v>-45.19</v>
       </c>
       <c r="L14" t="n">
-        <v>64.38</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.26</v>
+        <v>-10.36</v>
       </c>
       <c r="K15" t="n">
-        <v>-69.65000000000001</v>
+        <v>-70.33</v>
       </c>
       <c r="L15" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3</v>
+        <v>7.06</v>
       </c>
       <c r="K16" t="n">
-        <v>61.47</v>
+        <v>59.5</v>
       </c>
       <c r="L16" t="n">
-        <v>61.9</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>71.89</v>
+        <v>72.75</v>
       </c>
       <c r="K17" t="n">
-        <v>70.45999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="L17" t="n">
-        <v>100.66</v>
+        <v>101.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-85.16</v>
+        <v>-79.02</v>
       </c>
       <c r="K18" t="n">
-        <v>48.77</v>
+        <v>45.26</v>
       </c>
       <c r="L18" t="n">
-        <v>98.13</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>69.2</v>
+        <v>68.83</v>
       </c>
       <c r="K19" t="n">
-        <v>24.8</v>
+        <v>24.67</v>
       </c>
       <c r="L19" t="n">
-        <v>73.51000000000001</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-182.82</v>
+        <v>-178.36</v>
       </c>
       <c r="K20" t="n">
-        <v>132.33</v>
+        <v>129.1</v>
       </c>
       <c r="L20" t="n">
-        <v>225.69</v>
+        <v>220.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>119.12</v>
+        <v>123.29</v>
       </c>
       <c r="K21" t="n">
-        <v>-128.23</v>
+        <v>-132.71</v>
       </c>
       <c r="L21" t="n">
-        <v>175.02</v>
+        <v>181.14</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-110.74</v>
+        <v>-105.7</v>
       </c>
       <c r="K22" t="n">
-        <v>-51.81</v>
+        <v>-49.45</v>
       </c>
       <c r="L22" t="n">
-        <v>122.26</v>
+        <v>116.69</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-34.01</v>
+        <v>-35.66</v>
       </c>
       <c r="K23" t="n">
-        <v>-169.94</v>
+        <v>-178.19</v>
       </c>
       <c r="L23" t="n">
-        <v>173.31</v>
+        <v>181.72</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-94.51000000000001</v>
+        <v>-93.3</v>
       </c>
       <c r="K24" t="n">
-        <v>187.96</v>
+        <v>185.56</v>
       </c>
       <c r="L24" t="n">
-        <v>210.38</v>
+        <v>207.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>139.89</v>
+        <v>144.06</v>
       </c>
       <c r="K25" t="n">
-        <v>149.68</v>
+        <v>154.14</v>
       </c>
       <c r="L25" t="n">
-        <v>204.87</v>
+        <v>210.98</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>318.3</v>
+        <v>337.37</v>
       </c>
       <c r="K26" t="n">
-        <v>-31.66</v>
+        <v>-33.56</v>
       </c>
       <c r="L26" t="n">
-        <v>319.87</v>
+        <v>339.03</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-196.52</v>
+        <v>-195.81</v>
       </c>
       <c r="K27" t="n">
-        <v>-130.83</v>
+        <v>-130.36</v>
       </c>
       <c r="L27" t="n">
-        <v>236.09</v>
+        <v>235.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>33.52</v>
+        <v>32.79</v>
       </c>
       <c r="K28" t="n">
-        <v>309.25</v>
+        <v>302.53</v>
       </c>
       <c r="L28" t="n">
-        <v>311.06</v>
+        <v>304.3</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-47.95</v>
+        <v>-46.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-43.73</v>
+        <v>-42.51</v>
       </c>
       <c r="L29" t="n">
-        <v>64.90000000000001</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>13.27</v>
+        <v>13.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-82.11</v>
+        <v>-84.72</v>
       </c>
       <c r="L30" t="n">
-        <v>83.17</v>
+        <v>85.81999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>4.92</v>
+        <v>4.56</v>
       </c>
       <c r="K31" t="n">
-        <v>-66.64</v>
+        <v>-61.71</v>
       </c>
       <c r="L31" t="n">
-        <v>66.81999999999999</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>22</v>
+        <v>20.39</v>
       </c>
       <c r="K32" t="n">
-        <v>95.58</v>
+        <v>88.61</v>
       </c>
       <c r="L32" t="n">
-        <v>98.08</v>
+        <v>90.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>23.11</v>
+        <v>22.92</v>
       </c>
       <c r="K33" t="n">
-        <v>-69.63</v>
+        <v>-69.06999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>73.37</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>98.08</v>
+        <v>100.95</v>
       </c>
       <c r="K34" t="n">
-        <v>12.03</v>
+        <v>12.39</v>
       </c>
       <c r="L34" t="n">
-        <v>98.81</v>
+        <v>101.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-129.72</v>
+        <v>-136.37</v>
       </c>
       <c r="K35" t="n">
-        <v>140.49</v>
+        <v>147.69</v>
       </c>
       <c r="L35" t="n">
-        <v>191.22</v>
+        <v>201.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>20.62</v>
+        <v>20.11</v>
       </c>
       <c r="K36" t="n">
-        <v>-220.19</v>
+        <v>-214.78</v>
       </c>
       <c r="L36" t="n">
-        <v>221.15</v>
+        <v>215.72</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>100.89</v>
+        <v>106.17</v>
       </c>
       <c r="K37" t="n">
-        <v>-126.24</v>
+        <v>-132.84</v>
       </c>
       <c r="L37" t="n">
-        <v>161.6</v>
+        <v>170.06</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>209.83</v>
+        <v>203.47</v>
       </c>
       <c r="K38" t="n">
-        <v>109.34</v>
+        <v>106.03</v>
       </c>
       <c r="L38" t="n">
-        <v>236.61</v>
+        <v>229.44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>80.59</v>
+        <v>86</v>
       </c>
       <c r="K39" t="n">
-        <v>229.55</v>
+        <v>244.99</v>
       </c>
       <c r="L39" t="n">
-        <v>243.28</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>113.69</v>
+        <v>107.56</v>
       </c>
       <c r="K40" t="n">
-        <v>189.79</v>
+        <v>179.55</v>
       </c>
       <c r="L40" t="n">
-        <v>221.24</v>
+        <v>209.31</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>219.88</v>
+        <v>220.51</v>
       </c>
       <c r="K41" t="n">
-        <v>11.91</v>
+        <v>11.94</v>
       </c>
       <c r="L41" t="n">
-        <v>220.2</v>
+        <v>220.83</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>124.66</v>
+        <v>134.57</v>
       </c>
       <c r="K42" t="n">
-        <v>551.34</v>
+        <v>595.1900000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>565.26</v>
+        <v>610.22</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>230.54</v>
+        <v>226.19</v>
       </c>
       <c r="K43" t="n">
-        <v>310.51</v>
+        <v>304.65</v>
       </c>
       <c r="L43" t="n">
-        <v>386.74</v>
+        <v>379.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>80.52</v>
+        <v>84.33</v>
       </c>
       <c r="K44" t="n">
-        <v>26.89</v>
+        <v>28.16</v>
       </c>
       <c r="L44" t="n">
-        <v>84.90000000000001</v>
+        <v>88.91</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-105.31</v>
+        <v>-108.11</v>
       </c>
       <c r="K45" t="n">
-        <v>-33.52</v>
+        <v>-34.41</v>
       </c>
       <c r="L45" t="n">
-        <v>110.52</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>-48.13</v>
+        <v>-43.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-42.07</v>
+        <v>-38.44</v>
       </c>
       <c r="L46" t="n">
-        <v>63.92</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>125.41</v>
+        <v>113.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.68</v>
+        <v>-6.96</v>
       </c>
       <c r="L47" t="n">
-        <v>125.64</v>
+        <v>113.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-68.77</v>
+        <v>-65.25</v>
       </c>
       <c r="K48" t="n">
-        <v>68.56</v>
+        <v>65.05</v>
       </c>
       <c r="L48" t="n">
-        <v>97.09999999999999</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-38.67</v>
+        <v>-35.08</v>
       </c>
       <c r="K49" t="n">
-        <v>124.51</v>
+        <v>112.97</v>
       </c>
       <c r="L49" t="n">
-        <v>130.38</v>
+        <v>118.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-122.09</v>
+        <v>-121.59</v>
       </c>
       <c r="K50" t="n">
-        <v>-83.51000000000001</v>
+        <v>-83.17</v>
       </c>
       <c r="L50" t="n">
-        <v>147.92</v>
+        <v>147.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-104.81</v>
+        <v>-104.42</v>
       </c>
       <c r="K51" t="n">
-        <v>131.21</v>
+        <v>130.73</v>
       </c>
       <c r="L51" t="n">
-        <v>167.93</v>
+        <v>167.31</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>66.23</v>
+        <v>61.74</v>
       </c>
       <c r="K52" t="n">
-        <v>123.6</v>
+        <v>115.23</v>
       </c>
       <c r="L52" t="n">
-        <v>140.23</v>
+        <v>130.73</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>186.26</v>
+        <v>195.33</v>
       </c>
       <c r="K53" t="n">
-        <v>8.5</v>
+        <v>8.91</v>
       </c>
       <c r="L53" t="n">
-        <v>186.45</v>
+        <v>195.54</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-136.85</v>
+        <v>-143.7</v>
       </c>
       <c r="K54" t="n">
-        <v>-248.14</v>
+        <v>-260.57</v>
       </c>
       <c r="L54" t="n">
-        <v>283.37</v>
+        <v>297.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>204.55</v>
+        <v>198.49</v>
       </c>
       <c r="K55" t="n">
-        <v>155.59</v>
+        <v>150.98</v>
       </c>
       <c r="L55" t="n">
-        <v>256.99</v>
+        <v>249.38</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-447.08</v>
+        <v>-465.45</v>
       </c>
       <c r="K56" t="n">
-        <v>-109.31</v>
+        <v>-113.8</v>
       </c>
       <c r="L56" t="n">
-        <v>460.25</v>
+        <v>479.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>55.6</v>
+        <v>54.48</v>
       </c>
       <c r="K57" t="n">
-        <v>448.53</v>
+        <v>439.46</v>
       </c>
       <c r="L57" t="n">
-        <v>451.97</v>
+        <v>442.82</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-118.06</v>
+        <v>-127.17</v>
       </c>
       <c r="K58" t="n">
-        <v>252.53</v>
+        <v>272.01</v>
       </c>
       <c r="L58" t="n">
-        <v>278.76</v>
+        <v>300.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-103.03</v>
+        <v>-106.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.04</v>
+        <v>-5.22</v>
       </c>
       <c r="L59" t="n">
-        <v>103.15</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>24.59</v>
+        <v>22.81</v>
       </c>
       <c r="K60" t="n">
-        <v>75.79000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>79.68000000000001</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>62.38</v>
+        <v>57.79</v>
       </c>
       <c r="K61" t="n">
-        <v>-33.85</v>
+        <v>-31.36</v>
       </c>
       <c r="L61" t="n">
-        <v>70.97</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-89.91</v>
+        <v>-90.48</v>
       </c>
       <c r="K62" t="n">
-        <v>-100.43</v>
+        <v>-101.06</v>
       </c>
       <c r="L62" t="n">
-        <v>134.8</v>
+        <v>135.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-109.74</v>
+        <v>-108.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-59</v>
+        <v>-58.42</v>
       </c>
       <c r="L63" t="n">
-        <v>124.59</v>
+        <v>123.38</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>19.6</v>
+        <v>20.53</v>
       </c>
       <c r="K64" t="n">
-        <v>86.15000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="L64" t="n">
-        <v>88.34999999999999</v>
+        <v>92.56</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-211.49</v>
+        <v>-214.91</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.68</v>
       </c>
       <c r="L65" t="n">
-        <v>211.66</v>
+        <v>215.08</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-116.33</v>
+        <v>-113.39</v>
       </c>
       <c r="K66" t="n">
-        <v>79.93000000000001</v>
+        <v>77.91</v>
       </c>
       <c r="L66" t="n">
-        <v>141.15</v>
+        <v>137.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-59.99</v>
+        <v>-59.73</v>
       </c>
       <c r="K67" t="n">
-        <v>-142.19</v>
+        <v>-141.58</v>
       </c>
       <c r="L67" t="n">
-        <v>154.33</v>
+        <v>153.66</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>181.58</v>
+        <v>187.07</v>
       </c>
       <c r="K68" t="n">
-        <v>161.86</v>
+        <v>166.75</v>
       </c>
       <c r="L68" t="n">
-        <v>243.24</v>
+        <v>250.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>51.98</v>
+        <v>55.47</v>
       </c>
       <c r="K69" t="n">
-        <v>268.7</v>
+        <v>286.75</v>
       </c>
       <c r="L69" t="n">
-        <v>273.68</v>
+        <v>292.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-351.74</v>
+        <v>-376.21</v>
       </c>
       <c r="K70" t="n">
-        <v>39.44</v>
+        <v>42.18</v>
       </c>
       <c r="L70" t="n">
-        <v>353.95</v>
+        <v>378.56</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>361.04</v>
+        <v>390.66</v>
       </c>
       <c r="K71" t="n">
-        <v>173.1</v>
+        <v>187.3</v>
       </c>
       <c r="L71" t="n">
-        <v>400.39</v>
+        <v>433.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-436.94</v>
+        <v>-463.18</v>
       </c>
       <c r="K72" t="n">
-        <v>406.97</v>
+        <v>431.42</v>
       </c>
       <c r="L72" t="n">
-        <v>597.12</v>
+        <v>632.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-515.16</v>
+        <v>-538.7</v>
       </c>
       <c r="K73" t="n">
-        <v>49.31</v>
+        <v>51.56</v>
       </c>
       <c r="L73" t="n">
-        <v>517.51</v>
+        <v>541.16</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K74" t="n">
-        <v>77.84999999999999</v>
+        <v>75.58</v>
       </c>
       <c r="L74" t="n">
-        <v>77.84999999999999</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>39.59</v>
+        <v>40.68</v>
       </c>
       <c r="K75" t="n">
-        <v>-62.6</v>
+        <v>-64.33</v>
       </c>
       <c r="L75" t="n">
-        <v>74.06999999999999</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.9</v>
+        <v>-54.22</v>
       </c>
       <c r="K76" t="n">
-        <v>11.61</v>
+        <v>11.26</v>
       </c>
       <c r="L76" t="n">
-        <v>57.09</v>
+        <v>55.37</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>59.67</v>
+        <v>57.87</v>
       </c>
       <c r="K77" t="n">
-        <v>-65.12</v>
+        <v>-63.16</v>
       </c>
       <c r="L77" t="n">
-        <v>88.31999999999999</v>
+        <v>85.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-89.3</v>
+        <v>-90.05</v>
       </c>
       <c r="K78" t="n">
-        <v>27.06</v>
+        <v>27.28</v>
       </c>
       <c r="L78" t="n">
-        <v>93.31</v>
+        <v>94.09</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-14.09</v>
+        <v>-13.39</v>
       </c>
       <c r="K79" t="n">
-        <v>105.87</v>
+        <v>100.63</v>
       </c>
       <c r="L79" t="n">
-        <v>106.8</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>101.37</v>
+        <v>100.9</v>
       </c>
       <c r="K80" t="n">
-        <v>166.69</v>
+        <v>165.92</v>
       </c>
       <c r="L80" t="n">
-        <v>195.09</v>
+        <v>194.19</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-181.11</v>
+        <v>-187.01</v>
       </c>
       <c r="K81" t="n">
-        <v>67.88</v>
+        <v>70.09</v>
       </c>
       <c r="L81" t="n">
-        <v>193.41</v>
+        <v>199.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>61.41</v>
+        <v>59.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-148.05</v>
+        <v>-144.29</v>
       </c>
       <c r="L82" t="n">
-        <v>160.28</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-60.13</v>
+        <v>-64.29000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-366.71</v>
+        <v>-392.06</v>
       </c>
       <c r="L83" t="n">
-        <v>371.6</v>
+        <v>397.29</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-174.67</v>
+        <v>-176.41</v>
       </c>
       <c r="K84" t="n">
-        <v>-97.94</v>
+        <v>-98.91</v>
       </c>
       <c r="L84" t="n">
-        <v>200.25</v>
+        <v>202.24</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-48</v>
+        <v>-51.39</v>
       </c>
       <c r="K85" t="n">
-        <v>461.57</v>
+        <v>494.11</v>
       </c>
       <c r="L85" t="n">
-        <v>464.06</v>
+        <v>496.77</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-568.61</v>
+        <v>-614.54</v>
       </c>
       <c r="K86" t="n">
-        <v>178.26</v>
+        <v>192.66</v>
       </c>
       <c r="L86" t="n">
-        <v>595.9</v>
+        <v>644.03</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-111.32</v>
+        <v>-116.29</v>
       </c>
       <c r="K87" t="n">
-        <v>436.26</v>
+        <v>455.73</v>
       </c>
       <c r="L87" t="n">
-        <v>450.24</v>
+        <v>470.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>509.73</v>
+        <v>521.45</v>
       </c>
       <c r="K88" t="n">
-        <v>-131.35</v>
+        <v>-134.37</v>
       </c>
       <c r="L88" t="n">
-        <v>526.38</v>
+        <v>538.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2</v>
+        <v>6.37</v>
       </c>
       <c r="F14" t="n">
-        <v>12.79</v>
+        <v>14.45</v>
       </c>
       <c r="G14" t="n">
-        <v>326.6</v>
+        <v>314.6</v>
       </c>
       <c r="H14" t="n">
-        <v>80.8</v>
+        <v>42.5</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>45.04</v>
+        <v>-3.44</v>
       </c>
       <c r="K14" t="n">
-        <v>-45.19</v>
+        <v>142.59</v>
       </c>
       <c r="L14" t="n">
-        <v>63.8</v>
+        <v>142.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:43:41</t>
+          <t>05:44:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.38</v>
+        <v>5.63</v>
       </c>
       <c r="F15" t="n">
-        <v>11.82</v>
+        <v>14.37</v>
       </c>
       <c r="G15" t="n">
         <v>324.3</v>
       </c>
       <c r="H15" t="n">
-        <v>76.3</v>
+        <v>61.9</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.36</v>
+        <v>-112.56</v>
       </c>
       <c r="K15" t="n">
-        <v>-70.33</v>
+        <v>-43.17</v>
       </c>
       <c r="L15" t="n">
-        <v>71.09</v>
+        <v>120.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:44:46</t>
+          <t>05:45:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.92</v>
+        <v>4.98</v>
       </c>
       <c r="F16" t="n">
-        <v>14.46</v>
+        <v>8.27</v>
       </c>
       <c r="G16" t="n">
-        <v>324.7</v>
+        <v>323.4</v>
       </c>
       <c r="H16" t="n">
-        <v>77.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>7.06</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>59.5</v>
+        <v>-47.6</v>
       </c>
       <c r="L16" t="n">
-        <v>59.91</v>
+        <v>95.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:50:17</t>
+          <t>05:50:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="F17" t="n">
-        <v>11.9</v>
+        <v>11.48</v>
       </c>
       <c r="G17" t="n">
-        <v>334.1</v>
+        <v>323.6</v>
       </c>
       <c r="H17" t="n">
-        <v>73.3</v>
+        <v>40.1</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>72.75</v>
+        <v>-68.78</v>
       </c>
       <c r="K17" t="n">
-        <v>71.3</v>
+        <v>91.53</v>
       </c>
       <c r="L17" t="n">
-        <v>101.87</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:51:42</t>
+          <t>05:51:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.23</v>
+        <v>4.77</v>
       </c>
       <c r="F18" t="n">
-        <v>13.35</v>
+        <v>12.41</v>
       </c>
       <c r="G18" t="n">
-        <v>317.5</v>
+        <v>313.2</v>
       </c>
       <c r="H18" t="n">
-        <v>84</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-79.02</v>
+        <v>-55.55</v>
       </c>
       <c r="K18" t="n">
-        <v>45.26</v>
+        <v>137.03</v>
       </c>
       <c r="L18" t="n">
-        <v>91.06</v>
+        <v>147.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:53:42</t>
+          <t>05:54:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.38</v>
+        <v>5.41</v>
       </c>
       <c r="F19" t="n">
-        <v>8.710000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="G19" t="n">
-        <v>344.4</v>
+        <v>321.4</v>
       </c>
       <c r="H19" t="n">
-        <v>77.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>68.83</v>
+        <v>-153.18</v>
       </c>
       <c r="K19" t="n">
-        <v>24.67</v>
+        <v>-18.9</v>
       </c>
       <c r="L19" t="n">
-        <v>73.12</v>
+        <v>154.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:57:53</t>
+          <t>05:58:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.57</v>
+        <v>6.34</v>
       </c>
       <c r="F20" t="n">
-        <v>15.41</v>
+        <v>15.83</v>
       </c>
       <c r="G20" t="n">
-        <v>305.2</v>
+        <v>321.5</v>
       </c>
       <c r="H20" t="n">
-        <v>72</v>
+        <v>56.4</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-178.36</v>
+        <v>-142.95</v>
       </c>
       <c r="K20" t="n">
-        <v>129.1</v>
+        <v>54.52</v>
       </c>
       <c r="L20" t="n">
-        <v>220.18</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:00:06</t>
+          <t>05:59:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.99</v>
+        <v>5.05</v>
       </c>
       <c r="F21" t="n">
-        <v>16.52</v>
+        <v>11.21</v>
       </c>
       <c r="G21" t="n">
-        <v>330.8</v>
+        <v>329.9</v>
       </c>
       <c r="H21" t="n">
-        <v>75.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>123.29</v>
+        <v>-117.5</v>
       </c>
       <c r="K21" t="n">
-        <v>-132.71</v>
+        <v>165.08</v>
       </c>
       <c r="L21" t="n">
-        <v>181.14</v>
+        <v>202.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:02:27</t>
+          <t>06:01:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.53</v>
+        <v>6.65</v>
       </c>
       <c r="F22" t="n">
-        <v>12.18</v>
+        <v>17.36</v>
       </c>
       <c r="G22" t="n">
-        <v>310.3</v>
+        <v>322.6</v>
       </c>
       <c r="H22" t="n">
-        <v>76.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>-105.7</v>
+        <v>-8.92</v>
       </c>
       <c r="K22" t="n">
-        <v>-49.45</v>
+        <v>168.34</v>
       </c>
       <c r="L22" t="n">
-        <v>116.69</v>
+        <v>168.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:05:21</t>
+          <t>06:05:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.22</v>
+        <v>4.34</v>
       </c>
       <c r="F23" t="n">
-        <v>14.68</v>
+        <v>10.69</v>
       </c>
       <c r="G23" t="n">
-        <v>323.1</v>
+        <v>335.4</v>
       </c>
       <c r="H23" t="n">
-        <v>74.7</v>
+        <v>29</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-35.66</v>
+        <v>-112.28</v>
       </c>
       <c r="K23" t="n">
-        <v>-178.19</v>
+        <v>-138.22</v>
       </c>
       <c r="L23" t="n">
-        <v>181.72</v>
+        <v>178.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:06:29</t>
+          <t>06:06:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.61</v>
+        <v>5.55</v>
       </c>
       <c r="F24" t="n">
-        <v>13.83</v>
+        <v>10.1</v>
       </c>
       <c r="G24" t="n">
-        <v>324</v>
+        <v>334.2</v>
       </c>
       <c r="H24" t="n">
-        <v>76.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-93.3</v>
+        <v>-372.98</v>
       </c>
       <c r="K24" t="n">
-        <v>185.56</v>
+        <v>-58.72</v>
       </c>
       <c r="L24" t="n">
-        <v>207.7</v>
+        <v>377.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:08:26</t>
+          <t>06:07:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.35</v>
+        <v>5.63</v>
       </c>
       <c r="F25" t="n">
-        <v>15.13</v>
+        <v>16.4</v>
       </c>
       <c r="G25" t="n">
-        <v>302.8</v>
+        <v>317.9</v>
       </c>
       <c r="H25" t="n">
-        <v>78.59999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>144.06</v>
+        <v>175.16</v>
       </c>
       <c r="K25" t="n">
-        <v>154.14</v>
+        <v>144.82</v>
       </c>
       <c r="L25" t="n">
-        <v>210.98</v>
+        <v>227.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:12:57</t>
+          <t>06:12:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="F26" t="n">
-        <v>13.7</v>
+        <v>12.77</v>
       </c>
       <c r="G26" t="n">
-        <v>326.1</v>
+        <v>322.9</v>
       </c>
       <c r="H26" t="n">
-        <v>81</v>
+        <v>26.3</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>337.37</v>
+        <v>315.92</v>
       </c>
       <c r="K26" t="n">
-        <v>-33.56</v>
+        <v>58.52</v>
       </c>
       <c r="L26" t="n">
-        <v>339.03</v>
+        <v>321.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:13:35</t>
+          <t>06:14:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.8</v>
+        <v>5.77</v>
       </c>
       <c r="F27" t="n">
-        <v>12.93</v>
+        <v>16.38</v>
       </c>
       <c r="G27" t="n">
-        <v>332.2</v>
+        <v>327.7</v>
       </c>
       <c r="H27" t="n">
-        <v>79.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-195.81</v>
+        <v>-115.67</v>
       </c>
       <c r="K27" t="n">
-        <v>-130.36</v>
+        <v>425.09</v>
       </c>
       <c r="L27" t="n">
-        <v>235.23</v>
+        <v>440.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:15:38</t>
+          <t>06:16:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.46</v>
+        <v>5.57</v>
       </c>
       <c r="F28" t="n">
-        <v>13.62</v>
+        <v>12.38</v>
       </c>
       <c r="G28" t="n">
-        <v>312.8</v>
+        <v>325.2</v>
       </c>
       <c r="H28" t="n">
-        <v>87.59999999999999</v>
+        <v>43.6</v>
       </c>
       <c r="I28" t="n">
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>32.79</v>
+        <v>-256.01</v>
       </c>
       <c r="K28" t="n">
-        <v>302.53</v>
+        <v>411.59</v>
       </c>
       <c r="L28" t="n">
-        <v>304.3</v>
+        <v>484.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:26:13</t>
+          <t>06:28:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.94</v>
+        <v>5.45</v>
       </c>
       <c r="F29" t="n">
-        <v>11.54</v>
+        <v>13.87</v>
       </c>
       <c r="G29" t="n">
-        <v>330.1</v>
+        <v>325</v>
       </c>
       <c r="H29" t="n">
-        <v>80</v>
+        <v>52.3</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-46.6</v>
+        <v>77.56</v>
       </c>
       <c r="K29" t="n">
-        <v>-42.51</v>
+        <v>59.29</v>
       </c>
       <c r="L29" t="n">
-        <v>63.08</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:27:25</t>
+          <t>06:29:42</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.62</v>
+        <v>5.49</v>
       </c>
       <c r="F30" t="n">
-        <v>12.85</v>
+        <v>13.01</v>
       </c>
       <c r="G30" t="n">
-        <v>324.6</v>
+        <v>322.2</v>
       </c>
       <c r="H30" t="n">
-        <v>74.90000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="I30" t="n">
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>13.69</v>
+        <v>-85.81</v>
       </c>
       <c r="K30" t="n">
-        <v>-84.72</v>
+        <v>-15.43</v>
       </c>
       <c r="L30" t="n">
-        <v>85.81999999999999</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:28:51</t>
+          <t>06:31:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.66</v>
+        <v>5.68</v>
       </c>
       <c r="F31" t="n">
-        <v>15.28</v>
+        <v>15.09</v>
       </c>
       <c r="G31" t="n">
-        <v>324.6</v>
+        <v>336.9</v>
       </c>
       <c r="H31" t="n">
-        <v>71</v>
+        <v>57.1</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J31" t="n">
-        <v>4.56</v>
+        <v>-85.48999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-61.71</v>
+        <v>35.85</v>
       </c>
       <c r="L31" t="n">
-        <v>61.88</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:33:57</t>
+          <t>06:36:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.39</v>
+        <v>4.78</v>
       </c>
       <c r="F32" t="n">
-        <v>16.39</v>
+        <v>9.26</v>
       </c>
       <c r="G32" t="n">
-        <v>314</v>
+        <v>321.4</v>
       </c>
       <c r="H32" t="n">
-        <v>73.8</v>
+        <v>63.8</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>20.39</v>
+        <v>47.74</v>
       </c>
       <c r="K32" t="n">
-        <v>88.61</v>
+        <v>57.25</v>
       </c>
       <c r="L32" t="n">
-        <v>90.92</v>
+        <v>74.54000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:35:39</t>
+          <t>06:37:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.03</v>
+        <v>4.4</v>
       </c>
       <c r="F33" t="n">
-        <v>12.42</v>
+        <v>9.52</v>
       </c>
       <c r="G33" t="n">
-        <v>306.7</v>
+        <v>325.8</v>
       </c>
       <c r="H33" t="n">
-        <v>79.7</v>
+        <v>43.4</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>22.92</v>
+        <v>48.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-69.06999999999999</v>
+        <v>82.16</v>
       </c>
       <c r="L33" t="n">
-        <v>72.78</v>
+        <v>95.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:37:34</t>
+          <t>06:39:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.23</v>
+        <v>5.31</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42</v>
+        <v>13.04</v>
       </c>
       <c r="G34" t="n">
-        <v>319.1</v>
+        <v>324.4</v>
       </c>
       <c r="H34" t="n">
-        <v>72.5</v>
+        <v>59.9</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>100.95</v>
+        <v>102.06</v>
       </c>
       <c r="K34" t="n">
-        <v>12.39</v>
+        <v>-81.98999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>101.71</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:41:48</t>
+          <t>06:43:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6.58</v>
+        <v>5.07</v>
       </c>
       <c r="F35" t="n">
-        <v>17.36</v>
+        <v>17.23</v>
       </c>
       <c r="G35" t="n">
-        <v>325.4</v>
+        <v>330</v>
       </c>
       <c r="H35" t="n">
-        <v>75.3</v>
+        <v>23.2</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-136.37</v>
+        <v>37.99</v>
       </c>
       <c r="K35" t="n">
-        <v>147.69</v>
+        <v>202.37</v>
       </c>
       <c r="L35" t="n">
-        <v>201.02</v>
+        <v>205.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:43:51</t>
+          <t>06:45:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.72</v>
+        <v>6.11</v>
       </c>
       <c r="F36" t="n">
-        <v>14.96</v>
+        <v>14.17</v>
       </c>
       <c r="G36" t="n">
-        <v>320.1</v>
+        <v>328.4</v>
       </c>
       <c r="H36" t="n">
-        <v>78.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>20.11</v>
+        <v>-96.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-214.78</v>
+        <v>201.87</v>
       </c>
       <c r="L36" t="n">
-        <v>215.72</v>
+        <v>223.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:45:49</t>
+          <t>06:47:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.52</v>
+        <v>5.58</v>
       </c>
       <c r="F37" t="n">
-        <v>9.949999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="G37" t="n">
-        <v>313.3</v>
+        <v>318.5</v>
       </c>
       <c r="H37" t="n">
-        <v>78.40000000000001</v>
+        <v>57</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>106.17</v>
+        <v>173.69</v>
       </c>
       <c r="K37" t="n">
-        <v>-132.84</v>
+        <v>48.05</v>
       </c>
       <c r="L37" t="n">
-        <v>170.06</v>
+        <v>180.21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:49:37</t>
+          <t>06:51:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.24</v>
+        <v>6.04</v>
       </c>
       <c r="F38" t="n">
-        <v>15.04</v>
+        <v>15.3</v>
       </c>
       <c r="G38" t="n">
-        <v>319.5</v>
+        <v>318.2</v>
       </c>
       <c r="H38" t="n">
-        <v>76</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>203.47</v>
+        <v>-234.85</v>
       </c>
       <c r="K38" t="n">
-        <v>106.03</v>
+        <v>174.09</v>
       </c>
       <c r="L38" t="n">
-        <v>229.44</v>
+        <v>292.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:51:06</t>
+          <t>06:52:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.37</v>
+        <v>6.46</v>
       </c>
       <c r="F39" t="n">
-        <v>12.43</v>
+        <v>14.68</v>
       </c>
       <c r="G39" t="n">
-        <v>337.9</v>
+        <v>325.5</v>
       </c>
       <c r="H39" t="n">
-        <v>81</v>
+        <v>26.8</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>86</v>
+        <v>-4.15</v>
       </c>
       <c r="K39" t="n">
-        <v>244.99</v>
+        <v>265.16</v>
       </c>
       <c r="L39" t="n">
-        <v>259.64</v>
+        <v>265.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:53:01</t>
+          <t>06:54:03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.59</v>
+        <v>6.12</v>
       </c>
       <c r="F40" t="n">
-        <v>17.26</v>
+        <v>16.24</v>
       </c>
       <c r="G40" t="n">
-        <v>317.4</v>
+        <v>315.4</v>
       </c>
       <c r="H40" t="n">
-        <v>82.8</v>
+        <v>64.2</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>107.56</v>
+        <v>136.82</v>
       </c>
       <c r="K40" t="n">
-        <v>179.55</v>
+        <v>286.77</v>
       </c>
       <c r="L40" t="n">
-        <v>209.31</v>
+        <v>317.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:57:43</t>
+          <t>06:58:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6.19</v>
+        <v>5.58</v>
       </c>
       <c r="F41" t="n">
-        <v>16.99</v>
+        <v>12.16</v>
       </c>
       <c r="G41" t="n">
-        <v>324.5</v>
+        <v>322.9</v>
       </c>
       <c r="H41" t="n">
-        <v>78.7</v>
+        <v>59.6</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>220.51</v>
+        <v>-142.73</v>
       </c>
       <c r="K41" t="n">
-        <v>11.94</v>
+        <v>-229.95</v>
       </c>
       <c r="L41" t="n">
-        <v>220.83</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:59:27</t>
+          <t>07:00:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.66</v>
+        <v>5.63</v>
       </c>
       <c r="F42" t="n">
-        <v>12.7</v>
+        <v>15.55</v>
       </c>
       <c r="G42" t="n">
-        <v>337.6</v>
+        <v>323.2</v>
       </c>
       <c r="H42" t="n">
-        <v>83.90000000000001</v>
+        <v>15.4</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>134.57</v>
+        <v>273.01</v>
       </c>
       <c r="K42" t="n">
-        <v>595.1900000000001</v>
+        <v>225.55</v>
       </c>
       <c r="L42" t="n">
-        <v>610.22</v>
+        <v>354.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:00:17</t>
+          <t>07:02:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="F43" t="n">
-        <v>15.77</v>
+        <v>14.62</v>
       </c>
       <c r="G43" t="n">
-        <v>334.7</v>
+        <v>327.1</v>
       </c>
       <c r="H43" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>226.19</v>
+        <v>102.35</v>
       </c>
       <c r="K43" t="n">
-        <v>304.65</v>
+        <v>279.31</v>
       </c>
       <c r="L43" t="n">
-        <v>379.44</v>
+        <v>297.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:11:09</t>
+          <t>07:14:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.18</v>
+        <v>6.2</v>
       </c>
       <c r="F44" t="n">
-        <v>12.39</v>
+        <v>15.71</v>
       </c>
       <c r="G44" t="n">
-        <v>318.7</v>
+        <v>319.1</v>
       </c>
       <c r="H44" t="n">
-        <v>78.3</v>
+        <v>15.6</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>84.33</v>
+        <v>129.19</v>
       </c>
       <c r="K44" t="n">
-        <v>28.16</v>
+        <v>-3.02</v>
       </c>
       <c r="L44" t="n">
-        <v>88.91</v>
+        <v>129.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:12:37</t>
+          <t>07:16:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.82</v>
+        <v>4.46</v>
       </c>
       <c r="F45" t="n">
-        <v>17.36</v>
+        <v>13.15</v>
       </c>
       <c r="G45" t="n">
-        <v>336.9</v>
+        <v>322.2</v>
       </c>
       <c r="H45" t="n">
-        <v>78.3</v>
+        <v>63.6</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-108.11</v>
+        <v>50.26</v>
       </c>
       <c r="K45" t="n">
-        <v>-34.41</v>
+        <v>-68.86</v>
       </c>
       <c r="L45" t="n">
-        <v>113.45</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:14:42</t>
+          <t>07:18:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="F46" t="n">
-        <v>17.36</v>
+        <v>17.13</v>
       </c>
       <c r="G46" t="n">
-        <v>320.1</v>
+        <v>326.5</v>
       </c>
       <c r="H46" t="n">
-        <v>83.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="I46" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-43.98</v>
+        <v>17.21</v>
       </c>
       <c r="K46" t="n">
-        <v>-38.44</v>
+        <v>166.36</v>
       </c>
       <c r="L46" t="n">
-        <v>58.41</v>
+        <v>167.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:20:32</t>
+          <t>07:23:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.45</v>
+        <v>5.17</v>
       </c>
       <c r="F47" t="n">
-        <v>17.36</v>
+        <v>13.21</v>
       </c>
       <c r="G47" t="n">
-        <v>328.3</v>
+        <v>317.3</v>
       </c>
       <c r="H47" t="n">
-        <v>79.5</v>
+        <v>72.3</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>113.53</v>
+        <v>-116.85</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.96</v>
+        <v>131.03</v>
       </c>
       <c r="L47" t="n">
-        <v>113.75</v>
+        <v>175.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:21:43</t>
+          <t>07:25:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.17</v>
+        <v>5.29</v>
       </c>
       <c r="F48" t="n">
-        <v>13.15</v>
+        <v>14.63</v>
       </c>
       <c r="G48" t="n">
-        <v>323.5</v>
+        <v>325.1</v>
       </c>
       <c r="H48" t="n">
-        <v>75.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-65.25</v>
+        <v>-134.98</v>
       </c>
       <c r="K48" t="n">
-        <v>65.05</v>
+        <v>48.27</v>
       </c>
       <c r="L48" t="n">
-        <v>92.14</v>
+        <v>143.35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:23:01</t>
+          <t>07:28:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.08</v>
+        <v>6.3</v>
       </c>
       <c r="F49" t="n">
-        <v>15.33</v>
+        <v>17.36</v>
       </c>
       <c r="G49" t="n">
-        <v>335.8</v>
+        <v>322.2</v>
       </c>
       <c r="H49" t="n">
-        <v>77.2</v>
+        <v>28.5</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-35.08</v>
+        <v>12.66</v>
       </c>
       <c r="K49" t="n">
-        <v>112.97</v>
+        <v>-167.12</v>
       </c>
       <c r="L49" t="n">
-        <v>118.29</v>
+        <v>167.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:27:53</t>
+          <t>07:33:09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.57</v>
+        <v>5.92</v>
       </c>
       <c r="F50" t="n">
-        <v>12.4</v>
+        <v>15.22</v>
       </c>
       <c r="G50" t="n">
-        <v>327.5</v>
+        <v>315.4</v>
       </c>
       <c r="H50" t="n">
-        <v>71.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-121.59</v>
+        <v>151.15</v>
       </c>
       <c r="K50" t="n">
-        <v>-83.17</v>
+        <v>-137.8</v>
       </c>
       <c r="L50" t="n">
-        <v>147.31</v>
+        <v>204.54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:29:23</t>
+          <t>07:35:03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.23</v>
+        <v>6.81</v>
       </c>
       <c r="F51" t="n">
-        <v>15.26</v>
+        <v>17.36</v>
       </c>
       <c r="G51" t="n">
-        <v>330.3</v>
+        <v>324.7</v>
       </c>
       <c r="H51" t="n">
-        <v>83.7</v>
+        <v>51.9</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-104.42</v>
+        <v>-192.56</v>
       </c>
       <c r="K51" t="n">
-        <v>130.73</v>
+        <v>-37.42</v>
       </c>
       <c r="L51" t="n">
-        <v>167.31</v>
+        <v>196.17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:30:50</t>
+          <t>07:36:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.64</v>
+        <v>5.46</v>
       </c>
       <c r="F52" t="n">
-        <v>17.36</v>
+        <v>14.05</v>
       </c>
       <c r="G52" t="n">
-        <v>343</v>
+        <v>337.6</v>
       </c>
       <c r="H52" t="n">
-        <v>77.09999999999999</v>
+        <v>34.3</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>61.74</v>
+        <v>200.53</v>
       </c>
       <c r="K52" t="n">
-        <v>115.23</v>
+        <v>74.84</v>
       </c>
       <c r="L52" t="n">
-        <v>130.73</v>
+        <v>214.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:33:45</t>
+          <t>07:39:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="F53" t="n">
-        <v>16.29</v>
+        <v>15.57</v>
       </c>
       <c r="G53" t="n">
-        <v>309.6</v>
+        <v>326.5</v>
       </c>
       <c r="H53" t="n">
-        <v>77.8</v>
+        <v>57.9</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>195.33</v>
+        <v>-39.11</v>
       </c>
       <c r="K53" t="n">
-        <v>8.91</v>
+        <v>288.74</v>
       </c>
       <c r="L53" t="n">
-        <v>195.54</v>
+        <v>291.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:35:58</t>
+          <t>07:41:42</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.89</v>
+        <v>5.58</v>
       </c>
       <c r="F54" t="n">
-        <v>15.24</v>
+        <v>14.75</v>
       </c>
       <c r="G54" t="n">
-        <v>335.9</v>
+        <v>323.3</v>
       </c>
       <c r="H54" t="n">
-        <v>80.3</v>
+        <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-143.7</v>
+        <v>37.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-260.57</v>
+        <v>104.5</v>
       </c>
       <c r="L54" t="n">
-        <v>297.57</v>
+        <v>111.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:38:37</t>
+          <t>07:43:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.69</v>
+        <v>5.39</v>
       </c>
       <c r="F55" t="n">
-        <v>14.43</v>
+        <v>17.36</v>
       </c>
       <c r="G55" t="n">
-        <v>318.8</v>
+        <v>320.4</v>
       </c>
       <c r="H55" t="n">
-        <v>75.09999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>198.49</v>
+        <v>48.8</v>
       </c>
       <c r="K55" t="n">
-        <v>150.98</v>
+        <v>249.4</v>
       </c>
       <c r="L55" t="n">
-        <v>249.38</v>
+        <v>254.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:43:43</t>
+          <t>07:48:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.52</v>
+        <v>5.56</v>
       </c>
       <c r="F56" t="n">
-        <v>14.61</v>
+        <v>16.6</v>
       </c>
       <c r="G56" t="n">
-        <v>324.8</v>
+        <v>335.7</v>
       </c>
       <c r="H56" t="n">
-        <v>74.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-465.45</v>
+        <v>311.2</v>
       </c>
       <c r="K56" t="n">
-        <v>-113.8</v>
+        <v>298.03</v>
       </c>
       <c r="L56" t="n">
-        <v>479.16</v>
+        <v>430.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:44:33</t>
+          <t>07:49:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.82</v>
+        <v>6.18</v>
       </c>
       <c r="F57" t="n">
-        <v>16.67</v>
+        <v>16.57</v>
       </c>
       <c r="G57" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H57" t="n">
-        <v>77.8</v>
+        <v>44.4</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>54.48</v>
+        <v>-329.34</v>
       </c>
       <c r="K57" t="n">
-        <v>439.46</v>
+        <v>-263.07</v>
       </c>
       <c r="L57" t="n">
-        <v>442.82</v>
+        <v>421.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:46:12</t>
+          <t>07:51:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.19</v>
+        <v>6.26</v>
       </c>
       <c r="F58" t="n">
-        <v>14.13</v>
+        <v>16.55</v>
       </c>
       <c r="G58" t="n">
-        <v>344</v>
+        <v>322.5</v>
       </c>
       <c r="H58" t="n">
-        <v>78.2</v>
+        <v>47.7</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-127.17</v>
+        <v>12.6</v>
       </c>
       <c r="K58" t="n">
-        <v>272.01</v>
+        <v>507.75</v>
       </c>
       <c r="L58" t="n">
-        <v>300.27</v>
+        <v>507.91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:55:31</t>
+          <t>08:03:09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="F59" t="n">
-        <v>17.29</v>
+        <v>11.68</v>
       </c>
       <c r="G59" t="n">
-        <v>336.8</v>
+        <v>304</v>
       </c>
       <c r="H59" t="n">
-        <v>82.3</v>
+        <v>59.7</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-106.73</v>
+        <v>14.05</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.22</v>
+        <v>102.68</v>
       </c>
       <c r="L59" t="n">
-        <v>106.85</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:56:59</t>
+          <t>08:05:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.12</v>
+        <v>5.71</v>
       </c>
       <c r="F60" t="n">
-        <v>13.47</v>
+        <v>13.97</v>
       </c>
       <c r="G60" t="n">
-        <v>333.6</v>
+        <v>328.4</v>
       </c>
       <c r="H60" t="n">
-        <v>73.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>22.81</v>
+        <v>-127.77</v>
       </c>
       <c r="K60" t="n">
-        <v>70.29000000000001</v>
+        <v>42.99</v>
       </c>
       <c r="L60" t="n">
-        <v>73.90000000000001</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:59:26</t>
+          <t>08:06:08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.13</v>
+        <v>5.33</v>
       </c>
       <c r="F61" t="n">
-        <v>16.53</v>
+        <v>10.58</v>
       </c>
       <c r="G61" t="n">
-        <v>330.6</v>
+        <v>328</v>
       </c>
       <c r="H61" t="n">
-        <v>71.3</v>
+        <v>73.5</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>57.79</v>
+        <v>-109.53</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.36</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>65.75</v>
+        <v>127.72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:03:23</t>
+          <t>08:10:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.11</v>
+        <v>6.07</v>
       </c>
       <c r="F62" t="n">
-        <v>15.49</v>
+        <v>17.36</v>
       </c>
       <c r="G62" t="n">
-        <v>330.8</v>
+        <v>329.3</v>
       </c>
       <c r="H62" t="n">
-        <v>77.7</v>
+        <v>41.8</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-90.48</v>
+        <v>28.37</v>
       </c>
       <c r="K62" t="n">
-        <v>-101.06</v>
+        <v>230.24</v>
       </c>
       <c r="L62" t="n">
-        <v>135.65</v>
+        <v>231.98</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:05:24</t>
+          <t>08:12:47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.47</v>
+        <v>4.95</v>
       </c>
       <c r="F63" t="n">
-        <v>17.05</v>
+        <v>11.2</v>
       </c>
       <c r="G63" t="n">
-        <v>338.5</v>
+        <v>323.8</v>
       </c>
       <c r="H63" t="n">
-        <v>72.2</v>
+        <v>30.3</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-108.67</v>
+        <v>-29.99</v>
       </c>
       <c r="K63" t="n">
-        <v>-58.42</v>
+        <v>156.8</v>
       </c>
       <c r="L63" t="n">
-        <v>123.38</v>
+        <v>159.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:06:52</t>
+          <t>08:14:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="F64" t="n">
-        <v>13.75</v>
+        <v>14.08</v>
       </c>
       <c r="G64" t="n">
-        <v>308.6</v>
+        <v>319.6</v>
       </c>
       <c r="H64" t="n">
-        <v>76.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>20.53</v>
+        <v>35.11</v>
       </c>
       <c r="K64" t="n">
-        <v>90.25</v>
+        <v>139.18</v>
       </c>
       <c r="L64" t="n">
-        <v>92.56</v>
+        <v>143.54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:11:34</t>
+          <t>08:21:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.99</v>
+        <v>5.4</v>
       </c>
       <c r="F65" t="n">
-        <v>14.96</v>
+        <v>14.19</v>
       </c>
       <c r="G65" t="n">
-        <v>314.2</v>
+        <v>323.5</v>
       </c>
       <c r="H65" t="n">
-        <v>76.09999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="I65" t="n">
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-214.91</v>
+        <v>-68.98</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.68</v>
+        <v>211.55</v>
       </c>
       <c r="L65" t="n">
-        <v>215.08</v>
+        <v>222.51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:13:16</t>
+          <t>08:22:12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.43</v>
+        <v>5.55</v>
       </c>
       <c r="F66" t="n">
-        <v>16.5</v>
+        <v>12.91</v>
       </c>
       <c r="G66" t="n">
-        <v>322.9</v>
+        <v>324.3</v>
       </c>
       <c r="H66" t="n">
-        <v>73.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="I66" t="n">
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-113.39</v>
+        <v>-154.33</v>
       </c>
       <c r="K66" t="n">
-        <v>77.91</v>
+        <v>-79.11</v>
       </c>
       <c r="L66" t="n">
-        <v>137.58</v>
+        <v>173.42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:14:20</t>
+          <t>08:23:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.78</v>
+        <v>7.48</v>
       </c>
       <c r="F67" t="n">
-        <v>13.81</v>
+        <v>17.36</v>
       </c>
       <c r="G67" t="n">
-        <v>325.8</v>
+        <v>309.3</v>
       </c>
       <c r="H67" t="n">
-        <v>74.09999999999999</v>
+        <v>32</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-59.73</v>
+        <v>217.08</v>
       </c>
       <c r="K67" t="n">
-        <v>-141.58</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>153.66</v>
+        <v>230.35</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:18:32</t>
+          <t>08:27:23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.53</v>
+        <v>6.37</v>
       </c>
       <c r="F68" t="n">
-        <v>13.97</v>
+        <v>17.36</v>
       </c>
       <c r="G68" t="n">
-        <v>326.9</v>
+        <v>313</v>
       </c>
       <c r="H68" t="n">
-        <v>80.59999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>187.07</v>
+        <v>-336.75</v>
       </c>
       <c r="K68" t="n">
-        <v>166.75</v>
+        <v>244.07</v>
       </c>
       <c r="L68" t="n">
-        <v>250.6</v>
+        <v>415.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:20:33</t>
+          <t>08:29:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.35</v>
+        <v>5.84</v>
       </c>
       <c r="F69" t="n">
-        <v>12.31</v>
+        <v>15.54</v>
       </c>
       <c r="G69" t="n">
-        <v>311.5</v>
+        <v>330.5</v>
       </c>
       <c r="H69" t="n">
-        <v>79.8</v>
+        <v>64.2</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>55.47</v>
+        <v>-208.44</v>
       </c>
       <c r="K69" t="n">
-        <v>286.75</v>
+        <v>277.9</v>
       </c>
       <c r="L69" t="n">
-        <v>292.07</v>
+        <v>347.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:22:16</t>
+          <t>08:31:19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.48</v>
+        <v>6.18</v>
       </c>
       <c r="F70" t="n">
-        <v>17.36</v>
+        <v>15.86</v>
       </c>
       <c r="G70" t="n">
-        <v>322.1</v>
+        <v>338.4</v>
       </c>
       <c r="H70" t="n">
-        <v>78</v>
+        <v>65.7</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-376.21</v>
+        <v>278.81</v>
       </c>
       <c r="K70" t="n">
-        <v>42.18</v>
+        <v>-64.75</v>
       </c>
       <c r="L70" t="n">
-        <v>378.56</v>
+        <v>286.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:25:28</t>
+          <t>08:36:03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.29</v>
+        <v>6.75</v>
       </c>
       <c r="F71" t="n">
-        <v>16.21</v>
+        <v>17.36</v>
       </c>
       <c r="G71" t="n">
-        <v>332.7</v>
+        <v>314.2</v>
       </c>
       <c r="H71" t="n">
-        <v>75.40000000000001</v>
+        <v>43.7</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>390.66</v>
+        <v>-273.11</v>
       </c>
       <c r="K71" t="n">
-        <v>187.3</v>
+        <v>-304.32</v>
       </c>
       <c r="L71" t="n">
-        <v>433.24</v>
+        <v>408.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:26:32</t>
+          <t>08:37:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.46</v>
+        <v>6.55</v>
       </c>
       <c r="F72" t="n">
-        <v>16.8</v>
+        <v>14.33</v>
       </c>
       <c r="G72" t="n">
-        <v>312.9</v>
+        <v>325.3</v>
       </c>
       <c r="H72" t="n">
-        <v>72.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-463.18</v>
+        <v>-202.73</v>
       </c>
       <c r="K72" t="n">
-        <v>431.42</v>
+        <v>269.77</v>
       </c>
       <c r="L72" t="n">
-        <v>632.98</v>
+        <v>337.46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:27:27</t>
+          <t>08:38:40</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.78</v>
+        <v>6.34</v>
       </c>
       <c r="F73" t="n">
         <v>17.36</v>
       </c>
       <c r="G73" t="n">
-        <v>320.5</v>
+        <v>324.4</v>
       </c>
       <c r="H73" t="n">
-        <v>81.59999999999999</v>
+        <v>51.2</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-538.7</v>
+        <v>-416.16</v>
       </c>
       <c r="K73" t="n">
-        <v>51.56</v>
+        <v>-62.08</v>
       </c>
       <c r="L73" t="n">
-        <v>541.16</v>
+        <v>420.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:36:11</t>
+          <t>08:50:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.21</v>
+        <v>5.98</v>
       </c>
       <c r="F74" t="n">
-        <v>13.66</v>
+        <v>14.63</v>
       </c>
       <c r="G74" t="n">
-        <v>323.5</v>
+        <v>319.9</v>
       </c>
       <c r="H74" t="n">
-        <v>74.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1</v>
+        <v>139.87</v>
       </c>
       <c r="K74" t="n">
-        <v>75.58</v>
+        <v>-75.88</v>
       </c>
       <c r="L74" t="n">
-        <v>75.58</v>
+        <v>159.12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:37:55</t>
+          <t>08:51:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.57</v>
+        <v>6.7</v>
       </c>
       <c r="F75" t="n">
-        <v>15.45</v>
+        <v>17.36</v>
       </c>
       <c r="G75" t="n">
-        <v>319.1</v>
+        <v>313.4</v>
       </c>
       <c r="H75" t="n">
-        <v>76.09999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>40.68</v>
+        <v>-37.05</v>
       </c>
       <c r="K75" t="n">
-        <v>-64.33</v>
+        <v>-2.82</v>
       </c>
       <c r="L75" t="n">
-        <v>76.12</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:38:21</t>
+          <t>08:53:31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.44</v>
+        <v>6.44</v>
       </c>
       <c r="F76" t="n">
-        <v>15.95</v>
+        <v>15.8</v>
       </c>
       <c r="G76" t="n">
-        <v>334.4</v>
+        <v>342.4</v>
       </c>
       <c r="H76" t="n">
-        <v>80.2</v>
+        <v>50.7</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-54.22</v>
+        <v>109.6</v>
       </c>
       <c r="K76" t="n">
-        <v>11.26</v>
+        <v>-18.32</v>
       </c>
       <c r="L76" t="n">
-        <v>55.37</v>
+        <v>111.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:43:09</t>
+          <t>08:58:53</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.51</v>
+        <v>6.62</v>
       </c>
       <c r="F77" t="n">
-        <v>14.9</v>
+        <v>17.36</v>
       </c>
       <c r="G77" t="n">
-        <v>313.8</v>
+        <v>321.1</v>
       </c>
       <c r="H77" t="n">
-        <v>76.59999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>57.87</v>
+        <v>201.4</v>
       </c>
       <c r="K77" t="n">
-        <v>-63.16</v>
+        <v>9.23</v>
       </c>
       <c r="L77" t="n">
-        <v>85.67</v>
+        <v>201.61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:45:37</t>
+          <t>09:01:23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.79</v>
+        <v>6.12</v>
       </c>
       <c r="F78" t="n">
-        <v>14.31</v>
+        <v>16.19</v>
       </c>
       <c r="G78" t="n">
-        <v>314.7</v>
+        <v>319</v>
       </c>
       <c r="H78" t="n">
-        <v>80.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-90.05</v>
+        <v>-143.38</v>
       </c>
       <c r="K78" t="n">
-        <v>27.28</v>
+        <v>30.17</v>
       </c>
       <c r="L78" t="n">
-        <v>94.09</v>
+        <v>146.52</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:47:13</t>
+          <t>09:02:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.89</v>
+        <v>6.16</v>
       </c>
       <c r="F79" t="n">
         <v>17.36</v>
       </c>
       <c r="G79" t="n">
-        <v>322.3</v>
+        <v>324.6</v>
       </c>
       <c r="H79" t="n">
-        <v>73.40000000000001</v>
+        <v>43.9</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.39</v>
+        <v>-216.65</v>
       </c>
       <c r="K79" t="n">
-        <v>100.63</v>
+        <v>56.43</v>
       </c>
       <c r="L79" t="n">
-        <v>101.52</v>
+        <v>223.88</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:51:23</t>
+          <t>09:07:38</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.06</v>
+        <v>5.64</v>
       </c>
       <c r="F80" t="n">
-        <v>17.19</v>
+        <v>14.84</v>
       </c>
       <c r="G80" t="n">
-        <v>313.3</v>
+        <v>324.4</v>
       </c>
       <c r="H80" t="n">
-        <v>78.40000000000001</v>
+        <v>33.2</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>100.9</v>
+        <v>-86.06</v>
       </c>
       <c r="K80" t="n">
-        <v>165.92</v>
+        <v>-180.84</v>
       </c>
       <c r="L80" t="n">
-        <v>194.19</v>
+        <v>200.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:52:46</t>
+          <t>09:10:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>7.32</v>
+        <v>6</v>
       </c>
       <c r="F81" t="n">
-        <v>17.36</v>
+        <v>15.29</v>
       </c>
       <c r="G81" t="n">
-        <v>320.8</v>
+        <v>319.9</v>
       </c>
       <c r="H81" t="n">
-        <v>73.2</v>
+        <v>41</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>-187.01</v>
+        <v>-182.15</v>
       </c>
       <c r="K81" t="n">
-        <v>70.09</v>
+        <v>143.83</v>
       </c>
       <c r="L81" t="n">
-        <v>199.71</v>
+        <v>232.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:55:21</t>
+          <t>09:12:33</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.56</v>
+        <v>6.44</v>
       </c>
       <c r="F82" t="n">
-        <v>17.36</v>
+        <v>16.28</v>
       </c>
       <c r="G82" t="n">
-        <v>323.7</v>
+        <v>315.7</v>
       </c>
       <c r="H82" t="n">
-        <v>78</v>
+        <v>36.2</v>
       </c>
       <c r="I82" t="n">
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>59.85</v>
+        <v>81.77</v>
       </c>
       <c r="K82" t="n">
-        <v>-144.29</v>
+        <v>221.9</v>
       </c>
       <c r="L82" t="n">
-        <v>156.21</v>
+        <v>236.48</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:59:22</t>
+          <t>09:16:15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.24</v>
+        <v>5.5</v>
       </c>
       <c r="F83" t="n">
-        <v>17.04</v>
+        <v>15.13</v>
       </c>
       <c r="G83" t="n">
-        <v>319.4</v>
+        <v>313.2</v>
       </c>
       <c r="H83" t="n">
-        <v>74.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-64.29000000000001</v>
+        <v>-264.31</v>
       </c>
       <c r="K83" t="n">
-        <v>-392.06</v>
+        <v>36.24</v>
       </c>
       <c r="L83" t="n">
-        <v>397.29</v>
+        <v>266.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:01:37</t>
+          <t>09:18:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.32</v>
+        <v>6.21</v>
       </c>
       <c r="F84" t="n">
-        <v>14.83</v>
+        <v>15.87</v>
       </c>
       <c r="G84" t="n">
-        <v>332.6</v>
+        <v>318.7</v>
       </c>
       <c r="H84" t="n">
-        <v>73.3</v>
+        <v>59.9</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-176.41</v>
+        <v>-364.57</v>
       </c>
       <c r="K84" t="n">
-        <v>-98.91</v>
+        <v>26.11</v>
       </c>
       <c r="L84" t="n">
-        <v>202.24</v>
+        <v>365.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:03:33</t>
+          <t>09:20:31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>7.12</v>
+        <v>5.79</v>
       </c>
       <c r="F85" t="n">
         <v>17.36</v>
       </c>
       <c r="G85" t="n">
-        <v>320</v>
+        <v>340.5</v>
       </c>
       <c r="H85" t="n">
-        <v>68.8</v>
+        <v>44.4</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-51.39</v>
+        <v>-157.14</v>
       </c>
       <c r="K85" t="n">
-        <v>494.11</v>
+        <v>187.42</v>
       </c>
       <c r="L85" t="n">
-        <v>496.77</v>
+        <v>244.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:07:31</t>
+          <t>09:24:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.95</v>
+        <v>6.32</v>
       </c>
       <c r="F86" t="n">
-        <v>17.36</v>
+        <v>16.09</v>
       </c>
       <c r="G86" t="n">
-        <v>327.4</v>
+        <v>333.1</v>
       </c>
       <c r="H86" t="n">
-        <v>76.8</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-614.54</v>
+        <v>461.44</v>
       </c>
       <c r="K86" t="n">
-        <v>192.66</v>
+        <v>160.61</v>
       </c>
       <c r="L86" t="n">
-        <v>644.03</v>
+        <v>488.59</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:09:30</t>
+          <t>09:26:09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.43</v>
+        <v>6.05</v>
       </c>
       <c r="F87" t="n">
-        <v>17.36</v>
+        <v>14.57</v>
       </c>
       <c r="G87" t="n">
-        <v>336.5</v>
+        <v>319.2</v>
       </c>
       <c r="H87" t="n">
-        <v>72.7</v>
+        <v>58.2</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-116.29</v>
+        <v>359.5</v>
       </c>
       <c r="K87" t="n">
-        <v>455.73</v>
+        <v>235.19</v>
       </c>
       <c r="L87" t="n">
-        <v>470.33</v>
+        <v>429.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:10:58</t>
+          <t>09:27:59</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.98</v>
+        <v>6.97</v>
       </c>
       <c r="F88" t="n">
-        <v>15.93</v>
+        <v>17.36</v>
       </c>
       <c r="G88" t="n">
-        <v>323.4</v>
+        <v>330.1</v>
       </c>
       <c r="H88" t="n">
-        <v>76.7</v>
+        <v>92.3</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>521.45</v>
+        <v>-359.12</v>
       </c>
       <c r="K88" t="n">
-        <v>-134.37</v>
+        <v>388.49</v>
       </c>
       <c r="L88" t="n">
-        <v>538.48</v>
+        <v>529.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>6.37</v>
+        <v>5.34</v>
       </c>
       <c r="F14" t="n">
-        <v>14.45</v>
+        <v>13.38</v>
       </c>
       <c r="G14" t="n">
-        <v>314.6</v>
+        <v>322.5</v>
       </c>
       <c r="H14" t="n">
-        <v>42.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.44</v>
+        <v>27.9</v>
       </c>
       <c r="K14" t="n">
-        <v>142.59</v>
+        <v>109.28</v>
       </c>
       <c r="L14" t="n">
-        <v>142.63</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:44:24</t>
+          <t>05:43:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="n">
-        <v>14.37</v>
+        <v>15.28</v>
       </c>
       <c r="G15" t="n">
-        <v>324.3</v>
+        <v>315</v>
       </c>
       <c r="H15" t="n">
-        <v>61.9</v>
+        <v>68.7</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>-112.56</v>
+        <v>-54.16</v>
       </c>
       <c r="K15" t="n">
-        <v>-43.17</v>
+        <v>-71.81</v>
       </c>
       <c r="L15" t="n">
-        <v>120.56</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:45:35</t>
+          <t>05:44:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.98</v>
+        <v>5.86</v>
       </c>
       <c r="F16" t="n">
-        <v>8.27</v>
+        <v>14.9</v>
       </c>
       <c r="G16" t="n">
-        <v>323.4</v>
+        <v>330.9</v>
       </c>
       <c r="H16" t="n">
-        <v>96.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>82.54000000000001</v>
+        <v>6.97</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.6</v>
+        <v>141.84</v>
       </c>
       <c r="L16" t="n">
-        <v>95.28</v>
+        <v>142.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:50:18</t>
+          <t>05:50:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.75</v>
+        <v>5.55</v>
       </c>
       <c r="F17" t="n">
-        <v>11.48</v>
+        <v>12.09</v>
       </c>
       <c r="G17" t="n">
-        <v>323.6</v>
+        <v>333.4</v>
       </c>
       <c r="H17" t="n">
-        <v>40.1</v>
+        <v>46.9</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-68.78</v>
+        <v>-393.95</v>
       </c>
       <c r="K17" t="n">
-        <v>91.53</v>
+        <v>177.08</v>
       </c>
       <c r="L17" t="n">
-        <v>114.5</v>
+        <v>431.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:51:56</t>
+          <t>05:52:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.77</v>
+        <v>5.23</v>
       </c>
       <c r="F18" t="n">
-        <v>12.41</v>
+        <v>14.31</v>
       </c>
       <c r="G18" t="n">
-        <v>313.2</v>
+        <v>319.8</v>
       </c>
       <c r="H18" t="n">
-        <v>66.90000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>-55.55</v>
+        <v>125.45</v>
       </c>
       <c r="K18" t="n">
-        <v>137.03</v>
+        <v>90.94</v>
       </c>
       <c r="L18" t="n">
-        <v>147.86</v>
+        <v>154.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:54:24</t>
+          <t>05:53:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.41</v>
+        <v>5.64</v>
       </c>
       <c r="F19" t="n">
-        <v>15.3</v>
+        <v>16.04</v>
       </c>
       <c r="G19" t="n">
-        <v>321.4</v>
+        <v>317.1</v>
       </c>
       <c r="H19" t="n">
-        <v>76.09999999999999</v>
+        <v>52</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-153.18</v>
+        <v>20.09</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.9</v>
+        <v>151.37</v>
       </c>
       <c r="L19" t="n">
-        <v>154.34</v>
+        <v>152.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:58:17</t>
+          <t>05:57:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6.34</v>
+        <v>5.44</v>
       </c>
       <c r="F20" t="n">
-        <v>15.83</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>321.5</v>
+        <v>313.2</v>
       </c>
       <c r="H20" t="n">
-        <v>56.4</v>
+        <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.95</v>
+        <v>-23.58</v>
       </c>
       <c r="K20" t="n">
-        <v>54.52</v>
+        <v>138.69</v>
       </c>
       <c r="L20" t="n">
-        <v>152.99</v>
+        <v>140.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:59:36</t>
+          <t>05:58:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.05</v>
+        <v>4.77</v>
       </c>
       <c r="F21" t="n">
-        <v>11.21</v>
+        <v>12.4</v>
       </c>
       <c r="G21" t="n">
-        <v>329.9</v>
+        <v>315.3</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>-117.5</v>
+        <v>-51.48</v>
       </c>
       <c r="K21" t="n">
-        <v>165.08</v>
+        <v>-138.27</v>
       </c>
       <c r="L21" t="n">
-        <v>202.62</v>
+        <v>147.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:01:35</t>
+          <t>06:00:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.65</v>
+        <v>4.7</v>
       </c>
       <c r="F22" t="n">
-        <v>17.36</v>
+        <v>12.27</v>
       </c>
       <c r="G22" t="n">
-        <v>322.6</v>
+        <v>332.2</v>
       </c>
       <c r="H22" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-8.92</v>
+        <v>-87.12</v>
       </c>
       <c r="K22" t="n">
-        <v>168.34</v>
+        <v>67.09</v>
       </c>
       <c r="L22" t="n">
-        <v>168.58</v>
+        <v>109.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:05:11</t>
+          <t>06:04:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.34</v>
+        <v>4.95</v>
       </c>
       <c r="F23" t="n">
-        <v>10.69</v>
+        <v>13.07</v>
       </c>
       <c r="G23" t="n">
-        <v>335.4</v>
+        <v>329.9</v>
       </c>
       <c r="H23" t="n">
-        <v>29</v>
+        <v>53.1</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-112.28</v>
+        <v>219.69</v>
       </c>
       <c r="K23" t="n">
-        <v>-138.22</v>
+        <v>239.12</v>
       </c>
       <c r="L23" t="n">
-        <v>178.08</v>
+        <v>324.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:06:25</t>
+          <t>06:06:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.55</v>
+        <v>6.1</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1</v>
+        <v>16.03</v>
       </c>
       <c r="G24" t="n">
-        <v>334.2</v>
+        <v>320.9</v>
       </c>
       <c r="H24" t="n">
-        <v>66.90000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>-372.98</v>
+        <v>-318.67</v>
       </c>
       <c r="K24" t="n">
-        <v>-58.72</v>
+        <v>-60.37</v>
       </c>
       <c r="L24" t="n">
-        <v>377.57</v>
+        <v>324.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:07:54</t>
+          <t>06:08:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="F25" t="n">
-        <v>16.4</v>
+        <v>13.54</v>
       </c>
       <c r="G25" t="n">
-        <v>317.9</v>
+        <v>320.2</v>
       </c>
       <c r="H25" t="n">
-        <v>55.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>175.16</v>
+        <v>249.19</v>
       </c>
       <c r="K25" t="n">
-        <v>144.82</v>
+        <v>29</v>
       </c>
       <c r="L25" t="n">
-        <v>227.27</v>
+        <v>250.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:12:19</t>
+          <t>06:12:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.41</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>12.77</v>
+        <v>16.38</v>
       </c>
       <c r="G26" t="n">
-        <v>322.9</v>
+        <v>316.6</v>
       </c>
       <c r="H26" t="n">
-        <v>26.3</v>
+        <v>59.7</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>315.92</v>
+        <v>386.98</v>
       </c>
       <c r="K26" t="n">
-        <v>58.52</v>
+        <v>-52.33</v>
       </c>
       <c r="L26" t="n">
-        <v>321.29</v>
+        <v>390.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:14:21</t>
+          <t>06:13:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.77</v>
+        <v>6.57</v>
       </c>
       <c r="F27" t="n">
-        <v>16.38</v>
+        <v>15.13</v>
       </c>
       <c r="G27" t="n">
-        <v>327.7</v>
+        <v>318.1</v>
       </c>
       <c r="H27" t="n">
-        <v>63</v>
+        <v>78.7</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>-115.67</v>
+        <v>454.28</v>
       </c>
       <c r="K27" t="n">
-        <v>425.09</v>
+        <v>-56.89</v>
       </c>
       <c r="L27" t="n">
-        <v>440.54</v>
+        <v>457.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:16:14</t>
+          <t>06:15:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.57</v>
+        <v>4.35</v>
       </c>
       <c r="F28" t="n">
-        <v>12.38</v>
+        <v>12.19</v>
       </c>
       <c r="G28" t="n">
-        <v>325.2</v>
+        <v>326.3</v>
       </c>
       <c r="H28" t="n">
-        <v>43.6</v>
+        <v>63.7</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>-256.01</v>
+        <v>174.2</v>
       </c>
       <c r="K28" t="n">
-        <v>411.59</v>
+        <v>104.84</v>
       </c>
       <c r="L28" t="n">
-        <v>484.71</v>
+        <v>203.31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:28:04</t>
+          <t>06:27:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="F29" t="n">
-        <v>13.87</v>
+        <v>14.42</v>
       </c>
       <c r="G29" t="n">
-        <v>325</v>
+        <v>328.3</v>
       </c>
       <c r="H29" t="n">
-        <v>52.3</v>
+        <v>53.7</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>77.56</v>
+        <v>-38.52</v>
       </c>
       <c r="K29" t="n">
-        <v>59.29</v>
+        <v>112.55</v>
       </c>
       <c r="L29" t="n">
-        <v>97.62</v>
+        <v>118.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:29:42</t>
+          <t>06:28:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.49</v>
+        <v>4.61</v>
       </c>
       <c r="F30" t="n">
-        <v>13.01</v>
+        <v>10.62</v>
       </c>
       <c r="G30" t="n">
-        <v>322.2</v>
+        <v>329.4</v>
       </c>
       <c r="H30" t="n">
-        <v>26.5</v>
+        <v>45.6</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-85.81</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-15.43</v>
+        <v>-82.25</v>
       </c>
       <c r="L30" t="n">
-        <v>87.19</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:31:05</t>
+          <t>06:31:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.68</v>
+        <v>5.4</v>
       </c>
       <c r="F31" t="n">
-        <v>15.09</v>
+        <v>13.49</v>
       </c>
       <c r="G31" t="n">
-        <v>336.9</v>
+        <v>328.8</v>
       </c>
       <c r="H31" t="n">
-        <v>57.1</v>
+        <v>35</v>
       </c>
       <c r="I31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-85.48999999999999</v>
+        <v>-7.89</v>
       </c>
       <c r="K31" t="n">
-        <v>35.85</v>
+        <v>-206.91</v>
       </c>
       <c r="L31" t="n">
-        <v>92.70999999999999</v>
+        <v>207.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:36:14</t>
+          <t>06:34:06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.78</v>
+        <v>4.58</v>
       </c>
       <c r="F32" t="n">
-        <v>9.26</v>
+        <v>10.98</v>
       </c>
       <c r="G32" t="n">
-        <v>321.4</v>
+        <v>324.9</v>
       </c>
       <c r="H32" t="n">
-        <v>63.8</v>
+        <v>61.4</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>47.74</v>
+        <v>-138.75</v>
       </c>
       <c r="K32" t="n">
-        <v>57.25</v>
+        <v>14.68</v>
       </c>
       <c r="L32" t="n">
-        <v>74.54000000000001</v>
+        <v>139.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:37:36</t>
+          <t>06:35:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.4</v>
+        <v>5.28</v>
       </c>
       <c r="F33" t="n">
-        <v>9.52</v>
+        <v>14.24</v>
       </c>
       <c r="G33" t="n">
-        <v>325.8</v>
+        <v>328.7</v>
       </c>
       <c r="H33" t="n">
-        <v>43.4</v>
+        <v>61.9</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>48.97</v>
+        <v>-6.74</v>
       </c>
       <c r="K33" t="n">
-        <v>82.16</v>
+        <v>148.31</v>
       </c>
       <c r="L33" t="n">
-        <v>95.64</v>
+        <v>148.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:39:00</t>
+          <t>06:37:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.31</v>
+        <v>6.28</v>
       </c>
       <c r="F34" t="n">
-        <v>13.04</v>
+        <v>13.16</v>
       </c>
       <c r="G34" t="n">
-        <v>324.4</v>
+        <v>319.9</v>
       </c>
       <c r="H34" t="n">
-        <v>59.9</v>
+        <v>50.9</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>102.06</v>
+        <v>-165.48</v>
       </c>
       <c r="K34" t="n">
-        <v>-81.98999999999999</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>130.91</v>
+        <v>187.56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:43:46</t>
+          <t>06:42:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.07</v>
+        <v>5.41</v>
       </c>
       <c r="F35" t="n">
-        <v>17.23</v>
+        <v>14.68</v>
       </c>
       <c r="G35" t="n">
-        <v>330</v>
+        <v>323.1</v>
       </c>
       <c r="H35" t="n">
-        <v>23.2</v>
+        <v>9.6</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>37.99</v>
+        <v>206.71</v>
       </c>
       <c r="K35" t="n">
-        <v>202.37</v>
+        <v>8.68</v>
       </c>
       <c r="L35" t="n">
-        <v>205.9</v>
+        <v>206.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:45:42</t>
+          <t>06:44:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.11</v>
+        <v>5.89</v>
       </c>
       <c r="F36" t="n">
-        <v>14.17</v>
+        <v>12.35</v>
       </c>
       <c r="G36" t="n">
-        <v>328.4</v>
+        <v>334.1</v>
       </c>
       <c r="H36" t="n">
-        <v>77.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-96.95</v>
+        <v>-218.44</v>
       </c>
       <c r="K36" t="n">
-        <v>201.87</v>
+        <v>209.1</v>
       </c>
       <c r="L36" t="n">
-        <v>223.94</v>
+        <v>302.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:47:03</t>
+          <t>06:47:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.58</v>
+        <v>5.21</v>
       </c>
       <c r="F37" t="n">
-        <v>12.59</v>
+        <v>11.24</v>
       </c>
       <c r="G37" t="n">
-        <v>318.5</v>
+        <v>326</v>
       </c>
       <c r="H37" t="n">
-        <v>57</v>
+        <v>52.1</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>173.69</v>
+        <v>191.43</v>
       </c>
       <c r="K37" t="n">
-        <v>48.05</v>
+        <v>187.01</v>
       </c>
       <c r="L37" t="n">
-        <v>180.21</v>
+        <v>267.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:51:03</t>
+          <t>06:52:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.04</v>
+        <v>5.43</v>
       </c>
       <c r="F38" t="n">
-        <v>15.3</v>
+        <v>11.28</v>
       </c>
       <c r="G38" t="n">
-        <v>318.2</v>
+        <v>324.3</v>
       </c>
       <c r="H38" t="n">
-        <v>71.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-234.85</v>
+        <v>-220</v>
       </c>
       <c r="K38" t="n">
-        <v>174.09</v>
+        <v>-188.53</v>
       </c>
       <c r="L38" t="n">
-        <v>292.33</v>
+        <v>289.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:52:21</t>
+          <t>06:53:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.46</v>
+        <v>5.37</v>
       </c>
       <c r="F39" t="n">
-        <v>14.68</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>325.5</v>
+        <v>330.9</v>
       </c>
       <c r="H39" t="n">
-        <v>26.8</v>
+        <v>53.1</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.15</v>
+        <v>-126.44</v>
       </c>
       <c r="K39" t="n">
-        <v>265.16</v>
+        <v>252.69</v>
       </c>
       <c r="L39" t="n">
-        <v>265.2</v>
+        <v>282.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:54:03</t>
+          <t>06:54:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>6.12</v>
+        <v>5.12</v>
       </c>
       <c r="F40" t="n">
-        <v>16.24</v>
+        <v>10.33</v>
       </c>
       <c r="G40" t="n">
-        <v>315.4</v>
+        <v>323.6</v>
       </c>
       <c r="H40" t="n">
-        <v>64.2</v>
+        <v>40.1</v>
       </c>
       <c r="I40" t="n">
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>136.82</v>
+        <v>-155.5</v>
       </c>
       <c r="K40" t="n">
-        <v>286.77</v>
+        <v>205.61</v>
       </c>
       <c r="L40" t="n">
-        <v>317.74</v>
+        <v>257.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:58:58</t>
+          <t>06:58:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.58</v>
+        <v>5.15</v>
       </c>
       <c r="F41" t="n">
-        <v>12.16</v>
+        <v>13.94</v>
       </c>
       <c r="G41" t="n">
-        <v>322.9</v>
+        <v>331.2</v>
       </c>
       <c r="H41" t="n">
-        <v>59.6</v>
+        <v>27.5</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J41" t="n">
-        <v>-142.73</v>
+        <v>-17.11</v>
       </c>
       <c r="K41" t="n">
-        <v>-229.95</v>
+        <v>-426.84</v>
       </c>
       <c r="L41" t="n">
-        <v>270.65</v>
+        <v>427.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:00:20</t>
+          <t>07:00:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.63</v>
+        <v>4.84</v>
       </c>
       <c r="F42" t="n">
-        <v>15.55</v>
+        <v>14.68</v>
       </c>
       <c r="G42" t="n">
-        <v>323.2</v>
+        <v>321.4</v>
       </c>
       <c r="H42" t="n">
-        <v>15.4</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>273.01</v>
+        <v>-298.05</v>
       </c>
       <c r="K42" t="n">
-        <v>225.55</v>
+        <v>-145.16</v>
       </c>
       <c r="L42" t="n">
-        <v>354.13</v>
+        <v>331.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:02:21</t>
+          <t>07:02:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.4</v>
+        <v>6.71</v>
       </c>
       <c r="F43" t="n">
-        <v>14.62</v>
+        <v>17.36</v>
       </c>
       <c r="G43" t="n">
-        <v>327.1</v>
+        <v>325.1</v>
       </c>
       <c r="H43" t="n">
-        <v>79.2</v>
+        <v>48.3</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>102.35</v>
+        <v>-157.06</v>
       </c>
       <c r="K43" t="n">
-        <v>279.31</v>
+        <v>441.09</v>
       </c>
       <c r="L43" t="n">
-        <v>297.47</v>
+        <v>468.22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:14:53</t>
+          <t>07:11:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.2</v>
+        <v>6.39</v>
       </c>
       <c r="F44" t="n">
-        <v>15.71</v>
+        <v>17.12</v>
       </c>
       <c r="G44" t="n">
-        <v>319.1</v>
+        <v>329.9</v>
       </c>
       <c r="H44" t="n">
-        <v>15.6</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>129.19</v>
+        <v>-88.66</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.02</v>
+        <v>117.81</v>
       </c>
       <c r="L44" t="n">
-        <v>129.22</v>
+        <v>147.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:16:50</t>
+          <t>07:13:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.46</v>
+        <v>7.06</v>
       </c>
       <c r="F45" t="n">
-        <v>13.15</v>
+        <v>17.36</v>
       </c>
       <c r="G45" t="n">
-        <v>322.2</v>
+        <v>308.1</v>
       </c>
       <c r="H45" t="n">
-        <v>63.6</v>
+        <v>51</v>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>50.26</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-68.86</v>
+        <v>18.54</v>
       </c>
       <c r="L45" t="n">
-        <v>85.25</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:18:14</t>
+          <t>07:15:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.05</v>
+        <v>5.56</v>
       </c>
       <c r="F46" t="n">
-        <v>17.13</v>
+        <v>13.94</v>
       </c>
       <c r="G46" t="n">
-        <v>326.5</v>
+        <v>335.4</v>
       </c>
       <c r="H46" t="n">
-        <v>62.6</v>
+        <v>29</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>17.21</v>
+        <v>-41.42</v>
       </c>
       <c r="K46" t="n">
-        <v>166.36</v>
+        <v>-78.14</v>
       </c>
       <c r="L46" t="n">
-        <v>167.25</v>
+        <v>88.44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:23:56</t>
+          <t>07:20:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.17</v>
+        <v>5.96</v>
       </c>
       <c r="F47" t="n">
-        <v>13.21</v>
+        <v>11.87</v>
       </c>
       <c r="G47" t="n">
-        <v>317.3</v>
+        <v>323.8</v>
       </c>
       <c r="H47" t="n">
-        <v>72.3</v>
+        <v>80.2</v>
       </c>
       <c r="I47" t="n">
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-116.85</v>
+        <v>-47.27</v>
       </c>
       <c r="K47" t="n">
-        <v>131.03</v>
+        <v>-141.92</v>
       </c>
       <c r="L47" t="n">
-        <v>175.56</v>
+        <v>149.58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:25:26</t>
+          <t>07:22:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.29</v>
+        <v>6.24</v>
       </c>
       <c r="F48" t="n">
-        <v>14.63</v>
+        <v>17.36</v>
       </c>
       <c r="G48" t="n">
-        <v>325.1</v>
+        <v>317.9</v>
       </c>
       <c r="H48" t="n">
-        <v>64.59999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-134.98</v>
+        <v>121.5</v>
       </c>
       <c r="K48" t="n">
-        <v>48.27</v>
+        <v>50.36</v>
       </c>
       <c r="L48" t="n">
-        <v>143.35</v>
+        <v>131.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:28:11</t>
+          <t>07:24:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.3</v>
+        <v>5.82</v>
       </c>
       <c r="F49" t="n">
-        <v>17.36</v>
+        <v>14.5</v>
       </c>
       <c r="G49" t="n">
-        <v>322.2</v>
+        <v>307.8</v>
       </c>
       <c r="H49" t="n">
-        <v>28.5</v>
+        <v>51.8</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>12.66</v>
+        <v>-147.32</v>
       </c>
       <c r="K49" t="n">
-        <v>-167.12</v>
+        <v>-19.1</v>
       </c>
       <c r="L49" t="n">
-        <v>167.6</v>
+        <v>148.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:33:09</t>
+          <t>07:28:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2140,31 +2140,31 @@
         <v>5.92</v>
       </c>
       <c r="F50" t="n">
-        <v>15.22</v>
+        <v>14.67</v>
       </c>
       <c r="G50" t="n">
-        <v>315.4</v>
+        <v>327.7</v>
       </c>
       <c r="H50" t="n">
-        <v>25.3</v>
+        <v>63</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J50" t="n">
-        <v>151.15</v>
+        <v>-35.12</v>
       </c>
       <c r="K50" t="n">
-        <v>-137.8</v>
+        <v>230.1</v>
       </c>
       <c r="L50" t="n">
-        <v>204.54</v>
+        <v>232.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:35:03</t>
+          <t>07:29:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.81</v>
+        <v>5.97</v>
       </c>
       <c r="F51" t="n">
-        <v>17.36</v>
+        <v>14.11</v>
       </c>
       <c r="G51" t="n">
-        <v>324.7</v>
+        <v>317.3</v>
       </c>
       <c r="H51" t="n">
-        <v>51.9</v>
+        <v>57.5</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-192.56</v>
+        <v>-153.56</v>
       </c>
       <c r="K51" t="n">
-        <v>-37.42</v>
+        <v>172.54</v>
       </c>
       <c r="L51" t="n">
-        <v>196.17</v>
+        <v>230.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:36:52</t>
+          <t>07:30:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.46</v>
+        <v>6.13</v>
       </c>
       <c r="F52" t="n">
-        <v>14.05</v>
+        <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>337.6</v>
+        <v>322.3</v>
       </c>
       <c r="H52" t="n">
-        <v>34.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>200.53</v>
+        <v>184.92</v>
       </c>
       <c r="K52" t="n">
-        <v>74.84</v>
+        <v>-31.32</v>
       </c>
       <c r="L52" t="n">
-        <v>214.04</v>
+        <v>187.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:39:42</t>
+          <t>07:34:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.29</v>
+        <v>6.07</v>
       </c>
       <c r="F53" t="n">
-        <v>15.57</v>
+        <v>13.55</v>
       </c>
       <c r="G53" t="n">
-        <v>326.5</v>
+        <v>308.5</v>
       </c>
       <c r="H53" t="n">
-        <v>57.9</v>
+        <v>46.5</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-39.11</v>
+        <v>-114.45</v>
       </c>
       <c r="K53" t="n">
-        <v>288.74</v>
+        <v>225.83</v>
       </c>
       <c r="L53" t="n">
-        <v>291.38</v>
+        <v>253.18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:41:42</t>
+          <t>07:35:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.58</v>
+        <v>6.04</v>
       </c>
       <c r="F54" t="n">
-        <v>14.75</v>
+        <v>15.88</v>
       </c>
       <c r="G54" t="n">
-        <v>323.3</v>
+        <v>314.9</v>
       </c>
       <c r="H54" t="n">
-        <v>16</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>37.68</v>
+        <v>-327.27</v>
       </c>
       <c r="K54" t="n">
-        <v>104.5</v>
+        <v>153.63</v>
       </c>
       <c r="L54" t="n">
-        <v>111.08</v>
+        <v>361.54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:43:25</t>
+          <t>07:36:54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.39</v>
+        <v>5.54</v>
       </c>
       <c r="F55" t="n">
-        <v>17.36</v>
+        <v>11.74</v>
       </c>
       <c r="G55" t="n">
-        <v>320.4</v>
+        <v>330.8</v>
       </c>
       <c r="H55" t="n">
-        <v>61.2</v>
+        <v>48</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>48.8</v>
+        <v>191.67</v>
       </c>
       <c r="K55" t="n">
-        <v>249.4</v>
+        <v>82.05</v>
       </c>
       <c r="L55" t="n">
-        <v>254.13</v>
+        <v>208.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:48:00</t>
+          <t>07:40:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.56</v>
+        <v>5.77</v>
       </c>
       <c r="F56" t="n">
-        <v>16.6</v>
+        <v>13.44</v>
       </c>
       <c r="G56" t="n">
-        <v>335.7</v>
+        <v>325.8</v>
       </c>
       <c r="H56" t="n">
-        <v>77.2</v>
+        <v>43.4</v>
       </c>
       <c r="I56" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>311.2</v>
+        <v>257.15</v>
       </c>
       <c r="K56" t="n">
-        <v>298.03</v>
+        <v>276.15</v>
       </c>
       <c r="L56" t="n">
-        <v>430.89</v>
+        <v>377.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:49:39</t>
+          <t>07:43:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.18</v>
+        <v>5.66</v>
       </c>
       <c r="F57" t="n">
-        <v>16.57</v>
+        <v>14.52</v>
       </c>
       <c r="G57" t="n">
-        <v>322</v>
+        <v>331.4</v>
       </c>
       <c r="H57" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-329.34</v>
+        <v>-226.4</v>
       </c>
       <c r="K57" t="n">
-        <v>-263.07</v>
+        <v>-324.81</v>
       </c>
       <c r="L57" t="n">
-        <v>421.51</v>
+        <v>395.93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:51:48</t>
+          <t>07:44:16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.26</v>
+        <v>6.14</v>
       </c>
       <c r="F58" t="n">
-        <v>16.55</v>
+        <v>17.36</v>
       </c>
       <c r="G58" t="n">
-        <v>322.5</v>
+        <v>323.1</v>
       </c>
       <c r="H58" t="n">
-        <v>47.7</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>12.6</v>
+        <v>584.6900000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>507.75</v>
+        <v>-315.51</v>
       </c>
       <c r="L58" t="n">
-        <v>507.91</v>
+        <v>664.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:03:09</t>
+          <t>07:56:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.25</v>
+        <v>6.81</v>
       </c>
       <c r="F59" t="n">
-        <v>11.68</v>
+        <v>15.79</v>
       </c>
       <c r="G59" t="n">
-        <v>304</v>
+        <v>324.3</v>
       </c>
       <c r="H59" t="n">
-        <v>59.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J59" t="n">
-        <v>14.05</v>
+        <v>3.03</v>
       </c>
       <c r="K59" t="n">
-        <v>102.68</v>
+        <v>159.73</v>
       </c>
       <c r="L59" t="n">
-        <v>103.64</v>
+        <v>159.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:05:22</t>
+          <t>07:57:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.71</v>
+        <v>6.12</v>
       </c>
       <c r="F60" t="n">
-        <v>13.97</v>
+        <v>15.22</v>
       </c>
       <c r="G60" t="n">
-        <v>328.4</v>
+        <v>316</v>
       </c>
       <c r="H60" t="n">
-        <v>64.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I60" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>-127.77</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>42.99</v>
+        <v>114.77</v>
       </c>
       <c r="L60" t="n">
-        <v>134.81</v>
+        <v>137.29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:06:08</t>
+          <t>07:59:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.33</v>
+        <v>5.92</v>
       </c>
       <c r="F61" t="n">
-        <v>10.58</v>
+        <v>13.67</v>
       </c>
       <c r="G61" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H61" t="n">
-        <v>73.5</v>
+        <v>55.2</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J61" t="n">
-        <v>-109.53</v>
+        <v>147.76</v>
       </c>
       <c r="K61" t="n">
-        <v>65.68000000000001</v>
+        <v>-7.25</v>
       </c>
       <c r="L61" t="n">
-        <v>127.72</v>
+        <v>147.94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:10:34</t>
+          <t>08:03:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.07</v>
+        <v>5.53</v>
       </c>
       <c r="F62" t="n">
-        <v>17.36</v>
+        <v>13.88</v>
       </c>
       <c r="G62" t="n">
-        <v>329.3</v>
+        <v>324.4</v>
       </c>
       <c r="H62" t="n">
-        <v>41.8</v>
+        <v>60.9</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>28.37</v>
+        <v>-69.84999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>230.24</v>
+        <v>184.45</v>
       </c>
       <c r="L62" t="n">
-        <v>231.98</v>
+        <v>197.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:12:47</t>
+          <t>08:05:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.95</v>
+        <v>5.22</v>
       </c>
       <c r="F63" t="n">
-        <v>11.2</v>
+        <v>10.48</v>
       </c>
       <c r="G63" t="n">
-        <v>323.8</v>
+        <v>334.1</v>
       </c>
       <c r="H63" t="n">
-        <v>30.3</v>
+        <v>46.8</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>-29.99</v>
+        <v>25.7</v>
       </c>
       <c r="K63" t="n">
-        <v>156.8</v>
+        <v>162.08</v>
       </c>
       <c r="L63" t="n">
-        <v>159.64</v>
+        <v>164.11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:14:50</t>
+          <t>08:07:37</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.17</v>
+        <v>5.38</v>
       </c>
       <c r="F64" t="n">
-        <v>14.08</v>
+        <v>15.45</v>
       </c>
       <c r="G64" t="n">
-        <v>319.6</v>
+        <v>306.5</v>
       </c>
       <c r="H64" t="n">
-        <v>65.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>35.11</v>
+        <v>89.61</v>
       </c>
       <c r="K64" t="n">
-        <v>139.18</v>
+        <v>116.77</v>
       </c>
       <c r="L64" t="n">
-        <v>143.54</v>
+        <v>147.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:21:12</t>
+          <t>08:12:06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.4</v>
+        <v>5.85</v>
       </c>
       <c r="F65" t="n">
-        <v>14.19</v>
+        <v>13.69</v>
       </c>
       <c r="G65" t="n">
-        <v>323.5</v>
+        <v>322.3</v>
       </c>
       <c r="H65" t="n">
-        <v>52.6</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-68.98</v>
+        <v>-223.09</v>
       </c>
       <c r="K65" t="n">
-        <v>211.55</v>
+        <v>80.12</v>
       </c>
       <c r="L65" t="n">
-        <v>222.51</v>
+        <v>237.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:22:12</t>
+          <t>08:13:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.55</v>
+        <v>5.49</v>
       </c>
       <c r="F66" t="n">
-        <v>12.91</v>
+        <v>15.94</v>
       </c>
       <c r="G66" t="n">
-        <v>324.3</v>
+        <v>339</v>
       </c>
       <c r="H66" t="n">
-        <v>60.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>-154.33</v>
+        <v>-180.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-79.11</v>
+        <v>-31.22</v>
       </c>
       <c r="L66" t="n">
-        <v>173.42</v>
+        <v>183.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:23:41</t>
+          <t>08:14:09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>7.48</v>
+        <v>6.53</v>
       </c>
       <c r="F67" t="n">
-        <v>17.36</v>
+        <v>15.62</v>
       </c>
       <c r="G67" t="n">
-        <v>309.3</v>
+        <v>322.2</v>
       </c>
       <c r="H67" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="I67" t="n">
         <v>32</v>
       </c>
-      <c r="I67" t="n">
-        <v>21</v>
-      </c>
       <c r="J67" t="n">
-        <v>217.08</v>
+        <v>-92.83</v>
       </c>
       <c r="K67" t="n">
-        <v>77.04000000000001</v>
+        <v>-243.21</v>
       </c>
       <c r="L67" t="n">
-        <v>230.35</v>
+        <v>260.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:27:23</t>
+          <t>08:19:03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>6.37</v>
+        <v>5.66</v>
       </c>
       <c r="F68" t="n">
-        <v>17.36</v>
+        <v>15.7</v>
       </c>
       <c r="G68" t="n">
-        <v>313</v>
+        <v>317.5</v>
       </c>
       <c r="H68" t="n">
-        <v>39.2</v>
+        <v>54.4</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-336.75</v>
+        <v>-0.68</v>
       </c>
       <c r="K68" t="n">
-        <v>244.07</v>
+        <v>-181.58</v>
       </c>
       <c r="L68" t="n">
-        <v>415.9</v>
+        <v>181.58</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:29:02</t>
+          <t>08:21:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.84</v>
+        <v>6.18</v>
       </c>
       <c r="F69" t="n">
-        <v>15.54</v>
+        <v>14.11</v>
       </c>
       <c r="G69" t="n">
-        <v>330.5</v>
+        <v>332.3</v>
       </c>
       <c r="H69" t="n">
-        <v>64.2</v>
+        <v>71.5</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-208.44</v>
+        <v>109.63</v>
       </c>
       <c r="K69" t="n">
-        <v>277.9</v>
+        <v>224.83</v>
       </c>
       <c r="L69" t="n">
-        <v>347.39</v>
+        <v>250.14</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:31:19</t>
+          <t>08:23:21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.18</v>
+        <v>7.16</v>
       </c>
       <c r="F70" t="n">
-        <v>15.86</v>
+        <v>17.36</v>
       </c>
       <c r="G70" t="n">
-        <v>338.4</v>
+        <v>340.3</v>
       </c>
       <c r="H70" t="n">
-        <v>65.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>278.81</v>
+        <v>66.75</v>
       </c>
       <c r="K70" t="n">
-        <v>-64.75</v>
+        <v>341.25</v>
       </c>
       <c r="L70" t="n">
-        <v>286.23</v>
+        <v>347.72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:36:03</t>
+          <t>08:28:37</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.75</v>
+        <v>5.02</v>
       </c>
       <c r="F71" t="n">
-        <v>17.36</v>
+        <v>12.09</v>
       </c>
       <c r="G71" t="n">
-        <v>314.2</v>
+        <v>341.1</v>
       </c>
       <c r="H71" t="n">
-        <v>43.7</v>
+        <v>41.4</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-273.11</v>
+        <v>-51.86</v>
       </c>
       <c r="K71" t="n">
-        <v>-304.32</v>
+        <v>-316.56</v>
       </c>
       <c r="L71" t="n">
-        <v>408.9</v>
+        <v>320.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:37:29</t>
+          <t>08:30:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.55</v>
+        <v>6.08</v>
       </c>
       <c r="F72" t="n">
-        <v>14.33</v>
+        <v>17.07</v>
       </c>
       <c r="G72" t="n">
-        <v>325.3</v>
+        <v>324</v>
       </c>
       <c r="H72" t="n">
-        <v>61.7</v>
+        <v>57.4</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-202.73</v>
+        <v>-431.92</v>
       </c>
       <c r="K72" t="n">
-        <v>269.77</v>
+        <v>-164.91</v>
       </c>
       <c r="L72" t="n">
-        <v>337.46</v>
+        <v>462.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:38:40</t>
+          <t>08:31:09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.34</v>
+        <v>5.91</v>
       </c>
       <c r="F73" t="n">
-        <v>17.36</v>
+        <v>15.73</v>
       </c>
       <c r="G73" t="n">
-        <v>324.4</v>
+        <v>319</v>
       </c>
       <c r="H73" t="n">
-        <v>51.2</v>
+        <v>50</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-416.16</v>
+        <v>-34.71</v>
       </c>
       <c r="K73" t="n">
-        <v>-62.08</v>
+        <v>403.97</v>
       </c>
       <c r="L73" t="n">
-        <v>420.77</v>
+        <v>405.46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:50:28</t>
+          <t>08:41:41</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.98</v>
+        <v>6.82</v>
       </c>
       <c r="F74" t="n">
-        <v>14.63</v>
+        <v>17.36</v>
       </c>
       <c r="G74" t="n">
-        <v>319.9</v>
+        <v>312.3</v>
       </c>
       <c r="H74" t="n">
-        <v>60.2</v>
+        <v>53</v>
       </c>
       <c r="I74" t="n">
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>139.87</v>
+        <v>-78.95</v>
       </c>
       <c r="K74" t="n">
-        <v>-75.88</v>
+        <v>123.99</v>
       </c>
       <c r="L74" t="n">
-        <v>159.12</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:51:40</t>
+          <t>08:42:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.7</v>
+        <v>5.32</v>
       </c>
       <c r="F75" t="n">
-        <v>17.36</v>
+        <v>14.42</v>
       </c>
       <c r="G75" t="n">
-        <v>313.4</v>
+        <v>318.4</v>
       </c>
       <c r="H75" t="n">
-        <v>61.8</v>
+        <v>56.4</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-37.05</v>
+        <v>-66.52</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.82</v>
+        <v>-96.51000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>37.16</v>
+        <v>117.22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:53:31</t>
+          <t>08:43:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.44</v>
+        <v>5.76</v>
       </c>
       <c r="F76" t="n">
-        <v>15.8</v>
+        <v>14.47</v>
       </c>
       <c r="G76" t="n">
-        <v>342.4</v>
+        <v>315.9</v>
       </c>
       <c r="H76" t="n">
-        <v>50.7</v>
+        <v>53</v>
       </c>
       <c r="I76" t="n">
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>109.6</v>
+        <v>7.58</v>
       </c>
       <c r="K76" t="n">
-        <v>-18.32</v>
+        <v>127.63</v>
       </c>
       <c r="L76" t="n">
-        <v>111.12</v>
+        <v>127.86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:58:53</t>
+          <t>08:49:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.62</v>
+        <v>6.02</v>
       </c>
       <c r="F77" t="n">
-        <v>17.36</v>
+        <v>16.95</v>
       </c>
       <c r="G77" t="n">
-        <v>321.1</v>
+        <v>325.3</v>
       </c>
       <c r="H77" t="n">
-        <v>49.3</v>
+        <v>59.4</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>201.4</v>
+        <v>42.58</v>
       </c>
       <c r="K77" t="n">
-        <v>9.23</v>
+        <v>-170.29</v>
       </c>
       <c r="L77" t="n">
-        <v>201.61</v>
+        <v>175.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:01:23</t>
+          <t>08:50:08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.12</v>
+        <v>6.7</v>
       </c>
       <c r="F78" t="n">
-        <v>16.19</v>
+        <v>17.36</v>
       </c>
       <c r="G78" t="n">
-        <v>319</v>
+        <v>308.6</v>
       </c>
       <c r="H78" t="n">
-        <v>58.3</v>
+        <v>57.4</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-143.38</v>
+        <v>176</v>
       </c>
       <c r="K78" t="n">
-        <v>30.17</v>
+        <v>36.81</v>
       </c>
       <c r="L78" t="n">
-        <v>146.52</v>
+        <v>179.81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:02:12</t>
+          <t>08:51:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.16</v>
+        <v>6.26</v>
       </c>
       <c r="F79" t="n">
-        <v>17.36</v>
+        <v>13.69</v>
       </c>
       <c r="G79" t="n">
-        <v>324.6</v>
+        <v>321.4</v>
       </c>
       <c r="H79" t="n">
-        <v>43.9</v>
+        <v>45.7</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-216.65</v>
+        <v>37.01</v>
       </c>
       <c r="K79" t="n">
-        <v>56.43</v>
+        <v>-187.07</v>
       </c>
       <c r="L79" t="n">
-        <v>223.88</v>
+        <v>190.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:07:38</t>
+          <t>08:56:35</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.64</v>
+        <v>6.71</v>
       </c>
       <c r="F80" t="n">
-        <v>14.84</v>
+        <v>17.36</v>
       </c>
       <c r="G80" t="n">
-        <v>324.4</v>
+        <v>333.1</v>
       </c>
       <c r="H80" t="n">
-        <v>33.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-86.06</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-180.84</v>
+        <v>236.3</v>
       </c>
       <c r="L80" t="n">
-        <v>200.27</v>
+        <v>245.15</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:10:02</t>
+          <t>08:58:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>5.14</v>
       </c>
       <c r="F81" t="n">
-        <v>15.29</v>
+        <v>14.87</v>
       </c>
       <c r="G81" t="n">
         <v>319.9</v>
       </c>
       <c r="H81" t="n">
-        <v>41</v>
+        <v>48.8</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-182.15</v>
+        <v>103.2</v>
       </c>
       <c r="K81" t="n">
-        <v>143.83</v>
+        <v>-48.66</v>
       </c>
       <c r="L81" t="n">
-        <v>232.09</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:12:33</t>
+          <t>08:59:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.44</v>
+        <v>6.12</v>
       </c>
       <c r="F82" t="n">
-        <v>16.28</v>
+        <v>15.05</v>
       </c>
       <c r="G82" t="n">
-        <v>315.7</v>
+        <v>319.7</v>
       </c>
       <c r="H82" t="n">
-        <v>36.2</v>
+        <v>87</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>81.77</v>
+        <v>-196.4</v>
       </c>
       <c r="K82" t="n">
-        <v>221.9</v>
+        <v>-97.98</v>
       </c>
       <c r="L82" t="n">
-        <v>236.48</v>
+        <v>219.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:16:15</t>
+          <t>09:03:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.5</v>
+        <v>6.89</v>
       </c>
       <c r="F83" t="n">
-        <v>15.13</v>
+        <v>17.36</v>
       </c>
       <c r="G83" t="n">
-        <v>313.2</v>
+        <v>313.6</v>
       </c>
       <c r="H83" t="n">
-        <v>62.2</v>
+        <v>30</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-264.31</v>
+        <v>-140.44</v>
       </c>
       <c r="K83" t="n">
-        <v>36.24</v>
+        <v>249.21</v>
       </c>
       <c r="L83" t="n">
-        <v>266.79</v>
+        <v>286.06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:18:25</t>
+          <t>09:04:09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.21</v>
+        <v>5.55</v>
       </c>
       <c r="F84" t="n">
-        <v>15.87</v>
+        <v>15.65</v>
       </c>
       <c r="G84" t="n">
-        <v>318.7</v>
+        <v>319.5</v>
       </c>
       <c r="H84" t="n">
-        <v>59.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-364.57</v>
+        <v>247.42</v>
       </c>
       <c r="K84" t="n">
-        <v>26.11</v>
+        <v>18.47</v>
       </c>
       <c r="L84" t="n">
-        <v>365.51</v>
+        <v>248.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:20:31</t>
+          <t>09:06:21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.79</v>
+        <v>6.52</v>
       </c>
       <c r="F85" t="n">
         <v>17.36</v>
       </c>
       <c r="G85" t="n">
-        <v>340.5</v>
+        <v>314.8</v>
       </c>
       <c r="H85" t="n">
-        <v>44.4</v>
+        <v>20.8</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-157.14</v>
+        <v>173.38</v>
       </c>
       <c r="K85" t="n">
-        <v>187.42</v>
+        <v>-239.01</v>
       </c>
       <c r="L85" t="n">
-        <v>244.58</v>
+        <v>295.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:24:00</t>
+          <t>09:11:07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.32</v>
+        <v>6.11</v>
       </c>
       <c r="F86" t="n">
-        <v>16.09</v>
+        <v>16.07</v>
       </c>
       <c r="G86" t="n">
-        <v>333.1</v>
+        <v>312.4</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>61.1</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>461.44</v>
+        <v>310.46</v>
       </c>
       <c r="K86" t="n">
-        <v>160.61</v>
+        <v>297.53</v>
       </c>
       <c r="L86" t="n">
-        <v>488.59</v>
+        <v>430.01</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:26:09</t>
+          <t>09:12:49</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.05</v>
+        <v>6.76</v>
       </c>
       <c r="F87" t="n">
-        <v>14.57</v>
+        <v>17.36</v>
       </c>
       <c r="G87" t="n">
-        <v>319.2</v>
+        <v>307.8</v>
       </c>
       <c r="H87" t="n">
-        <v>58.2</v>
+        <v>15.1</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>359.5</v>
+        <v>-325.19</v>
       </c>
       <c r="K87" t="n">
-        <v>235.19</v>
+        <v>-58.61</v>
       </c>
       <c r="L87" t="n">
-        <v>429.6</v>
+        <v>330.43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:27:59</t>
+          <t>09:15:14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.97</v>
+        <v>6.78</v>
       </c>
       <c r="F88" t="n">
         <v>17.36</v>
       </c>
       <c r="G88" t="n">
-        <v>330.1</v>
+        <v>319.8</v>
       </c>
       <c r="H88" t="n">
-        <v>92.3</v>
+        <v>22.8</v>
       </c>
       <c r="I88" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-359.12</v>
+        <v>-356.28</v>
       </c>
       <c r="K88" t="n">
-        <v>388.49</v>
+        <v>-38.44</v>
       </c>
       <c r="L88" t="n">
-        <v>529.05</v>
+        <v>358.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>40.53</v>
+        <v>47.77</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.79</v>
+        <v>-48.06</v>
       </c>
       <c r="L14" t="n">
-        <v>57.5</v>
+        <v>67.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.63</v>
+        <v>-8.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-60.73</v>
+        <v>-69.02</v>
       </c>
       <c r="L15" t="n">
-        <v>61.2</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>8.789999999999999</v>
+        <v>11.14</v>
       </c>
       <c r="K16" t="n">
-        <v>54.43</v>
+        <v>68.98</v>
       </c>
       <c r="L16" t="n">
-        <v>55.13</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>68</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>61.82</v>
+        <v>68.86</v>
       </c>
       <c r="L17" t="n">
-        <v>91.91</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-75.40000000000001</v>
+        <v>-84.65000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>43.33</v>
+        <v>48.65</v>
       </c>
       <c r="L18" t="n">
-        <v>86.97</v>
+        <v>97.64</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>64.28</v>
+        <v>75.92</v>
       </c>
       <c r="K19" t="n">
-        <v>17.84</v>
+        <v>21.07</v>
       </c>
       <c r="L19" t="n">
-        <v>66.7</v>
+        <v>78.79000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-167.26</v>
+        <v>-193.59</v>
       </c>
       <c r="K20" t="n">
-        <v>124.24</v>
+        <v>143.8</v>
       </c>
       <c r="L20" t="n">
-        <v>208.35</v>
+        <v>241.15</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>97.12</v>
+        <v>114.81</v>
       </c>
       <c r="K21" t="n">
-        <v>-112.56</v>
+        <v>-133.07</v>
       </c>
       <c r="L21" t="n">
-        <v>148.67</v>
+        <v>175.75</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-78.25</v>
+        <v>-103.17</v>
       </c>
       <c r="K22" t="n">
-        <v>-77.69</v>
+        <v>-102.43</v>
       </c>
       <c r="L22" t="n">
-        <v>110.27</v>
+        <v>145.39</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>11.1</v>
+        <v>15.63</v>
       </c>
       <c r="K23" t="n">
-        <v>-159.44</v>
+        <v>-224.56</v>
       </c>
       <c r="L23" t="n">
-        <v>159.83</v>
+        <v>225.11</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-72.56999999999999</v>
+        <v>-92.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>155.04</v>
+        <v>197.84</v>
       </c>
       <c r="L24" t="n">
-        <v>171.18</v>
+        <v>218.44</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>157.53</v>
+        <v>214.85</v>
       </c>
       <c r="K25" t="n">
-        <v>109.17</v>
+        <v>148.89</v>
       </c>
       <c r="L25" t="n">
-        <v>191.66</v>
+        <v>261.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>288.78</v>
+        <v>412.21</v>
       </c>
       <c r="K26" t="n">
-        <v>-63.74</v>
+        <v>-90.98</v>
       </c>
       <c r="L26" t="n">
-        <v>295.73</v>
+        <v>422.13</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-119.31</v>
+        <v>-173.07</v>
       </c>
       <c r="K27" t="n">
-        <v>-162.32</v>
+        <v>-235.45</v>
       </c>
       <c r="L27" t="n">
-        <v>201.45</v>
+        <v>292.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>118.71</v>
+        <v>169.21</v>
       </c>
       <c r="K28" t="n">
-        <v>274.89</v>
+        <v>391.84</v>
       </c>
       <c r="L28" t="n">
-        <v>299.42</v>
+        <v>426.82</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>39.35</v>
+        <v>44.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.57</v>
+        <v>-65.39</v>
       </c>
       <c r="L29" t="n">
-        <v>69.73999999999999</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.93</v>
+        <v>-7.21</v>
       </c>
       <c r="K30" t="n">
-        <v>18.81</v>
+        <v>22.87</v>
       </c>
       <c r="L30" t="n">
-        <v>19.72</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.07</v>
+        <v>-4.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.26</v>
+        <v>-1.49</v>
       </c>
       <c r="L31" t="n">
-        <v>4.26</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-40.12</v>
+        <v>-46.89</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.37</v>
+        <v>-95.11</v>
       </c>
       <c r="L32" t="n">
-        <v>90.72</v>
+        <v>106.04</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-17.91</v>
+        <v>-21.22</v>
       </c>
       <c r="K33" t="n">
-        <v>68.08</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>70.39</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.32</v>
+        <v>-1.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-73.58</v>
+        <v>-96.95</v>
       </c>
       <c r="L34" t="n">
-        <v>73.59999999999999</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>58.85</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-109.02</v>
+        <v>-134.58</v>
       </c>
       <c r="L35" t="n">
-        <v>123.89</v>
+        <v>152.94</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-157.52</v>
+        <v>-190.17</v>
       </c>
       <c r="K36" t="n">
-        <v>42.94</v>
+        <v>51.84</v>
       </c>
       <c r="L36" t="n">
-        <v>163.27</v>
+        <v>197.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-236.78</v>
+        <v>-269.16</v>
       </c>
       <c r="K37" t="n">
-        <v>78.77</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>249.53</v>
+        <v>283.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-13.76</v>
+        <v>-18.52</v>
       </c>
       <c r="K38" t="n">
-        <v>223.94</v>
+        <v>301.32</v>
       </c>
       <c r="L38" t="n">
-        <v>224.36</v>
+        <v>301.88</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-30.63</v>
+        <v>-42.86</v>
       </c>
       <c r="K39" t="n">
-        <v>-158.77</v>
+        <v>-222.14</v>
       </c>
       <c r="L39" t="n">
-        <v>161.7</v>
+        <v>226.24</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-201.62</v>
+        <v>-263.61</v>
       </c>
       <c r="K40" t="n">
-        <v>-52.1</v>
+        <v>-68.11</v>
       </c>
       <c r="L40" t="n">
-        <v>208.25</v>
+        <v>272.27</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>258.22</v>
+        <v>345.37</v>
       </c>
       <c r="K41" t="n">
-        <v>-216.08</v>
+        <v>-289.02</v>
       </c>
       <c r="L41" t="n">
-        <v>336.7</v>
+        <v>450.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-243.69</v>
+        <v>-361.37</v>
       </c>
       <c r="K42" t="n">
-        <v>181.22</v>
+        <v>268.73</v>
       </c>
       <c r="L42" t="n">
-        <v>303.68</v>
+        <v>450.33</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>340.17</v>
+        <v>475.58</v>
       </c>
       <c r="K43" t="n">
-        <v>-33.36</v>
+        <v>-46.64</v>
       </c>
       <c r="L43" t="n">
-        <v>341.81</v>
+        <v>477.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>20.78</v>
+        <v>24.01</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.64</v>
+        <v>-68.92</v>
       </c>
       <c r="L44" t="n">
-        <v>63.15</v>
+        <v>72.98</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>20.48</v>
+        <v>24.31</v>
       </c>
       <c r="K45" t="n">
-        <v>63.51</v>
+        <v>75.38</v>
       </c>
       <c r="L45" t="n">
-        <v>66.73</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.51</v>
+        <v>-66.34999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>59.02</v>
+        <v>71.84</v>
       </c>
       <c r="L46" t="n">
-        <v>80.34</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>88.86</v>
+        <v>101.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.83</v>
+        <v>-67.5</v>
       </c>
       <c r="L47" t="n">
-        <v>106.57</v>
+        <v>122.27</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.18</v>
+        <v>-30.94</v>
       </c>
       <c r="K48" t="n">
-        <v>89.55</v>
+        <v>110.03</v>
       </c>
       <c r="L48" t="n">
-        <v>93.02</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>70.79000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="K49" t="n">
-        <v>-25.41</v>
+        <v>-31.81</v>
       </c>
       <c r="L49" t="n">
-        <v>75.22</v>
+        <v>94.16</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>192.67</v>
+        <v>227.38</v>
       </c>
       <c r="K50" t="n">
-        <v>-23.55</v>
+        <v>-27.79</v>
       </c>
       <c r="L50" t="n">
-        <v>194.1</v>
+        <v>229.07</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-132.48</v>
+        <v>-161.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-89.51000000000001</v>
+        <v>-108.98</v>
       </c>
       <c r="L51" t="n">
-        <v>159.88</v>
+        <v>194.66</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>137.01</v>
+        <v>181.22</v>
       </c>
       <c r="K52" t="n">
-        <v>-22.71</v>
+        <v>-30.05</v>
       </c>
       <c r="L52" t="n">
-        <v>138.88</v>
+        <v>183.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-195.68</v>
+        <v>-259.35</v>
       </c>
       <c r="K53" t="n">
-        <v>165.06</v>
+        <v>218.77</v>
       </c>
       <c r="L53" t="n">
-        <v>255.99</v>
+        <v>339.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-161.5</v>
+        <v>-235.53</v>
       </c>
       <c r="K54" t="n">
-        <v>141.49</v>
+        <v>206.35</v>
       </c>
       <c r="L54" t="n">
-        <v>214.72</v>
+        <v>313.14</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>238.21</v>
+        <v>303.79</v>
       </c>
       <c r="K55" t="n">
-        <v>142.93</v>
+        <v>182.28</v>
       </c>
       <c r="L55" t="n">
-        <v>277.8</v>
+        <v>354.28</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>47.83</v>
+        <v>69.09</v>
       </c>
       <c r="K56" t="n">
-        <v>-197.39</v>
+        <v>-285.14</v>
       </c>
       <c r="L56" t="n">
-        <v>203.1</v>
+        <v>293.39</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-35.63</v>
+        <v>-46.74</v>
       </c>
       <c r="K57" t="n">
-        <v>393.21</v>
+        <v>515.77</v>
       </c>
       <c r="L57" t="n">
-        <v>394.83</v>
+        <v>517.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-469.77</v>
+        <v>-620.28</v>
       </c>
       <c r="K58" t="n">
-        <v>-186.54</v>
+        <v>-246.31</v>
       </c>
       <c r="L58" t="n">
-        <v>505.45</v>
+        <v>667.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>86.61</v>
+        <v>97.63</v>
       </c>
       <c r="K59" t="n">
-        <v>46.29</v>
+        <v>52.17</v>
       </c>
       <c r="L59" t="n">
-        <v>98.2</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>26.83</v>
+        <v>30.4</v>
       </c>
       <c r="K60" t="n">
-        <v>61.56</v>
+        <v>69.77</v>
       </c>
       <c r="L60" t="n">
-        <v>67.16</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>68.54000000000001</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>12.85</v>
+        <v>14.91</v>
       </c>
       <c r="L61" t="n">
-        <v>69.73999999999999</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>31.4</v>
+        <v>39.04</v>
       </c>
       <c r="K62" t="n">
-        <v>-89.31</v>
+        <v>-111.04</v>
       </c>
       <c r="L62" t="n">
-        <v>94.66</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-64.72</v>
+        <v>-73.97</v>
       </c>
       <c r="K63" t="n">
-        <v>93.89</v>
+        <v>107.3</v>
       </c>
       <c r="L63" t="n">
-        <v>114.04</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-122.05</v>
+        <v>-143.83</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="L64" t="n">
-        <v>122.05</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-137.05</v>
+        <v>-161.33</v>
       </c>
       <c r="K65" t="n">
-        <v>115.33</v>
+        <v>135.76</v>
       </c>
       <c r="L65" t="n">
-        <v>179.12</v>
+        <v>210.85</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>107.41</v>
+        <v>131.83</v>
       </c>
       <c r="K66" t="n">
-        <v>88.95</v>
+        <v>109.18</v>
       </c>
       <c r="L66" t="n">
-        <v>139.46</v>
+        <v>171.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>106.79</v>
+        <v>129.6</v>
       </c>
       <c r="K67" t="n">
-        <v>-111.3</v>
+        <v>-135.08</v>
       </c>
       <c r="L67" t="n">
-        <v>154.25</v>
+        <v>187.2</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-197.31</v>
+        <v>-263.15</v>
       </c>
       <c r="K68" t="n">
-        <v>-60.14</v>
+        <v>-80.2</v>
       </c>
       <c r="L68" t="n">
-        <v>206.27</v>
+        <v>275.1</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-376.73</v>
+        <v>-448.09</v>
       </c>
       <c r="K69" t="n">
-        <v>-128.33</v>
+        <v>-152.64</v>
       </c>
       <c r="L69" t="n">
-        <v>397.99</v>
+        <v>473.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>140.66</v>
+        <v>181.18</v>
       </c>
       <c r="K70" t="n">
-        <v>261.88</v>
+        <v>337.31</v>
       </c>
       <c r="L70" t="n">
-        <v>297.27</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>428.59</v>
+        <v>598.6799999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-106.03</v>
+        <v>-148.1</v>
       </c>
       <c r="L71" t="n">
-        <v>441.51</v>
+        <v>616.72</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-458.22</v>
+        <v>-636.49</v>
       </c>
       <c r="K72" t="n">
-        <v>11.41</v>
+        <v>15.85</v>
       </c>
       <c r="L72" t="n">
-        <v>458.36</v>
+        <v>636.6799999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>368.95</v>
+        <v>531.74</v>
       </c>
       <c r="K73" t="n">
-        <v>66.83</v>
+        <v>96.31</v>
       </c>
       <c r="L73" t="n">
-        <v>374.95</v>
+        <v>540.39</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-100.94</v>
+        <v>-116.22</v>
       </c>
       <c r="K74" t="n">
-        <v>10.71</v>
+        <v>12.33</v>
       </c>
       <c r="L74" t="n">
-        <v>101.5</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>61.42</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>18.43</v>
+        <v>22.51</v>
       </c>
       <c r="L75" t="n">
-        <v>64.13</v>
+        <v>78.31999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.79</v>
+        <v>-61.01</v>
       </c>
       <c r="K76" t="n">
-        <v>-80.64</v>
+        <v>-94.98</v>
       </c>
       <c r="L76" t="n">
-        <v>95.84</v>
+        <v>112.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-98.05</v>
+        <v>-117.65</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.26</v>
+        <v>-56.7</v>
       </c>
       <c r="L77" t="n">
-        <v>108.85</v>
+        <v>130.6</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-72.45</v>
+        <v>-88.16</v>
       </c>
       <c r="K78" t="n">
-        <v>-50.96</v>
+        <v>-62</v>
       </c>
       <c r="L78" t="n">
-        <v>88.56999999999999</v>
+        <v>107.78</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-74.51000000000001</v>
+        <v>-95.95</v>
       </c>
       <c r="K79" t="n">
-        <v>5.29</v>
+        <v>6.81</v>
       </c>
       <c r="L79" t="n">
-        <v>74.7</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>175.96</v>
+        <v>222.28</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.09</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>176.1</v>
+        <v>222.46</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>231.41</v>
+        <v>266.29</v>
       </c>
       <c r="K81" t="n">
-        <v>-138.42</v>
+        <v>-159.29</v>
       </c>
       <c r="L81" t="n">
-        <v>269.65</v>
+        <v>310.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-9.85</v>
+        <v>-12.47</v>
       </c>
       <c r="K82" t="n">
-        <v>142.6</v>
+        <v>180.54</v>
       </c>
       <c r="L82" t="n">
-        <v>142.94</v>
+        <v>180.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-11.13</v>
+        <v>-15.66</v>
       </c>
       <c r="K83" t="n">
-        <v>-248.15</v>
+        <v>-349.16</v>
       </c>
       <c r="L83" t="n">
-        <v>248.4</v>
+        <v>349.51</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-309.15</v>
+        <v>-375.21</v>
       </c>
       <c r="K84" t="n">
-        <v>-195.86</v>
+        <v>-237.71</v>
       </c>
       <c r="L84" t="n">
-        <v>365.98</v>
+        <v>444.17</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>288.26</v>
+        <v>375.09</v>
       </c>
       <c r="K85" t="n">
-        <v>69.27</v>
+        <v>90.13</v>
       </c>
       <c r="L85" t="n">
-        <v>296.46</v>
+        <v>385.77</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-227.67</v>
+        <v>-299.65</v>
       </c>
       <c r="K86" t="n">
-        <v>395.1</v>
+        <v>520.02</v>
       </c>
       <c r="L86" t="n">
-        <v>456</v>
+        <v>600.17</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>274.95</v>
+        <v>417.11</v>
       </c>
       <c r="K87" t="n">
-        <v>154.86</v>
+        <v>234.93</v>
       </c>
       <c r="L87" t="n">
-        <v>315.56</v>
+        <v>478.72</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-238.92</v>
+        <v>-336.36</v>
       </c>
       <c r="K88" t="n">
-        <v>324.55</v>
+        <v>456.9</v>
       </c>
       <c r="L88" t="n">
-        <v>403.01</v>
+        <v>567.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-26.xlsx
+++ b/output/2025-04-26.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>47.77</v>
+        <v>73.09</v>
       </c>
       <c r="K14" t="n">
-        <v>-48.06</v>
+        <v>-73.54000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>67.76000000000001</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.67</v>
+        <v>-13.73</v>
       </c>
       <c r="K15" t="n">
-        <v>-69.02</v>
+        <v>-109.23</v>
       </c>
       <c r="L15" t="n">
-        <v>69.56</v>
+        <v>110.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>11.14</v>
+        <v>19.43</v>
       </c>
       <c r="K16" t="n">
-        <v>68.98</v>
+        <v>120.35</v>
       </c>
       <c r="L16" t="n">
-        <v>69.88</v>
+        <v>121.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>75.73999999999999</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>68.86</v>
+        <v>90.72</v>
       </c>
       <c r="L17" t="n">
-        <v>102.36</v>
+        <v>134.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-84.65000000000001</v>
+        <v>-117.23</v>
       </c>
       <c r="K18" t="n">
-        <v>48.65</v>
+        <v>67.37</v>
       </c>
       <c r="L18" t="n">
-        <v>97.64</v>
+        <v>135.21</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>75.92</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>21.07</v>
+        <v>25.63</v>
       </c>
       <c r="L19" t="n">
-        <v>78.79000000000001</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>44.7</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-65.39</v>
+        <v>-95.2</v>
       </c>
       <c r="L29" t="n">
-        <v>79.20999999999999</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.21</v>
+        <v>-10.93</v>
       </c>
       <c r="K30" t="n">
-        <v>22.87</v>
+        <v>34.67</v>
       </c>
       <c r="L30" t="n">
-        <v>23.98</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.8</v>
+        <v>-7.82</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.49</v>
+        <v>-2.42</v>
       </c>
       <c r="L31" t="n">
-        <v>5.02</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-46.89</v>
+        <v>-67.59</v>
       </c>
       <c r="K32" t="n">
-        <v>-95.11</v>
+        <v>-137.09</v>
       </c>
       <c r="L32" t="n">
-        <v>106.04</v>
+        <v>152.84</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.22</v>
+        <v>-27.2</v>
       </c>
       <c r="K33" t="n">
-        <v>80.68000000000001</v>
+        <v>103.41</v>
       </c>
       <c r="L33" t="n">
-        <v>83.42</v>
+        <v>106.93</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.74</v>
+        <v>-2.65</v>
       </c>
       <c r="K34" t="n">
-        <v>-96.95</v>
+        <v>-147.88</v>
       </c>
       <c r="L34" t="n">
-        <v>96.97</v>
+        <v>147.91</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>24.01</v>
+        <v>39.71</v>
       </c>
       <c r="K44" t="n">
-        <v>-68.92</v>
+        <v>-113.97</v>
       </c>
       <c r="L44" t="n">
-        <v>72.98</v>
+        <v>120.69</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>24.31</v>
+        <v>41.67</v>
       </c>
       <c r="K45" t="n">
-        <v>75.38</v>
+        <v>129.2</v>
       </c>
       <c r="L45" t="n">
-        <v>79.2</v>
+        <v>135.76</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-66.34999999999999</v>
+        <v>-128.38</v>
       </c>
       <c r="K46" t="n">
-        <v>71.84</v>
+        <v>139.02</v>
       </c>
       <c r="L46" t="n">
-        <v>97.79000000000001</v>
+        <v>189.23</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>101.95</v>
+        <v>147.39</v>
       </c>
       <c r="K47" t="n">
-        <v>-67.5</v>
+        <v>-97.58</v>
       </c>
       <c r="L47" t="n">
-        <v>122.27</v>
+        <v>176.76</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-30.94</v>
+        <v>-48.41</v>
       </c>
       <c r="K48" t="n">
-        <v>110.03</v>
+        <v>172.17</v>
       </c>
       <c r="L48" t="n">
-        <v>114.3</v>
+        <v>178.85</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>88.63</v>
+        <v>130.58</v>
       </c>
       <c r="K49" t="n">
-        <v>-31.81</v>
+        <v>-46.87</v>
       </c>
       <c r="L49" t="n">
-        <v>94.16</v>
+        <v>138.74</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>97.63</v>
+        <v>173.32</v>
       </c>
       <c r="K59" t="n">
-        <v>52.17</v>
+        <v>92.62</v>
       </c>
       <c r="L59" t="n">
-        <v>110.7</v>
+        <v>196.52</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>30.4</v>
+        <v>45.82</v>
       </c>
       <c r="K60" t="n">
-        <v>69.77</v>
+        <v>105.15</v>
       </c>
       <c r="L60" t="n">
-        <v>76.11</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>79.56999999999999</v>
+        <v>118.32</v>
       </c>
       <c r="K61" t="n">
-        <v>14.91</v>
+        <v>22.18</v>
       </c>
       <c r="L61" t="n">
-        <v>80.95</v>
+        <v>120.38</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>39.04</v>
+        <v>61.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-111.04</v>
+        <v>-175.96</v>
       </c>
       <c r="L62" t="n">
-        <v>117.7</v>
+        <v>186.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-73.97</v>
+        <v>-109.62</v>
       </c>
       <c r="K63" t="n">
-        <v>107.3</v>
+        <v>159.01</v>
       </c>
       <c r="L63" t="n">
-        <v>130.32</v>
+        <v>193.13</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-143.83</v>
+        <v>-241.84</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.11</v>
+        <v>-1.87</v>
       </c>
       <c r="L64" t="n">
-        <v>143.83</v>
+        <v>241.85</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-116.22</v>
+        <v>-237.93</v>
       </c>
       <c r="K74" t="n">
-        <v>12.33</v>
+        <v>25.24</v>
       </c>
       <c r="L74" t="n">
-        <v>116.87</v>
+        <v>239.27</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>75.01000000000001</v>
+        <v>131.55</v>
       </c>
       <c r="K75" t="n">
-        <v>22.51</v>
+        <v>39.48</v>
       </c>
       <c r="L75" t="n">
-        <v>78.31999999999999</v>
+        <v>137.35</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-61.01</v>
+        <v>-128.07</v>
       </c>
       <c r="K76" t="n">
-        <v>-94.98</v>
+        <v>-199.39</v>
       </c>
       <c r="L76" t="n">
-        <v>112.88</v>
+        <v>236.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-117.65</v>
+        <v>-186.19</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.7</v>
+        <v>-89.73</v>
       </c>
       <c r="L77" t="n">
-        <v>130.6</v>
+        <v>206.68</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-88.16</v>
+        <v>-138.53</v>
       </c>
       <c r="K78" t="n">
-        <v>-62</v>
+        <v>-97.43000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>107.78</v>
+        <v>169.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-95.95</v>
+        <v>-152.27</v>
       </c>
       <c r="K79" t="n">
-        <v>6.81</v>
+        <v>10.8</v>
       </c>
       <c r="L79" t="n">
-        <v>96.19</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="80">
